--- a/data/source/catalogo.xlsx
+++ b/data/source/catalogo.xlsx
@@ -3938,11 +3938,6 @@
 el importador las genera solo.</t>
       </text>
     </comment>
-    <comment authorId="0" ref="V34">
-      <text>
-        <t xml:space="preserve">✔ Verificado. 50W×4@4Ω, 75W×4@2Ω, 150W×2 puente. Fuente: Creative Audio (distribuidor, no oficial), https://creativeaudio.net/srx300-4v/</t>
-      </text>
-    </comment>
     <comment authorId="0" ref="W1">
       <text>
         <t xml:space="preserve">======
@@ -4111,7 +4106,7 @@
     </comment>
     <comment authorId="0" ref="V19">
       <text>
-        <t xml:space="preserve">✔ Verificado. Oficial: 90W×2@2Ω, 60W×2@4Ω, 180W×1 puente. Fuente: Logistar (distribuidor KBT), https://logistar.mx/amplificador-soldier-2-canales-clase-ab-1800w-max/</t>
+        <t xml:space="preserve">Source: Logistar (distribuidor KBT, no es web oficial del fabricante), https://logistar.mx/amplificador-soldier-mono-clase-ab-1200w-max/</t>
       </text>
     </comment>
     <comment authorId="0" ref="N36">
@@ -4244,11 +4239,6 @@
         <t xml:space="preserve">Source: Logistar (distribuidor KBT, no es web oficial del fabricante), https://logistar.mx/amplificador-marino-rango-completo-clase-d-4-canales-1200w-max/</t>
       </text>
     </comment>
-    <comment authorId="0" ref="V37">
-      <text>
-        <t xml:space="preserve">✔ Verificado. 50W×4@4Ω, 100W×4@2Ω, 200W×2 puente; 400 W total. Fuente: Sonic Electronix (distribuidor, no oficial), https://www.sonicelectronix.com/item-177723-Rockford-Fosgate-Prime-R2-R2-300X4.html (ficha comparada P400X4)</t>
-      </text>
-    </comment>
     <comment authorId="0" ref="V4">
       <text>
         <t xml:space="preserve">Source: Logistar (distribuidor KBT, no es web oficial del fabricante), https://logistar.mx/amplificador-marino-rango-completo-clase-d-4-canales-1200w-max/</t>
@@ -4427,11 +4417,6 @@
     <comment authorId="0" ref="T23">
       <text>
         <t xml:space="preserve">Source: Memphis Audio (web oficial, sección Features; no publica rangos en Hz), https://www.memphiscaraudio.com/product/viv600-4v2/</t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="V23">
-      <text>
-        <t xml:space="preserve">✔ Verificado. Oficial: 80W×4@4Ω, 150W×4@2Ω, 300W×2 puente. Fuente: Memphis Audio (oficial), https://www.memphiscaraudio.com/product/viv600-4v2/</t>
       </text>
     </comment>
     <comment authorId="0" ref="N40">
@@ -7512,7 +7497,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7329" uniqueCount="2595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7313" uniqueCount="2594">
   <si>
     <t>SONORO — Catálogo 3.0</t>
   </si>
@@ -12188,7 +12173,7 @@
     <t>HP 60 u 80 Hz · LP 80 Hz, 12 dB/oct</t>
   </si>
   <si>
-    <t>&gt;80 dB (CTA-2006)</t>
+    <t>&gt;80 dB</t>
   </si>
   <si>
     <t>400 W RMS bajo norma CEA-2006</t>
@@ -12309,9 +12294,6 @@
   </si>
   <si>
     <t>205 × 173 × 49 mm</t>
-  </si>
-  <si>
-    <t>&gt;80 dB</t>
   </si>
   <si>
     <t>50 A</t>
@@ -15306,7 +15288,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="14">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -15384,11 +15366,6 @@
       <sz val="11.0"/>
       <color theme="1"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="14">
@@ -15493,7 +15470,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="58">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -15600,7 +15577,7 @@
     <xf borderId="0" fillId="8" fontId="5" numFmtId="49" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="13" fontId="5" numFmtId="49" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
@@ -15610,9 +15587,6 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="12" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="14" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -17227,7 +17201,7 @@
         <v>67</v>
       </c>
       <c r="N1" s="21" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="O1" s="22" t="s">
         <v>179</v>
@@ -17292,19 +17266,19 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="23" t="s">
+        <v>2029</v>
+      </c>
+      <c r="B2" s="23" t="s">
         <v>2030</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="C2" s="23" t="s">
         <v>2031</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>2032</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>144</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="F2" s="32">
         <v>395.0</v>
@@ -17328,13 +17302,13 @@
       </c>
       <c r="N2" s="25"/>
       <c r="O2" s="27" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="P2" s="27" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="Q2" s="27" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="R2" s="27" t="s">
         <v>144</v>
@@ -17343,7 +17317,7 @@
         <v>206</v>
       </c>
       <c r="T2" s="27" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="U2" s="27"/>
       <c r="V2" s="27"/>
@@ -17362,19 +17336,19 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="23" t="s">
+        <v>2035</v>
+      </c>
+      <c r="B3" s="23" t="s">
         <v>2036</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="C3" s="23" t="s">
         <v>2037</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>2038</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>144</v>
       </c>
       <c r="E3" s="23" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="F3" s="32">
         <v>185.0</v>
@@ -17401,19 +17375,19 @@
         <v>1506</v>
       </c>
       <c r="P3" s="27" t="s">
+        <v>2039</v>
+      </c>
+      <c r="Q3" s="27" t="s">
         <v>2040</v>
       </c>
-      <c r="Q3" s="27" t="s">
+      <c r="R3" s="27" t="s">
         <v>2041</v>
       </c>
-      <c r="R3" s="27" t="s">
+      <c r="S3" s="27" t="s">
         <v>2042</v>
       </c>
-      <c r="S3" s="27" t="s">
+      <c r="T3" s="27" t="s">
         <v>2043</v>
-      </c>
-      <c r="T3" s="27" t="s">
-        <v>2044</v>
       </c>
       <c r="U3" s="27"/>
       <c r="V3" s="27"/>
@@ -17432,19 +17406,19 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="23" t="s">
+        <v>2044</v>
+      </c>
+      <c r="B4" s="23" t="s">
         <v>2045</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="C4" s="23" t="s">
         <v>2046</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>2047</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>144</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="F4" s="32">
         <v>150.0</v>
@@ -17471,19 +17445,19 @@
         <v>1506</v>
       </c>
       <c r="P4" s="27" t="s">
+        <v>2039</v>
+      </c>
+      <c r="Q4" s="27" t="s">
         <v>2040</v>
       </c>
-      <c r="Q4" s="27" t="s">
-        <v>2041</v>
-      </c>
       <c r="R4" s="27" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="S4" s="27" t="s">
         <v>781</v>
       </c>
       <c r="T4" s="27" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="U4" s="27"/>
       <c r="V4" s="27"/>
@@ -17502,19 +17476,19 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="23" t="s">
+        <v>2050</v>
+      </c>
+      <c r="B5" s="23" t="s">
         <v>2051</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="C5" s="23" t="s">
         <v>2052</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>2053</v>
       </c>
       <c r="D5" s="23" t="s">
         <v>144</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>2054</v>
+        <v>2053</v>
       </c>
       <c r="F5" s="32">
         <v>395.0</v>
@@ -17538,28 +17512,28 @@
       </c>
       <c r="N5" s="25"/>
       <c r="O5" s="27" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="P5" s="27" t="s">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="Q5" s="27" t="s">
         <v>1506</v>
       </c>
       <c r="R5" s="27" t="s">
+        <v>2055</v>
+      </c>
+      <c r="S5" s="27" t="s">
+        <v>2040</v>
+      </c>
+      <c r="T5" s="27" t="s">
         <v>2056</v>
-      </c>
-      <c r="S5" s="27" t="s">
-        <v>2041</v>
-      </c>
-      <c r="T5" s="27" t="s">
-        <v>2057</v>
       </c>
       <c r="U5" s="27" t="s">
         <v>781</v>
       </c>
       <c r="V5" s="27" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="W5" s="27"/>
       <c r="X5" s="27"/>
@@ -17576,19 +17550,19 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="23" t="s">
+        <v>2058</v>
+      </c>
+      <c r="B6" s="23" t="s">
         <v>2059</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="C6" s="23" t="s">
         <v>2060</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>2061</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>144</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="F6" s="32">
         <v>195.0</v>
@@ -17612,28 +17586,28 @@
       </c>
       <c r="N6" s="25"/>
       <c r="O6" s="27" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="P6" s="27" t="s">
+        <v>2062</v>
+      </c>
+      <c r="Q6" s="27" t="s">
         <v>2063</v>
       </c>
-      <c r="Q6" s="27" t="s">
+      <c r="R6" s="27" t="s">
         <v>2064</v>
       </c>
-      <c r="R6" s="27" t="s">
+      <c r="S6" s="27" t="s">
+        <v>2040</v>
+      </c>
+      <c r="T6" s="27" t="s">
         <v>2065</v>
-      </c>
-      <c r="S6" s="27" t="s">
-        <v>2041</v>
-      </c>
-      <c r="T6" s="27" t="s">
-        <v>2066</v>
       </c>
       <c r="U6" s="27" t="s">
         <v>885</v>
       </c>
       <c r="V6" s="27" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
       <c r="W6" s="27"/>
       <c r="X6" s="27"/>
@@ -17650,19 +17624,19 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="23" t="s">
+        <v>2067</v>
+      </c>
+      <c r="B7" s="23" t="s">
         <v>2068</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="C7" s="23" t="s">
         <v>2069</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>2070</v>
       </c>
       <c r="D7" s="23" t="s">
         <v>144</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="F7" s="32">
         <v>25.0</v>
@@ -17689,10 +17663,10 @@
         <v>232</v>
       </c>
       <c r="P7" s="27" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="Q7" s="27" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="R7" s="27" t="s">
         <v>144</v>
@@ -17701,7 +17675,7 @@
         <v>206</v>
       </c>
       <c r="T7" s="27" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="U7" s="27"/>
       <c r="V7" s="27"/>
@@ -17720,19 +17694,19 @@
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="23" t="s">
+        <v>2073</v>
+      </c>
+      <c r="B8" s="23" t="s">
         <v>2074</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="C8" s="23" t="s">
         <v>2075</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>2076</v>
       </c>
       <c r="D8" s="23" t="s">
         <v>144</v>
       </c>
       <c r="E8" s="27" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="F8" s="32">
         <v>25.0</v>
@@ -17759,10 +17733,10 @@
         <v>232</v>
       </c>
       <c r="P8" s="27" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="Q8" s="27" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="R8" s="27" t="s">
         <v>144</v>
@@ -17771,7 +17745,7 @@
         <v>206</v>
       </c>
       <c r="T8" s="27" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="U8" s="27"/>
       <c r="V8" s="27"/>
@@ -17790,19 +17764,19 @@
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="23" t="s">
+        <v>2078</v>
+      </c>
+      <c r="B9" s="23" t="s">
         <v>2079</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="C9" s="23" t="s">
         <v>2080</v>
-      </c>
-      <c r="C9" s="23" t="s">
-        <v>2081</v>
       </c>
       <c r="D9" s="23" t="s">
         <v>144</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="F9" s="32">
         <v>35.0</v>
@@ -17828,16 +17802,16 @@
         <v>1.0</v>
       </c>
       <c r="O9" s="27" t="s">
+        <v>2082</v>
+      </c>
+      <c r="P9" s="27" t="s">
         <v>2083</v>
-      </c>
-      <c r="P9" s="27" t="s">
-        <v>2084</v>
       </c>
       <c r="Q9" s="27" t="s">
         <v>206</v>
       </c>
       <c r="R9" s="27" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="S9" s="23"/>
       <c r="T9" s="23"/>
@@ -17858,19 +17832,19 @@
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="23" t="s">
+        <v>2085</v>
+      </c>
+      <c r="B10" s="23" t="s">
         <v>2086</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="C10" s="23" t="s">
         <v>2087</v>
-      </c>
-      <c r="C10" s="23" t="s">
-        <v>2088</v>
       </c>
       <c r="D10" s="23" t="s">
         <v>144</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
       <c r="F10" s="32">
         <v>50.0</v>
@@ -17896,16 +17870,16 @@
         <v>2.0</v>
       </c>
       <c r="O10" s="27" t="s">
+        <v>2082</v>
+      </c>
+      <c r="P10" s="27" t="s">
         <v>2083</v>
-      </c>
-      <c r="P10" s="27" t="s">
-        <v>2084</v>
       </c>
       <c r="Q10" s="27" t="s">
         <v>206</v>
       </c>
       <c r="R10" s="27" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="S10" s="23"/>
       <c r="T10" s="23"/>
@@ -17926,19 +17900,19 @@
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="23" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B11" s="23" t="s">
         <v>2090</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="C11" s="27" t="s">
         <v>2091</v>
-      </c>
-      <c r="C11" s="27" t="s">
-        <v>2092</v>
       </c>
       <c r="D11" s="23" t="s">
         <v>144</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>2093</v>
+        <v>2092</v>
       </c>
       <c r="F11" s="32">
         <v>50.0</v>
@@ -17964,16 +17938,16 @@
         <v>3.0</v>
       </c>
       <c r="O11" s="27" t="s">
+        <v>2082</v>
+      </c>
+      <c r="P11" s="27" t="s">
         <v>2083</v>
-      </c>
-      <c r="P11" s="27" t="s">
-        <v>2084</v>
       </c>
       <c r="Q11" s="27" t="s">
         <v>206</v>
       </c>
       <c r="R11" s="27" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="S11" s="23"/>
       <c r="T11" s="23"/>
@@ -17994,19 +17968,19 @@
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="23" t="s">
+        <v>2093</v>
+      </c>
+      <c r="B12" s="23" t="s">
         <v>2094</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="C12" s="23" t="s">
         <v>2095</v>
-      </c>
-      <c r="C12" s="23" t="s">
-        <v>2096</v>
       </c>
       <c r="D12" s="23" t="s">
         <v>144</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>2097</v>
+        <v>2096</v>
       </c>
       <c r="F12" s="32">
         <v>65.0</v>
@@ -18032,16 +18006,16 @@
         <v>5.0</v>
       </c>
       <c r="O12" s="27" t="s">
+        <v>2082</v>
+      </c>
+      <c r="P12" s="27" t="s">
         <v>2083</v>
-      </c>
-      <c r="P12" s="27" t="s">
-        <v>2084</v>
       </c>
       <c r="Q12" s="27" t="s">
         <v>206</v>
       </c>
       <c r="R12" s="27" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="S12" s="23"/>
       <c r="T12" s="23"/>
@@ -18062,19 +18036,19 @@
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="23" t="s">
+        <v>2097</v>
+      </c>
+      <c r="B13" s="23" t="s">
         <v>2098</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="C13" s="23" t="s">
         <v>2099</v>
-      </c>
-      <c r="C13" s="23" t="s">
-        <v>2100</v>
       </c>
       <c r="D13" s="23" t="s">
         <v>144</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="F13" s="32">
         <v>295.0</v>
@@ -18098,19 +18072,19 @@
       </c>
       <c r="N13" s="25"/>
       <c r="O13" s="27" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="P13" s="27" t="s">
+        <v>2101</v>
+      </c>
+      <c r="Q13" s="27" t="s">
         <v>2102</v>
-      </c>
-      <c r="Q13" s="27" t="s">
-        <v>2103</v>
       </c>
       <c r="R13" s="27" t="s">
         <v>162</v>
       </c>
       <c r="S13" s="27" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="T13" s="27" t="s">
         <v>892</v>
@@ -18119,7 +18093,7 @@
         <v>885</v>
       </c>
       <c r="V13" s="27" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="W13" s="27"/>
       <c r="X13" s="27"/>
@@ -18136,19 +18110,19 @@
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="23" t="s">
+        <v>2105</v>
+      </c>
+      <c r="B14" s="23" t="s">
         <v>2106</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="C14" s="23" t="s">
         <v>2107</v>
-      </c>
-      <c r="C14" s="23" t="s">
-        <v>2108</v>
       </c>
       <c r="D14" s="23" t="s">
         <v>144</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="F14" s="32">
         <v>245.0</v>
@@ -18172,19 +18146,19 @@
       </c>
       <c r="N14" s="25"/>
       <c r="O14" s="27" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="P14" s="27" t="s">
+        <v>2101</v>
+      </c>
+      <c r="Q14" s="27" t="s">
         <v>2102</v>
       </c>
-      <c r="Q14" s="27" t="s">
+      <c r="R14" s="27" t="s">
+        <v>2109</v>
+      </c>
+      <c r="S14" s="27" t="s">
         <v>2103</v>
-      </c>
-      <c r="R14" s="27" t="s">
-        <v>2110</v>
-      </c>
-      <c r="S14" s="27" t="s">
-        <v>2104</v>
       </c>
       <c r="T14" s="27" t="s">
         <v>892</v>
@@ -18193,7 +18167,7 @@
         <v>885</v>
       </c>
       <c r="V14" s="27" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="W14" s="27"/>
       <c r="X14" s="27"/>
@@ -18210,19 +18184,19 @@
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="23" t="s">
+        <v>2110</v>
+      </c>
+      <c r="B15" s="23" t="s">
         <v>2111</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="C15" s="23" t="s">
         <v>2112</v>
-      </c>
-      <c r="C15" s="23" t="s">
-        <v>2113</v>
       </c>
       <c r="D15" s="23" t="s">
         <v>144</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
       <c r="F15" s="32">
         <v>220.0</v>
@@ -18246,19 +18220,19 @@
       </c>
       <c r="N15" s="25"/>
       <c r="O15" s="27" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="P15" s="27" t="s">
+        <v>2101</v>
+      </c>
+      <c r="Q15" s="27" t="s">
         <v>2102</v>
       </c>
-      <c r="Q15" s="27" t="s">
+      <c r="R15" s="27" t="s">
+        <v>2114</v>
+      </c>
+      <c r="S15" s="27" t="s">
         <v>2103</v>
-      </c>
-      <c r="R15" s="27" t="s">
-        <v>2115</v>
-      </c>
-      <c r="S15" s="27" t="s">
-        <v>2104</v>
       </c>
       <c r="T15" s="27" t="s">
         <v>892</v>
@@ -18267,7 +18241,7 @@
         <v>885</v>
       </c>
       <c r="V15" s="27" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="W15" s="27"/>
       <c r="X15" s="27"/>
@@ -18284,19 +18258,19 @@
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="23" t="s">
+        <v>2115</v>
+      </c>
+      <c r="B16" s="23" t="s">
         <v>2116</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="C16" s="23" t="s">
         <v>2117</v>
-      </c>
-      <c r="C16" s="23" t="s">
-        <v>2118</v>
       </c>
       <c r="D16" s="23" t="s">
         <v>144</v>
       </c>
       <c r="E16" s="27" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
       <c r="F16" s="32">
         <v>50.0</v>
@@ -18320,19 +18294,19 @@
       </c>
       <c r="N16" s="25"/>
       <c r="O16" s="27" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="P16" s="27" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="Q16" s="27" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="R16" s="27" t="s">
         <v>144</v>
       </c>
       <c r="S16" s="27" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="T16" s="27" t="s">
         <v>892</v>
@@ -18354,19 +18328,19 @@
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="23" t="s">
+        <v>2120</v>
+      </c>
+      <c r="B17" s="23" t="s">
         <v>2121</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="C17" s="27" t="s">
         <v>2122</v>
-      </c>
-      <c r="C17" s="27" t="s">
-        <v>2123</v>
       </c>
       <c r="D17" s="23" t="s">
         <v>144</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>2124</v>
+        <v>2123</v>
       </c>
       <c r="F17" s="32">
         <v>275.0</v>
@@ -18390,28 +18364,28 @@
       </c>
       <c r="N17" s="25"/>
       <c r="O17" s="27" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="P17" s="27" t="s">
+        <v>2124</v>
+      </c>
+      <c r="Q17" s="27" t="s">
+        <v>1988</v>
+      </c>
+      <c r="R17" s="27" t="s">
         <v>2125</v>
       </c>
-      <c r="Q17" s="27" t="s">
-        <v>1989</v>
-      </c>
-      <c r="R17" s="27" t="s">
+      <c r="S17" s="27" t="s">
+        <v>2102</v>
+      </c>
+      <c r="T17" s="27" t="s">
         <v>2126</v>
-      </c>
-      <c r="S17" s="27" t="s">
-        <v>2103</v>
-      </c>
-      <c r="T17" s="27" t="s">
-        <v>2127</v>
       </c>
       <c r="U17" s="27" t="s">
         <v>543</v>
       </c>
       <c r="V17" s="27" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="W17" s="27"/>
       <c r="X17" s="27"/>
@@ -18428,19 +18402,19 @@
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="23" t="s">
+        <v>2128</v>
+      </c>
+      <c r="B18" s="23" t="s">
         <v>2129</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="C18" s="23" t="s">
         <v>2130</v>
-      </c>
-      <c r="C18" s="23" t="s">
-        <v>2131</v>
       </c>
       <c r="D18" s="23" t="s">
         <v>144</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="F18" s="32">
         <v>150.0</v>
@@ -18464,19 +18438,19 @@
       </c>
       <c r="N18" s="25"/>
       <c r="O18" s="27" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="P18" s="27" t="s">
+        <v>2132</v>
+      </c>
+      <c r="Q18" s="27" t="s">
+        <v>1988</v>
+      </c>
+      <c r="R18" s="27" t="s">
         <v>2133</v>
       </c>
-      <c r="Q18" s="27" t="s">
-        <v>1989</v>
-      </c>
-      <c r="R18" s="27" t="s">
-        <v>2134</v>
-      </c>
       <c r="S18" s="27" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="T18" s="27" t="s">
         <v>144</v>
@@ -18485,10 +18459,10 @@
         <v>308</v>
       </c>
       <c r="V18" s="27" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="W18" s="27" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="X18" s="27" t="s">
         <v>892</v>
@@ -18506,19 +18480,19 @@
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="23" t="s">
+        <v>2135</v>
+      </c>
+      <c r="B19" s="23" t="s">
         <v>2136</v>
       </c>
-      <c r="B19" s="23" t="s">
+      <c r="C19" s="23" t="s">
         <v>2137</v>
-      </c>
-      <c r="C19" s="23" t="s">
-        <v>2138</v>
       </c>
       <c r="D19" s="23" t="s">
         <v>144</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="F19" s="32">
         <v>1995.0</v>
@@ -18542,40 +18516,40 @@
       </c>
       <c r="N19" s="25"/>
       <c r="O19" s="27" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="P19" s="27" t="s">
+        <v>2139</v>
+      </c>
+      <c r="Q19" s="27" t="s">
         <v>2140</v>
       </c>
-      <c r="Q19" s="27" t="s">
+      <c r="R19" s="27" t="s">
         <v>2141</v>
-      </c>
-      <c r="R19" s="27" t="s">
-        <v>2142</v>
       </c>
       <c r="S19" s="27" t="s">
         <v>891</v>
       </c>
       <c r="T19" s="27" t="s">
+        <v>2142</v>
+      </c>
+      <c r="U19" s="27" t="s">
         <v>2143</v>
       </c>
-      <c r="U19" s="27" t="s">
+      <c r="V19" s="27" t="s">
         <v>2144</v>
-      </c>
-      <c r="V19" s="27" t="s">
-        <v>2145</v>
       </c>
       <c r="W19" s="27" t="s">
         <v>781</v>
       </c>
       <c r="X19" s="27" t="s">
+        <v>2145</v>
+      </c>
+      <c r="Y19" s="27" t="s">
         <v>2146</v>
       </c>
-      <c r="Y19" s="27" t="s">
+      <c r="Z19" s="27" t="s">
         <v>2147</v>
-      </c>
-      <c r="Z19" s="27" t="s">
-        <v>2148</v>
       </c>
       <c r="AA19" s="27"/>
       <c r="AB19" s="27"/>
@@ -18588,19 +18562,19 @@
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="23" t="s">
+        <v>2148</v>
+      </c>
+      <c r="B20" s="23" t="s">
         <v>2149</v>
       </c>
-      <c r="B20" s="23" t="s">
+      <c r="C20" s="23" t="s">
         <v>2150</v>
-      </c>
-      <c r="C20" s="23" t="s">
-        <v>2151</v>
       </c>
       <c r="D20" s="23" t="s">
         <v>144</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="F20" s="32">
         <v>1245.0</v>
@@ -18624,40 +18598,40 @@
       </c>
       <c r="N20" s="25"/>
       <c r="O20" s="27" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="P20" s="27" t="s">
+        <v>2139</v>
+      </c>
+      <c r="Q20" s="27" t="s">
         <v>2140</v>
       </c>
-      <c r="Q20" s="27" t="s">
-        <v>2141</v>
-      </c>
       <c r="R20" s="27" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="S20" s="27" t="s">
         <v>891</v>
       </c>
       <c r="T20" s="27" t="s">
+        <v>2142</v>
+      </c>
+      <c r="U20" s="27" t="s">
         <v>2143</v>
       </c>
-      <c r="U20" s="27" t="s">
-        <v>2144</v>
-      </c>
       <c r="V20" s="27" t="s">
-        <v>2154</v>
+        <v>2153</v>
       </c>
       <c r="W20" s="27" t="s">
         <v>781</v>
       </c>
       <c r="X20" s="27" t="s">
+        <v>2145</v>
+      </c>
+      <c r="Y20" s="27" t="s">
         <v>2146</v>
       </c>
-      <c r="Y20" s="27" t="s">
+      <c r="Z20" s="27" t="s">
         <v>2147</v>
-      </c>
-      <c r="Z20" s="27" t="s">
-        <v>2148</v>
       </c>
       <c r="AA20" s="27"/>
       <c r="AB20" s="27"/>
@@ -18670,19 +18644,19 @@
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="23" t="s">
+        <v>2154</v>
+      </c>
+      <c r="B21" s="23" t="s">
         <v>2155</v>
       </c>
-      <c r="B21" s="23" t="s">
+      <c r="C21" s="23" t="s">
         <v>2156</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>2157</v>
       </c>
       <c r="D21" s="23" t="s">
         <v>144</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="F21" s="32">
         <v>950.0</v>
@@ -18706,52 +18680,52 @@
       </c>
       <c r="N21" s="25"/>
       <c r="O21" s="27" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="P21" s="27" t="s">
+        <v>2158</v>
+      </c>
+      <c r="Q21" s="27" t="s">
+        <v>2140</v>
+      </c>
+      <c r="R21" s="27" t="s">
+        <v>2152</v>
+      </c>
+      <c r="S21" s="27" t="s">
         <v>2159</v>
       </c>
-      <c r="Q21" s="27" t="s">
-        <v>2141</v>
-      </c>
-      <c r="R21" s="27" t="s">
-        <v>2153</v>
-      </c>
-      <c r="S21" s="27" t="s">
+      <c r="T21" s="27" t="s">
         <v>2160</v>
-      </c>
-      <c r="T21" s="27" t="s">
-        <v>2161</v>
       </c>
       <c r="U21" s="27" t="s">
         <v>294</v>
       </c>
       <c r="V21" s="27" t="s">
+        <v>2161</v>
+      </c>
+      <c r="W21" s="27" t="s">
         <v>2162</v>
       </c>
-      <c r="W21" s="27" t="s">
+      <c r="X21" s="27" t="s">
         <v>2163</v>
       </c>
-      <c r="X21" s="27" t="s">
+      <c r="Y21" s="27" t="s">
         <v>2164</v>
       </c>
-      <c r="Y21" s="27" t="s">
+      <c r="Z21" s="27" t="s">
         <v>2165</v>
-      </c>
-      <c r="Z21" s="27" t="s">
-        <v>2166</v>
       </c>
       <c r="AA21" s="27" t="s">
         <v>781</v>
       </c>
       <c r="AB21" s="27" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
       <c r="AC21" s="27" t="s">
         <v>781</v>
       </c>
       <c r="AD21" s="27" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
       <c r="AE21" s="27"/>
       <c r="AF21" s="27"/>
@@ -18760,19 +18734,19 @@
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c r="A22" s="23" t="s">
+        <v>2167</v>
+      </c>
+      <c r="B22" s="23" t="s">
         <v>2168</v>
       </c>
-      <c r="B22" s="23" t="s">
+      <c r="C22" s="27" t="s">
         <v>2169</v>
-      </c>
-      <c r="C22" s="27" t="s">
-        <v>2170</v>
       </c>
       <c r="D22" s="23" t="s">
         <v>84</v>
       </c>
       <c r="E22" s="27" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="F22" s="32">
         <v>1495.0</v>
@@ -18796,13 +18770,13 @@
       </c>
       <c r="N22" s="25"/>
       <c r="O22" s="27" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="P22" s="27" t="s">
-        <v>2172</v>
+        <v>2171</v>
       </c>
       <c r="Q22" s="27" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="R22" s="27" t="s">
         <v>84</v>
@@ -18811,25 +18785,25 @@
         <v>885</v>
       </c>
       <c r="T22" s="27" t="s">
+        <v>2172</v>
+      </c>
+      <c r="U22" s="27" t="s">
+        <v>1799</v>
+      </c>
+      <c r="V22" s="27" t="s">
         <v>2173</v>
       </c>
-      <c r="U22" s="27" t="s">
-        <v>1800</v>
-      </c>
-      <c r="V22" s="27" t="s">
+      <c r="W22" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="X22" s="27" t="s">
         <v>2174</v>
-      </c>
-      <c r="W22" s="27" t="s">
-        <v>1651</v>
-      </c>
-      <c r="X22" s="27" t="s">
-        <v>2175</v>
       </c>
       <c r="Y22" s="27" t="s">
         <v>1506</v>
       </c>
       <c r="Z22" s="27" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="AA22" s="27"/>
       <c r="AB22" s="27"/>
@@ -18842,19 +18816,19 @@
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="23" t="s">
+        <v>2176</v>
+      </c>
+      <c r="B23" s="23" t="s">
         <v>2177</v>
       </c>
-      <c r="B23" s="23" t="s">
+      <c r="C23" s="27" t="s">
         <v>2178</v>
-      </c>
-      <c r="C23" s="27" t="s">
-        <v>2179</v>
       </c>
       <c r="D23" s="23" t="s">
         <v>84</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="F23" s="32">
         <v>1595.0</v>
@@ -18878,28 +18852,28 @@
       </c>
       <c r="N23" s="25"/>
       <c r="O23" s="27" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="P23" s="27" t="s">
+        <v>2180</v>
+      </c>
+      <c r="Q23" s="27" t="s">
         <v>2181</v>
       </c>
-      <c r="Q23" s="27" t="s">
+      <c r="R23" s="27" t="s">
         <v>2182</v>
-      </c>
-      <c r="R23" s="27" t="s">
-        <v>2183</v>
       </c>
       <c r="S23" s="27" t="s">
         <v>885</v>
       </c>
       <c r="T23" s="27" t="s">
+        <v>2183</v>
+      </c>
+      <c r="U23" s="27" t="s">
+        <v>2146</v>
+      </c>
+      <c r="V23" s="27" t="s">
         <v>2184</v>
-      </c>
-      <c r="U23" s="27" t="s">
-        <v>2147</v>
-      </c>
-      <c r="V23" s="27" t="s">
-        <v>2185</v>
       </c>
       <c r="W23" s="27"/>
       <c r="X23" s="27"/>
@@ -18916,19 +18890,19 @@
     </row>
     <row r="24" ht="14.25" customHeight="1">
       <c r="A24" s="23" t="s">
+        <v>2185</v>
+      </c>
+      <c r="B24" s="23" t="s">
         <v>2186</v>
       </c>
-      <c r="B24" s="23" t="s">
+      <c r="C24" s="23" t="s">
         <v>2187</v>
-      </c>
-      <c r="C24" s="23" t="s">
-        <v>2188</v>
       </c>
       <c r="D24" s="23" t="s">
         <v>84</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="F24" s="32">
         <v>1995.0</v>
@@ -18952,16 +18926,16 @@
       </c>
       <c r="N24" s="25"/>
       <c r="O24" s="27" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="P24" s="27" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="Q24" s="27" t="s">
         <v>885</v>
       </c>
       <c r="R24" s="27" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="S24" s="23"/>
       <c r="T24" s="23"/>
@@ -18982,19 +18956,19 @@
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="23" t="s">
+        <v>2191</v>
+      </c>
+      <c r="B25" s="23" t="s">
         <v>2192</v>
       </c>
-      <c r="B25" s="23" t="s">
+      <c r="C25" s="23" t="s">
         <v>2193</v>
-      </c>
-      <c r="C25" s="23" t="s">
-        <v>2194</v>
       </c>
       <c r="D25" s="23" t="s">
         <v>84</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>2195</v>
+        <v>2194</v>
       </c>
       <c r="F25" s="32">
         <v>350.0</v>
@@ -19020,34 +18994,34 @@
         <v>5.18</v>
       </c>
       <c r="O25" s="27" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="P25" s="27" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
       <c r="Q25" s="27" t="s">
         <v>206</v>
       </c>
       <c r="R25" s="27" t="s">
+        <v>2196</v>
+      </c>
+      <c r="S25" s="27" t="s">
         <v>2197</v>
       </c>
-      <c r="S25" s="27" t="s">
+      <c r="T25" s="27" t="s">
         <v>2198</v>
       </c>
-      <c r="T25" s="27" t="s">
+      <c r="U25" s="27" t="s">
         <v>2199</v>
       </c>
-      <c r="U25" s="27" t="s">
+      <c r="V25" s="27" t="s">
         <v>2200</v>
-      </c>
-      <c r="V25" s="27" t="s">
-        <v>2201</v>
       </c>
       <c r="W25" s="27" t="s">
         <v>222</v>
       </c>
       <c r="X25" s="27" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="Y25" s="27"/>
       <c r="Z25" s="27"/>
@@ -19062,19 +19036,19 @@
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="23" t="s">
+        <v>2202</v>
+      </c>
+      <c r="B26" s="23" t="s">
         <v>2203</v>
       </c>
-      <c r="B26" s="23" t="s">
+      <c r="C26" s="23" t="s">
         <v>2204</v>
-      </c>
-      <c r="C26" s="23" t="s">
-        <v>2205</v>
       </c>
       <c r="D26" s="23" t="s">
         <v>84</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>2206</v>
+        <v>2205</v>
       </c>
       <c r="F26" s="32">
         <v>225.0</v>
@@ -19100,34 +19074,34 @@
         <v>7.62</v>
       </c>
       <c r="O26" s="27" t="s">
+        <v>2082</v>
+      </c>
+      <c r="P26" s="27" t="s">
         <v>2083</v>
-      </c>
-      <c r="P26" s="27" t="s">
-        <v>2084</v>
       </c>
       <c r="Q26" s="27" t="s">
         <v>206</v>
       </c>
       <c r="R26" s="27" t="s">
+        <v>2196</v>
+      </c>
+      <c r="S26" s="27" t="s">
         <v>2197</v>
       </c>
-      <c r="S26" s="27" t="s">
+      <c r="T26" s="27" t="s">
         <v>2198</v>
       </c>
-      <c r="T26" s="27" t="s">
+      <c r="U26" s="27" t="s">
         <v>2199</v>
       </c>
-      <c r="U26" s="27" t="s">
+      <c r="V26" s="27" t="s">
         <v>2200</v>
-      </c>
-      <c r="V26" s="27" t="s">
-        <v>2201</v>
       </c>
       <c r="W26" s="27" t="s">
         <v>222</v>
       </c>
       <c r="X26" s="27" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="Y26" s="27"/>
       <c r="Z26" s="27"/>
@@ -19142,19 +19116,19 @@
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="23" t="s">
+        <v>2206</v>
+      </c>
+      <c r="B27" s="23" t="s">
         <v>2207</v>
       </c>
-      <c r="B27" s="23" t="s">
+      <c r="C27" s="23" t="s">
         <v>2208</v>
-      </c>
-      <c r="C27" s="23" t="s">
-        <v>2209</v>
       </c>
       <c r="D27" s="23" t="s">
         <v>84</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>2210</v>
+        <v>2209</v>
       </c>
       <c r="F27" s="32">
         <v>265.0</v>
@@ -19180,34 +19154,34 @@
         <v>5.18</v>
       </c>
       <c r="O27" s="27" t="s">
+        <v>2082</v>
+      </c>
+      <c r="P27" s="27" t="s">
         <v>2083</v>
-      </c>
-      <c r="P27" s="27" t="s">
-        <v>2084</v>
       </c>
       <c r="Q27" s="27" t="s">
         <v>206</v>
       </c>
       <c r="R27" s="27" t="s">
+        <v>2196</v>
+      </c>
+      <c r="S27" s="27" t="s">
         <v>2197</v>
       </c>
-      <c r="S27" s="27" t="s">
+      <c r="T27" s="27" t="s">
         <v>2198</v>
       </c>
-      <c r="T27" s="27" t="s">
+      <c r="U27" s="27" t="s">
         <v>2199</v>
       </c>
-      <c r="U27" s="27" t="s">
+      <c r="V27" s="27" t="s">
         <v>2200</v>
-      </c>
-      <c r="V27" s="27" t="s">
-        <v>2201</v>
       </c>
       <c r="W27" s="27" t="s">
         <v>222</v>
       </c>
       <c r="X27" s="27" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="Y27" s="27"/>
       <c r="Z27" s="27"/>
@@ -19222,19 +19196,19 @@
     </row>
     <row r="28" ht="14.25" customHeight="1">
       <c r="A28" s="23" t="s">
+        <v>2210</v>
+      </c>
+      <c r="B28" s="23" t="s">
         <v>2211</v>
       </c>
-      <c r="B28" s="23" t="s">
+      <c r="C28" s="23" t="s">
         <v>2212</v>
-      </c>
-      <c r="C28" s="23" t="s">
-        <v>2213</v>
       </c>
       <c r="D28" s="23" t="s">
         <v>84</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>2214</v>
+        <v>2213</v>
       </c>
       <c r="F28" s="32">
         <v>175.0</v>
@@ -19260,34 +19234,34 @@
         <v>2.13</v>
       </c>
       <c r="O28" s="27" t="s">
+        <v>2082</v>
+      </c>
+      <c r="P28" s="27" t="s">
         <v>2083</v>
-      </c>
-      <c r="P28" s="27" t="s">
-        <v>2084</v>
       </c>
       <c r="Q28" s="27" t="s">
         <v>206</v>
       </c>
       <c r="R28" s="27" t="s">
+        <v>2196</v>
+      </c>
+      <c r="S28" s="27" t="s">
         <v>2197</v>
       </c>
-      <c r="S28" s="27" t="s">
+      <c r="T28" s="27" t="s">
         <v>2198</v>
       </c>
-      <c r="T28" s="27" t="s">
+      <c r="U28" s="27" t="s">
         <v>2199</v>
       </c>
-      <c r="U28" s="27" t="s">
+      <c r="V28" s="27" t="s">
         <v>2200</v>
-      </c>
-      <c r="V28" s="27" t="s">
-        <v>2201</v>
       </c>
       <c r="W28" s="27" t="s">
         <v>222</v>
       </c>
       <c r="X28" s="27" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="Y28" s="27"/>
       <c r="Z28" s="27"/>
@@ -19302,19 +19276,19 @@
     </row>
     <row r="29" ht="14.25" customHeight="1">
       <c r="A29" s="23" t="s">
+        <v>2214</v>
+      </c>
+      <c r="B29" s="23" t="s">
         <v>2215</v>
       </c>
-      <c r="B29" s="23" t="s">
+      <c r="C29" s="23" t="s">
         <v>2216</v>
-      </c>
-      <c r="C29" s="23" t="s">
-        <v>2217</v>
       </c>
       <c r="D29" s="23" t="s">
         <v>84</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>2218</v>
+        <v>2217</v>
       </c>
       <c r="F29" s="32">
         <v>150.0</v>
@@ -19340,34 +19314,34 @@
         <v>0.91</v>
       </c>
       <c r="O29" s="27" t="s">
+        <v>2082</v>
+      </c>
+      <c r="P29" s="27" t="s">
         <v>2083</v>
-      </c>
-      <c r="P29" s="27" t="s">
-        <v>2084</v>
       </c>
       <c r="Q29" s="27" t="s">
         <v>206</v>
       </c>
       <c r="R29" s="27" t="s">
+        <v>2196</v>
+      </c>
+      <c r="S29" s="27" t="s">
         <v>2197</v>
       </c>
-      <c r="S29" s="27" t="s">
+      <c r="T29" s="27" t="s">
         <v>2198</v>
       </c>
-      <c r="T29" s="27" t="s">
+      <c r="U29" s="27" t="s">
         <v>2199</v>
       </c>
-      <c r="U29" s="27" t="s">
+      <c r="V29" s="27" t="s">
         <v>2200</v>
-      </c>
-      <c r="V29" s="27" t="s">
-        <v>2201</v>
       </c>
       <c r="W29" s="27" t="s">
         <v>222</v>
       </c>
       <c r="X29" s="27" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="Y29" s="27"/>
       <c r="Z29" s="27"/>
@@ -19382,19 +19356,19 @@
     </row>
     <row r="30" ht="14.25" customHeight="1">
       <c r="A30" s="23" t="s">
+        <v>2218</v>
+      </c>
+      <c r="B30" s="23" t="s">
         <v>2219</v>
       </c>
-      <c r="B30" s="23" t="s">
+      <c r="C30" s="23" t="s">
         <v>2220</v>
-      </c>
-      <c r="C30" s="23" t="s">
-        <v>2221</v>
       </c>
       <c r="D30" s="23" t="s">
         <v>84</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>2222</v>
+        <v>2221</v>
       </c>
       <c r="F30" s="32">
         <v>150.0</v>
@@ -19420,34 +19394,34 @@
         <v>0.46</v>
       </c>
       <c r="O30" s="27" t="s">
+        <v>2082</v>
+      </c>
+      <c r="P30" s="27" t="s">
         <v>2083</v>
-      </c>
-      <c r="P30" s="27" t="s">
-        <v>2084</v>
       </c>
       <c r="Q30" s="27" t="s">
         <v>206</v>
       </c>
       <c r="R30" s="27" t="s">
+        <v>2196</v>
+      </c>
+      <c r="S30" s="27" t="s">
         <v>2197</v>
       </c>
-      <c r="S30" s="27" t="s">
+      <c r="T30" s="27" t="s">
         <v>2198</v>
       </c>
-      <c r="T30" s="27" t="s">
+      <c r="U30" s="27" t="s">
         <v>2199</v>
       </c>
-      <c r="U30" s="27" t="s">
+      <c r="V30" s="27" t="s">
         <v>2200</v>
-      </c>
-      <c r="V30" s="27" t="s">
-        <v>2201</v>
       </c>
       <c r="W30" s="27" t="s">
         <v>222</v>
       </c>
       <c r="X30" s="27" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="Y30" s="27"/>
       <c r="Z30" s="27"/>
@@ -19462,19 +19436,19 @@
     </row>
     <row r="31" ht="14.25" customHeight="1">
       <c r="A31" s="23" t="s">
+        <v>2222</v>
+      </c>
+      <c r="B31" s="23" t="s">
         <v>2223</v>
       </c>
-      <c r="B31" s="23" t="s">
+      <c r="C31" s="23" t="s">
         <v>2224</v>
-      </c>
-      <c r="C31" s="23" t="s">
-        <v>2225</v>
       </c>
       <c r="D31" s="23" t="s">
         <v>84</v>
       </c>
       <c r="E31" s="23" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
       <c r="F31" s="32">
         <v>95.0</v>
@@ -19501,19 +19475,19 @@
         <v>232</v>
       </c>
       <c r="P31" s="27" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
       <c r="Q31" s="27" t="s">
         <v>222</v>
       </c>
       <c r="R31" s="27" t="s">
+        <v>2227</v>
+      </c>
+      <c r="S31" s="27" t="s">
+        <v>2197</v>
+      </c>
+      <c r="T31" s="27" t="s">
         <v>2228</v>
-      </c>
-      <c r="S31" s="27" t="s">
-        <v>2198</v>
-      </c>
-      <c r="T31" s="27" t="s">
-        <v>2229</v>
       </c>
       <c r="U31" s="27"/>
       <c r="V31" s="27"/>
@@ -19532,19 +19506,19 @@
     </row>
     <row r="32" ht="14.25" customHeight="1">
       <c r="A32" s="23" t="s">
+        <v>2229</v>
+      </c>
+      <c r="B32" s="23" t="s">
         <v>2230</v>
       </c>
-      <c r="B32" s="23" t="s">
+      <c r="C32" s="23" t="s">
         <v>2231</v>
-      </c>
-      <c r="C32" s="23" t="s">
-        <v>2232</v>
       </c>
       <c r="D32" s="23" t="s">
         <v>84</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>2233</v>
+        <v>2232</v>
       </c>
       <c r="F32" s="32">
         <v>95.0</v>
@@ -19571,19 +19545,19 @@
         <v>232</v>
       </c>
       <c r="P32" s="27" t="s">
-        <v>2234</v>
+        <v>2233</v>
       </c>
       <c r="Q32" s="27" t="s">
         <v>222</v>
       </c>
       <c r="R32" s="27" t="s">
+        <v>2227</v>
+      </c>
+      <c r="S32" s="27" t="s">
+        <v>2197</v>
+      </c>
+      <c r="T32" s="27" t="s">
         <v>2228</v>
-      </c>
-      <c r="S32" s="27" t="s">
-        <v>2198</v>
-      </c>
-      <c r="T32" s="27" t="s">
-        <v>2229</v>
       </c>
       <c r="U32" s="27"/>
       <c r="V32" s="27"/>
@@ -19602,19 +19576,19 @@
     </row>
     <row r="33" ht="14.25" customHeight="1">
       <c r="A33" s="23" t="s">
+        <v>2234</v>
+      </c>
+      <c r="B33" s="23" t="s">
         <v>2235</v>
       </c>
-      <c r="B33" s="23" t="s">
+      <c r="C33" s="23" t="s">
         <v>2236</v>
-      </c>
-      <c r="C33" s="23" t="s">
-        <v>2237</v>
       </c>
       <c r="D33" s="23" t="s">
         <v>84</v>
       </c>
       <c r="E33" s="23" t="s">
-        <v>2238</v>
+        <v>2237</v>
       </c>
       <c r="F33" s="32">
         <v>650.0</v>
@@ -19640,40 +19614,40 @@
         <v>6.4</v>
       </c>
       <c r="O33" s="27" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="P33" s="27" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
       <c r="Q33" s="27" t="s">
         <v>206</v>
       </c>
       <c r="R33" s="27" t="s">
+        <v>2238</v>
+      </c>
+      <c r="S33" s="27" t="s">
+        <v>2197</v>
+      </c>
+      <c r="T33" s="27" t="s">
         <v>2239</v>
       </c>
-      <c r="S33" s="27" t="s">
-        <v>2198</v>
-      </c>
-      <c r="T33" s="27" t="s">
+      <c r="U33" s="27" t="s">
+        <v>2199</v>
+      </c>
+      <c r="V33" s="27" t="s">
         <v>2240</v>
       </c>
-      <c r="U33" s="27" t="s">
-        <v>2200</v>
-      </c>
-      <c r="V33" s="27" t="s">
+      <c r="W33" s="27" t="s">
+        <v>1797</v>
+      </c>
+      <c r="X33" s="27" t="s">
         <v>2241</v>
-      </c>
-      <c r="W33" s="27" t="s">
-        <v>1798</v>
-      </c>
-      <c r="X33" s="27" t="s">
-        <v>2242</v>
       </c>
       <c r="Y33" s="27" t="s">
         <v>222</v>
       </c>
       <c r="Z33" s="27" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
       <c r="AA33" s="27"/>
       <c r="AB33" s="27"/>
@@ -19686,19 +19660,19 @@
     </row>
     <row r="34" ht="14.25" customHeight="1">
       <c r="A34" s="23" t="s">
+        <v>2243</v>
+      </c>
+      <c r="B34" s="23" t="s">
         <v>2244</v>
       </c>
-      <c r="B34" s="23" t="s">
+      <c r="C34" s="23" t="s">
         <v>2245</v>
-      </c>
-      <c r="C34" s="23" t="s">
-        <v>2246</v>
       </c>
       <c r="D34" s="23" t="s">
         <v>84</v>
       </c>
       <c r="E34" s="23" t="s">
-        <v>2247</v>
+        <v>2246</v>
       </c>
       <c r="F34" s="32">
         <v>595.0</v>
@@ -19724,40 +19698,40 @@
         <v>5.18</v>
       </c>
       <c r="O34" s="27" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="P34" s="27" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
       <c r="Q34" s="27" t="s">
         <v>206</v>
       </c>
       <c r="R34" s="27" t="s">
+        <v>2238</v>
+      </c>
+      <c r="S34" s="27" t="s">
+        <v>2197</v>
+      </c>
+      <c r="T34" s="27" t="s">
         <v>2239</v>
       </c>
-      <c r="S34" s="27" t="s">
-        <v>2198</v>
-      </c>
-      <c r="T34" s="27" t="s">
+      <c r="U34" s="27" t="s">
+        <v>2199</v>
+      </c>
+      <c r="V34" s="27" t="s">
         <v>2240</v>
       </c>
-      <c r="U34" s="27" t="s">
-        <v>2200</v>
-      </c>
-      <c r="V34" s="27" t="s">
+      <c r="W34" s="27" t="s">
+        <v>1797</v>
+      </c>
+      <c r="X34" s="27" t="s">
         <v>2241</v>
-      </c>
-      <c r="W34" s="27" t="s">
-        <v>1798</v>
-      </c>
-      <c r="X34" s="27" t="s">
-        <v>2242</v>
       </c>
       <c r="Y34" s="27" t="s">
         <v>222</v>
       </c>
       <c r="Z34" s="27" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
       <c r="AA34" s="27"/>
       <c r="AB34" s="27"/>
@@ -19770,19 +19744,19 @@
     </row>
     <row r="35" ht="14.25" customHeight="1">
       <c r="A35" s="23" t="s">
+        <v>2247</v>
+      </c>
+      <c r="B35" s="23" t="s">
         <v>2248</v>
       </c>
-      <c r="B35" s="23" t="s">
+      <c r="C35" s="23" t="s">
         <v>2249</v>
-      </c>
-      <c r="C35" s="23" t="s">
-        <v>2250</v>
       </c>
       <c r="D35" s="23" t="s">
         <v>84</v>
       </c>
       <c r="E35" s="23" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
       <c r="F35" s="32">
         <v>295.0</v>
@@ -19808,40 +19782,40 @@
         <v>5.18</v>
       </c>
       <c r="O35" s="27" t="s">
+        <v>2082</v>
+      </c>
+      <c r="P35" s="27" t="s">
         <v>2083</v>
-      </c>
-      <c r="P35" s="27" t="s">
-        <v>2084</v>
       </c>
       <c r="Q35" s="27" t="s">
         <v>206</v>
       </c>
       <c r="R35" s="27" t="s">
+        <v>2238</v>
+      </c>
+      <c r="S35" s="27" t="s">
+        <v>2197</v>
+      </c>
+      <c r="T35" s="27" t="s">
         <v>2239</v>
       </c>
-      <c r="S35" s="27" t="s">
-        <v>2198</v>
-      </c>
-      <c r="T35" s="27" t="s">
+      <c r="U35" s="27" t="s">
+        <v>2199</v>
+      </c>
+      <c r="V35" s="27" t="s">
         <v>2240</v>
       </c>
-      <c r="U35" s="27" t="s">
-        <v>2200</v>
-      </c>
-      <c r="V35" s="27" t="s">
+      <c r="W35" s="27" t="s">
+        <v>1797</v>
+      </c>
+      <c r="X35" s="27" t="s">
         <v>2241</v>
-      </c>
-      <c r="W35" s="27" t="s">
-        <v>1798</v>
-      </c>
-      <c r="X35" s="27" t="s">
-        <v>2242</v>
       </c>
       <c r="Y35" s="27" t="s">
         <v>222</v>
       </c>
       <c r="Z35" s="27" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
       <c r="AA35" s="27"/>
       <c r="AB35" s="27"/>
@@ -19854,19 +19828,19 @@
     </row>
     <row r="36" ht="14.25" customHeight="1">
       <c r="A36" s="23" t="s">
+        <v>2251</v>
+      </c>
+      <c r="B36" s="23" t="s">
         <v>2252</v>
       </c>
-      <c r="B36" s="23" t="s">
+      <c r="C36" s="23" t="s">
         <v>2253</v>
-      </c>
-      <c r="C36" s="23" t="s">
-        <v>2254</v>
       </c>
       <c r="D36" s="23" t="s">
         <v>84</v>
       </c>
       <c r="E36" s="23" t="s">
-        <v>2255</v>
+        <v>2254</v>
       </c>
       <c r="F36" s="32">
         <v>250.0</v>
@@ -19892,40 +19866,40 @@
         <v>0.91</v>
       </c>
       <c r="O36" s="27" t="s">
+        <v>2082</v>
+      </c>
+      <c r="P36" s="27" t="s">
         <v>2083</v>
-      </c>
-      <c r="P36" s="27" t="s">
-        <v>2084</v>
       </c>
       <c r="Q36" s="27" t="s">
         <v>206</v>
       </c>
       <c r="R36" s="27" t="s">
+        <v>2238</v>
+      </c>
+      <c r="S36" s="27" t="s">
+        <v>2197</v>
+      </c>
+      <c r="T36" s="27" t="s">
         <v>2239</v>
       </c>
-      <c r="S36" s="27" t="s">
-        <v>2198</v>
-      </c>
-      <c r="T36" s="27" t="s">
+      <c r="U36" s="27" t="s">
+        <v>2199</v>
+      </c>
+      <c r="V36" s="27" t="s">
         <v>2240</v>
       </c>
-      <c r="U36" s="27" t="s">
-        <v>2200</v>
-      </c>
-      <c r="V36" s="27" t="s">
+      <c r="W36" s="27" t="s">
+        <v>1797</v>
+      </c>
+      <c r="X36" s="27" t="s">
         <v>2241</v>
-      </c>
-      <c r="W36" s="27" t="s">
-        <v>1798</v>
-      </c>
-      <c r="X36" s="27" t="s">
-        <v>2242</v>
       </c>
       <c r="Y36" s="27" t="s">
         <v>222</v>
       </c>
       <c r="Z36" s="27" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
       <c r="AA36" s="27"/>
       <c r="AB36" s="27"/>
@@ -19938,19 +19912,19 @@
     </row>
     <row r="37" ht="14.25" customHeight="1">
       <c r="A37" s="23" t="s">
+        <v>2255</v>
+      </c>
+      <c r="B37" s="23" t="s">
         <v>2256</v>
       </c>
-      <c r="B37" s="23" t="s">
+      <c r="C37" s="23" t="s">
         <v>2257</v>
-      </c>
-      <c r="C37" s="23" t="s">
-        <v>2258</v>
       </c>
       <c r="D37" s="23" t="s">
         <v>84</v>
       </c>
       <c r="E37" s="23" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
       <c r="F37" s="32">
         <v>125.0</v>
@@ -19979,19 +19953,19 @@
         <v>222</v>
       </c>
       <c r="P37" s="27" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
       <c r="Q37" s="27" t="s">
         <v>206</v>
       </c>
       <c r="R37" s="27" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="S37" s="27" t="s">
-        <v>2198</v>
+        <v>2197</v>
       </c>
       <c r="T37" s="27" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="U37" s="27"/>
       <c r="V37" s="27"/>
@@ -20010,19 +19984,19 @@
     </row>
     <row r="38" ht="14.25" customHeight="1">
       <c r="A38" s="23" t="s">
+        <v>2261</v>
+      </c>
+      <c r="B38" s="23" t="s">
         <v>2262</v>
       </c>
-      <c r="B38" s="23" t="s">
+      <c r="C38" s="23" t="s">
         <v>2263</v>
-      </c>
-      <c r="C38" s="23" t="s">
-        <v>2264</v>
       </c>
       <c r="D38" s="23" t="s">
         <v>84</v>
       </c>
       <c r="E38" s="23" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="F38" s="32">
         <v>150.0</v>
@@ -20051,19 +20025,19 @@
         <v>222</v>
       </c>
       <c r="P38" s="27" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
       <c r="Q38" s="27" t="s">
         <v>206</v>
       </c>
       <c r="R38" s="27" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="S38" s="27" t="s">
-        <v>2198</v>
+        <v>2197</v>
       </c>
       <c r="T38" s="27" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="U38" s="27"/>
       <c r="V38" s="27"/>
@@ -20082,19 +20056,19 @@
     </row>
     <row r="39" ht="14.25" customHeight="1">
       <c r="A39" s="23" t="s">
+        <v>2265</v>
+      </c>
+      <c r="B39" s="23" t="s">
         <v>2266</v>
       </c>
-      <c r="B39" s="23" t="s">
+      <c r="C39" s="27" t="s">
         <v>2267</v>
-      </c>
-      <c r="C39" s="27" t="s">
-        <v>2268</v>
       </c>
       <c r="D39" s="23" t="s">
         <v>84</v>
       </c>
       <c r="E39" s="27" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
       <c r="F39" s="32">
         <v>250.0</v>
@@ -20121,13 +20095,13 @@
         <v>206</v>
       </c>
       <c r="P39" s="27" t="s">
-        <v>2270</v>
+        <v>2269</v>
       </c>
       <c r="Q39" s="27" t="s">
         <v>885</v>
       </c>
       <c r="R39" s="27" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
       <c r="S39" s="23"/>
       <c r="T39" s="23"/>
@@ -20148,19 +20122,19 @@
     </row>
     <row r="40" ht="14.25" customHeight="1">
       <c r="A40" s="23" t="s">
+        <v>2271</v>
+      </c>
+      <c r="B40" s="23" t="s">
         <v>2272</v>
       </c>
-      <c r="B40" s="23" t="s">
+      <c r="C40" s="23" t="s">
         <v>2273</v>
-      </c>
-      <c r="C40" s="23" t="s">
-        <v>2274</v>
       </c>
       <c r="D40" s="23" t="s">
         <v>84</v>
       </c>
       <c r="E40" s="23" t="s">
-        <v>2275</v>
+        <v>2274</v>
       </c>
       <c r="F40" s="32">
         <v>295.0</v>
@@ -20184,16 +20158,16 @@
       </c>
       <c r="N40" s="25"/>
       <c r="O40" s="27" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="P40" s="27" t="s">
-        <v>2276</v>
+        <v>2275</v>
       </c>
       <c r="Q40" s="27" t="s">
         <v>222</v>
       </c>
       <c r="R40" s="27" t="s">
-        <v>2277</v>
+        <v>2276</v>
       </c>
       <c r="S40" s="23"/>
       <c r="T40" s="23"/>
@@ -20214,19 +20188,19 @@
     </row>
     <row r="41" ht="14.25" customHeight="1">
       <c r="A41" s="23" t="s">
+        <v>2277</v>
+      </c>
+      <c r="B41" s="23" t="s">
         <v>2278</v>
       </c>
-      <c r="B41" s="23" t="s">
+      <c r="C41" s="23" t="s">
         <v>2279</v>
-      </c>
-      <c r="C41" s="23" t="s">
-        <v>2280</v>
       </c>
       <c r="D41" s="23" t="s">
         <v>84</v>
       </c>
       <c r="E41" s="23" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
       <c r="F41" s="32">
         <v>295.0</v>
@@ -20250,16 +20224,16 @@
       </c>
       <c r="N41" s="25"/>
       <c r="O41" s="27" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="P41" s="27" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="Q41" s="27" t="s">
         <v>222</v>
       </c>
       <c r="R41" s="27" t="s">
-        <v>2277</v>
+        <v>2276</v>
       </c>
       <c r="S41" s="23"/>
       <c r="T41" s="23"/>
@@ -20280,19 +20254,19 @@
     </row>
     <row r="42" ht="14.25" customHeight="1">
       <c r="A42" s="23" t="s">
+        <v>2282</v>
+      </c>
+      <c r="B42" s="23" t="s">
         <v>2283</v>
       </c>
-      <c r="B42" s="23" t="s">
+      <c r="C42" s="23" t="s">
         <v>2284</v>
-      </c>
-      <c r="C42" s="23" t="s">
-        <v>2285</v>
       </c>
       <c r="D42" s="23" t="s">
         <v>84</v>
       </c>
       <c r="E42" s="23" t="s">
-        <v>2286</v>
+        <v>2285</v>
       </c>
       <c r="F42" s="32">
         <v>895.0</v>
@@ -20316,16 +20290,16 @@
       </c>
       <c r="N42" s="25"/>
       <c r="O42" s="27" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="P42" s="27" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="Q42" s="27" t="s">
         <v>891</v>
       </c>
       <c r="R42" s="27" t="s">
-        <v>2287</v>
+        <v>2286</v>
       </c>
       <c r="S42" s="23"/>
       <c r="T42" s="23"/>
@@ -20346,19 +20320,19 @@
     </row>
     <row r="43" ht="14.25" customHeight="1">
       <c r="A43" s="23" t="s">
+        <v>2287</v>
+      </c>
+      <c r="B43" s="23" t="s">
         <v>2288</v>
       </c>
-      <c r="B43" s="23" t="s">
+      <c r="C43" s="23" t="s">
         <v>2289</v>
-      </c>
-      <c r="C43" s="23" t="s">
-        <v>2290</v>
       </c>
       <c r="D43" s="23" t="s">
         <v>84</v>
       </c>
       <c r="E43" s="23" t="s">
-        <v>2291</v>
+        <v>2290</v>
       </c>
       <c r="F43" s="32">
         <v>750.0</v>
@@ -20382,16 +20356,16 @@
       </c>
       <c r="N43" s="25"/>
       <c r="O43" s="27" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="P43" s="27" t="s">
-        <v>2292</v>
+        <v>2291</v>
       </c>
       <c r="Q43" s="27" t="s">
         <v>891</v>
       </c>
       <c r="R43" s="27" t="s">
-        <v>2287</v>
+        <v>2286</v>
       </c>
       <c r="S43" s="23"/>
       <c r="T43" s="23"/>
@@ -20412,19 +20386,19 @@
     </row>
     <row r="44" ht="14.25" customHeight="1">
       <c r="A44" s="23" t="s">
+        <v>2292</v>
+      </c>
+      <c r="B44" s="23" t="s">
         <v>2293</v>
       </c>
-      <c r="B44" s="23" t="s">
+      <c r="C44" s="23" t="s">
         <v>2294</v>
-      </c>
-      <c r="C44" s="23" t="s">
-        <v>2295</v>
       </c>
       <c r="D44" s="23" t="s">
         <v>84</v>
       </c>
       <c r="E44" s="23" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="F44" s="32">
         <v>250.0</v>
@@ -20448,28 +20422,28 @@
       </c>
       <c r="N44" s="25"/>
       <c r="O44" s="27" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="P44" s="27" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
       <c r="Q44" s="27" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="R44" s="27" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="S44" s="27" t="s">
         <v>543</v>
       </c>
       <c r="T44" s="27" t="s">
-        <v>2298</v>
+        <v>2297</v>
       </c>
       <c r="U44" s="27" t="s">
         <v>885</v>
       </c>
       <c r="V44" s="27" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="W44" s="27"/>
       <c r="X44" s="27"/>
@@ -20486,19 +20460,19 @@
     </row>
     <row r="45" ht="14.25" customHeight="1">
       <c r="A45" s="23" t="s">
+        <v>2299</v>
+      </c>
+      <c r="B45" s="23" t="s">
         <v>2300</v>
       </c>
-      <c r="B45" s="23" t="s">
+      <c r="C45" s="23" t="s">
         <v>2301</v>
-      </c>
-      <c r="C45" s="23" t="s">
-        <v>2302</v>
       </c>
       <c r="D45" s="23" t="s">
         <v>84</v>
       </c>
       <c r="E45" s="23" t="s">
-        <v>2303</v>
+        <v>2302</v>
       </c>
       <c r="F45" s="32">
         <v>250.0</v>
@@ -20522,28 +20496,28 @@
       </c>
       <c r="N45" s="25"/>
       <c r="O45" s="27" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="P45" s="27" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
       <c r="Q45" s="27" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="R45" s="27" t="s">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="S45" s="27" t="s">
         <v>543</v>
       </c>
       <c r="T45" s="27" t="s">
-        <v>2298</v>
+        <v>2297</v>
       </c>
       <c r="U45" s="27" t="s">
         <v>885</v>
       </c>
       <c r="V45" s="27" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="W45" s="27"/>
       <c r="X45" s="27"/>
@@ -20560,19 +20534,19 @@
     </row>
     <row r="46" ht="14.25" customHeight="1">
       <c r="A46" s="23" t="s">
+        <v>2304</v>
+      </c>
+      <c r="B46" s="23" t="s">
         <v>2305</v>
       </c>
-      <c r="B46" s="23" t="s">
+      <c r="C46" s="23" t="s">
         <v>2306</v>
-      </c>
-      <c r="C46" s="23" t="s">
-        <v>2307</v>
       </c>
       <c r="D46" s="23" t="s">
         <v>151</v>
       </c>
       <c r="E46" s="23" t="s">
-        <v>2308</v>
+        <v>2307</v>
       </c>
       <c r="F46" s="32">
         <v>595.0</v>
@@ -20596,77 +20570,77 @@
       </c>
       <c r="N46" s="25"/>
       <c r="O46" s="27" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="P46" s="27" t="s">
+        <v>2308</v>
+      </c>
+      <c r="Q46" s="27" t="s">
+        <v>1988</v>
+      </c>
+      <c r="R46" s="27" t="s">
         <v>2309</v>
       </c>
-      <c r="Q46" s="27" t="s">
-        <v>1989</v>
-      </c>
-      <c r="R46" s="27" t="s">
+      <c r="S46" s="27" t="s">
         <v>2310</v>
       </c>
-      <c r="S46" s="27" t="s">
+      <c r="T46" s="27" t="s">
         <v>2311</v>
-      </c>
-      <c r="T46" s="27" t="s">
-        <v>2312</v>
       </c>
       <c r="U46" s="27" t="s">
         <v>543</v>
       </c>
       <c r="V46" s="27" t="s">
+        <v>2312</v>
+      </c>
+      <c r="W46" s="27" t="s">
+        <v>1799</v>
+      </c>
+      <c r="X46" s="27" t="s">
         <v>2313</v>
       </c>
-      <c r="W46" s="27" t="s">
-        <v>1800</v>
-      </c>
-      <c r="X46" s="27" t="s">
+      <c r="Y46" s="27" t="s">
+        <v>1899</v>
+      </c>
+      <c r="Z46" s="27" t="s">
         <v>2314</v>
       </c>
-      <c r="Y46" s="27" t="s">
-        <v>1900</v>
-      </c>
-      <c r="Z46" s="27" t="s">
+      <c r="AA46" s="27" t="s">
         <v>2315</v>
       </c>
-      <c r="AA46" s="27" t="s">
+      <c r="AB46" s="27" t="s">
         <v>2316</v>
-      </c>
-      <c r="AB46" s="27" t="s">
-        <v>2317</v>
       </c>
       <c r="AC46" s="27" t="s">
         <v>781</v>
       </c>
       <c r="AD46" s="27" t="s">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="AE46" s="27" t="s">
         <v>781</v>
       </c>
       <c r="AF46" s="27" t="s">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="AG46" s="27"/>
       <c r="AH46" s="27"/>
     </row>
     <row r="47" ht="14.25" customHeight="1">
       <c r="A47" s="23" t="s">
+        <v>2318</v>
+      </c>
+      <c r="B47" s="23" t="s">
         <v>2319</v>
       </c>
-      <c r="B47" s="23" t="s">
+      <c r="C47" s="23" t="s">
         <v>2320</v>
-      </c>
-      <c r="C47" s="23" t="s">
-        <v>2321</v>
       </c>
       <c r="D47" s="23" t="s">
         <v>151</v>
       </c>
       <c r="E47" s="23" t="s">
-        <v>2322</v>
+        <v>2321</v>
       </c>
       <c r="F47" s="32">
         <v>95.0</v>
@@ -20690,28 +20664,28 @@
       </c>
       <c r="N47" s="25"/>
       <c r="O47" s="27" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="P47" s="27" t="s">
+        <v>2322</v>
+      </c>
+      <c r="Q47" s="27" t="s">
+        <v>1988</v>
+      </c>
+      <c r="R47" s="27" t="s">
         <v>2323</v>
       </c>
-      <c r="Q47" s="27" t="s">
-        <v>1989</v>
-      </c>
-      <c r="R47" s="27" t="s">
+      <c r="S47" s="27" t="s">
         <v>2324</v>
       </c>
-      <c r="S47" s="27" t="s">
+      <c r="T47" s="27" t="s">
         <v>2325</v>
-      </c>
-      <c r="T47" s="27" t="s">
-        <v>2326</v>
       </c>
       <c r="U47" s="27" t="s">
         <v>605</v>
       </c>
       <c r="V47" s="27" t="s">
-        <v>2327</v>
+        <v>2326</v>
       </c>
       <c r="W47" s="27"/>
       <c r="X47" s="27"/>
@@ -20728,19 +20702,19 @@
     </row>
     <row r="48" ht="14.25" customHeight="1">
       <c r="A48" s="23" t="s">
+        <v>2327</v>
+      </c>
+      <c r="B48" s="23" t="s">
         <v>2328</v>
       </c>
-      <c r="B48" s="23" t="s">
+      <c r="C48" s="23" t="s">
         <v>2329</v>
-      </c>
-      <c r="C48" s="23" t="s">
-        <v>2330</v>
       </c>
       <c r="D48" s="23" t="s">
         <v>151</v>
       </c>
       <c r="E48" s="23" t="s">
-        <v>2331</v>
+        <v>2330</v>
       </c>
       <c r="F48" s="32">
         <v>125.0</v>
@@ -20764,22 +20738,22 @@
       </c>
       <c r="N48" s="25"/>
       <c r="O48" s="27" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="P48" s="27" t="s">
+        <v>2331</v>
+      </c>
+      <c r="Q48" s="27" t="s">
         <v>2332</v>
       </c>
-      <c r="Q48" s="27" t="s">
+      <c r="R48" s="27" t="s">
         <v>2333</v>
       </c>
-      <c r="R48" s="27" t="s">
+      <c r="S48" s="27" t="s">
         <v>2334</v>
       </c>
-      <c r="S48" s="27" t="s">
+      <c r="T48" s="27" t="s">
         <v>2335</v>
-      </c>
-      <c r="T48" s="27" t="s">
-        <v>2336</v>
       </c>
       <c r="U48" s="27"/>
       <c r="V48" s="27"/>
@@ -20798,19 +20772,19 @@
     </row>
     <row r="49" ht="14.25" customHeight="1">
       <c r="A49" s="23" t="s">
+        <v>2336</v>
+      </c>
+      <c r="B49" s="23" t="s">
         <v>2337</v>
       </c>
-      <c r="B49" s="23" t="s">
+      <c r="C49" s="23" t="s">
         <v>2338</v>
-      </c>
-      <c r="C49" s="23" t="s">
-        <v>2339</v>
       </c>
       <c r="D49" s="23" t="s">
         <v>114</v>
       </c>
       <c r="E49" s="23" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
       <c r="F49" s="32">
         <v>150.0</v>
@@ -20836,40 +20810,40 @@
         <v>4.88</v>
       </c>
       <c r="O49" s="27" t="s">
+        <v>2082</v>
+      </c>
+      <c r="P49" s="27" t="s">
         <v>2083</v>
-      </c>
-      <c r="P49" s="27" t="s">
-        <v>2084</v>
       </c>
       <c r="Q49" s="27" t="s">
         <v>206</v>
       </c>
       <c r="R49" s="27" t="s">
+        <v>2340</v>
+      </c>
+      <c r="S49" s="27" t="s">
         <v>2341</v>
       </c>
-      <c r="S49" s="27" t="s">
+      <c r="T49" s="27" t="s">
         <v>2342</v>
       </c>
-      <c r="T49" s="27" t="s">
+      <c r="U49" s="27" t="s">
+        <v>2197</v>
+      </c>
+      <c r="V49" s="27" t="s">
         <v>2343</v>
       </c>
-      <c r="U49" s="27" t="s">
-        <v>2198</v>
-      </c>
-      <c r="V49" s="27" t="s">
+      <c r="W49" s="27" t="s">
         <v>2344</v>
       </c>
-      <c r="W49" s="27" t="s">
+      <c r="X49" s="27" t="s">
         <v>2345</v>
       </c>
-      <c r="X49" s="27" t="s">
+      <c r="Y49" s="27" t="s">
         <v>2346</v>
       </c>
-      <c r="Y49" s="27" t="s">
+      <c r="Z49" s="27" t="s">
         <v>2347</v>
-      </c>
-      <c r="Z49" s="27" t="s">
-        <v>2348</v>
       </c>
       <c r="AA49" s="27"/>
       <c r="AB49" s="27"/>
@@ -20882,19 +20856,19 @@
     </row>
     <row r="50" ht="14.25" customHeight="1">
       <c r="A50" s="23" t="s">
+        <v>2348</v>
+      </c>
+      <c r="B50" s="23" t="s">
         <v>2349</v>
       </c>
-      <c r="B50" s="23" t="s">
+      <c r="C50" s="27" t="s">
         <v>2350</v>
-      </c>
-      <c r="C50" s="27" t="s">
-        <v>2351</v>
       </c>
       <c r="D50" s="23" t="s">
         <v>114</v>
       </c>
       <c r="E50" s="23" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
       <c r="F50" s="32">
         <v>150.0</v>
@@ -20920,40 +20894,40 @@
         <v>1.83</v>
       </c>
       <c r="O50" s="27" t="s">
+        <v>2082</v>
+      </c>
+      <c r="P50" s="27" t="s">
         <v>2083</v>
-      </c>
-      <c r="P50" s="27" t="s">
-        <v>2084</v>
       </c>
       <c r="Q50" s="27" t="s">
         <v>206</v>
       </c>
       <c r="R50" s="27" t="s">
+        <v>2340</v>
+      </c>
+      <c r="S50" s="27" t="s">
         <v>2341</v>
       </c>
-      <c r="S50" s="27" t="s">
+      <c r="T50" s="27" t="s">
         <v>2342</v>
       </c>
-      <c r="T50" s="27" t="s">
+      <c r="U50" s="27" t="s">
+        <v>2197</v>
+      </c>
+      <c r="V50" s="27" t="s">
         <v>2343</v>
       </c>
-      <c r="U50" s="27" t="s">
-        <v>2198</v>
-      </c>
-      <c r="V50" s="27" t="s">
+      <c r="W50" s="27" t="s">
         <v>2344</v>
       </c>
-      <c r="W50" s="27" t="s">
+      <c r="X50" s="27" t="s">
         <v>2345</v>
       </c>
-      <c r="X50" s="27" t="s">
+      <c r="Y50" s="27" t="s">
         <v>2346</v>
       </c>
-      <c r="Y50" s="27" t="s">
+      <c r="Z50" s="27" t="s">
         <v>2347</v>
-      </c>
-      <c r="Z50" s="27" t="s">
-        <v>2348</v>
       </c>
       <c r="AA50" s="27"/>
       <c r="AB50" s="27"/>
@@ -20966,19 +20940,19 @@
     </row>
     <row r="51" ht="14.25" customHeight="1">
       <c r="A51" s="23" t="s">
+        <v>2352</v>
+      </c>
+      <c r="B51" s="23" t="s">
         <v>2353</v>
       </c>
-      <c r="B51" s="23" t="s">
+      <c r="C51" s="23" t="s">
         <v>2354</v>
-      </c>
-      <c r="C51" s="23" t="s">
-        <v>2355</v>
       </c>
       <c r="D51" s="23" t="s">
         <v>114</v>
       </c>
       <c r="E51" s="23" t="s">
-        <v>2356</v>
+        <v>2355</v>
       </c>
       <c r="F51" s="32">
         <v>295.0</v>
@@ -21002,52 +20976,52 @@
       </c>
       <c r="N51" s="25"/>
       <c r="O51" s="27" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="P51" s="27" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="Q51" s="27" t="s">
         <v>1506</v>
       </c>
       <c r="R51" s="27" t="s">
+        <v>2357</v>
+      </c>
+      <c r="S51" s="27" t="s">
+        <v>2040</v>
+      </c>
+      <c r="T51" s="27" t="s">
         <v>2358</v>
       </c>
-      <c r="S51" s="27" t="s">
-        <v>2041</v>
-      </c>
-      <c r="T51" s="27" t="s">
+      <c r="U51" s="27" t="s">
         <v>2359</v>
       </c>
-      <c r="U51" s="27" t="s">
+      <c r="V51" s="27" t="s">
         <v>2360</v>
-      </c>
-      <c r="V51" s="27" t="s">
-        <v>2361</v>
       </c>
       <c r="W51" s="27" t="s">
         <v>891</v>
       </c>
       <c r="X51" s="27" t="s">
-        <v>2362</v>
+        <v>2361</v>
       </c>
       <c r="Y51" s="27" t="s">
         <v>294</v>
       </c>
       <c r="Z51" s="27" t="s">
-        <v>2363</v>
+        <v>2362</v>
       </c>
       <c r="AA51" s="27" t="s">
         <v>489</v>
       </c>
       <c r="AB51" s="27" t="s">
-        <v>2364</v>
+        <v>2363</v>
       </c>
       <c r="AC51" s="27" t="s">
         <v>489</v>
       </c>
       <c r="AD51" s="27" t="s">
-        <v>2364</v>
+        <v>2363</v>
       </c>
       <c r="AE51" s="27"/>
       <c r="AF51" s="27"/>
@@ -21056,19 +21030,19 @@
     </row>
     <row r="52" ht="14.25" customHeight="1">
       <c r="A52" s="23" t="s">
+        <v>2364</v>
+      </c>
+      <c r="B52" s="23" t="s">
         <v>2365</v>
       </c>
-      <c r="B52" s="23" t="s">
+      <c r="C52" s="23" t="s">
         <v>2366</v>
-      </c>
-      <c r="C52" s="23" t="s">
-        <v>2367</v>
       </c>
       <c r="D52" s="23" t="s">
         <v>138</v>
       </c>
       <c r="E52" s="23" t="s">
-        <v>2368</v>
+        <v>2367</v>
       </c>
       <c r="F52" s="32">
         <v>750.0</v>
@@ -21095,13 +21069,13 @@
         <v>885</v>
       </c>
       <c r="P52" s="27" t="s">
-        <v>2369</v>
+        <v>2368</v>
       </c>
       <c r="Q52" s="27" t="s">
         <v>308</v>
       </c>
       <c r="R52" s="27" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="S52" s="23"/>
       <c r="T52" s="23"/>
@@ -21122,19 +21096,19 @@
     </row>
     <row r="53" ht="14.25" customHeight="1">
       <c r="A53" s="23" t="s">
+        <v>2370</v>
+      </c>
+      <c r="B53" s="23" t="s">
         <v>2371</v>
       </c>
-      <c r="B53" s="23" t="s">
+      <c r="C53" s="23" t="s">
         <v>2372</v>
-      </c>
-      <c r="C53" s="23" t="s">
-        <v>2373</v>
       </c>
       <c r="D53" s="23" t="s">
         <v>138</v>
       </c>
       <c r="E53" s="23" t="s">
-        <v>2374</v>
+        <v>2373</v>
       </c>
       <c r="F53" s="32">
         <v>295.0</v>
@@ -21158,16 +21132,16 @@
       </c>
       <c r="N53" s="25"/>
       <c r="O53" s="27" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="P53" s="27" t="s">
-        <v>2375</v>
+        <v>2374</v>
       </c>
       <c r="Q53" s="27" t="s">
         <v>308</v>
       </c>
       <c r="R53" s="27" t="s">
-        <v>2376</v>
+        <v>2375</v>
       </c>
       <c r="S53" s="23"/>
       <c r="T53" s="23"/>
@@ -21188,19 +21162,19 @@
     </row>
     <row r="54" ht="14.25" customHeight="1">
       <c r="A54" s="23" t="s">
+        <v>2376</v>
+      </c>
+      <c r="B54" s="23" t="s">
         <v>2377</v>
       </c>
-      <c r="B54" s="23" t="s">
+      <c r="C54" s="23" t="s">
         <v>2378</v>
-      </c>
-      <c r="C54" s="23" t="s">
-        <v>2379</v>
       </c>
       <c r="D54" s="23" t="s">
         <v>138</v>
       </c>
       <c r="E54" s="23" t="s">
-        <v>2380</v>
+        <v>2379</v>
       </c>
       <c r="F54" s="32">
         <v>850.0</v>
@@ -21224,16 +21198,16 @@
       </c>
       <c r="N54" s="25"/>
       <c r="O54" s="27" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="P54" s="27" t="s">
-        <v>2381</v>
+        <v>2380</v>
       </c>
       <c r="Q54" s="27" t="s">
         <v>308</v>
       </c>
       <c r="R54" s="27" t="s">
-        <v>2376</v>
+        <v>2375</v>
       </c>
       <c r="S54" s="23"/>
       <c r="T54" s="23"/>
@@ -21254,19 +21228,19 @@
     </row>
     <row r="55" ht="14.25" customHeight="1">
       <c r="A55" s="23" t="s">
+        <v>2381</v>
+      </c>
+      <c r="B55" s="23" t="s">
         <v>2382</v>
       </c>
-      <c r="B55" s="23" t="s">
+      <c r="C55" s="23" t="s">
         <v>2383</v>
-      </c>
-      <c r="C55" s="23" t="s">
-        <v>2384</v>
       </c>
       <c r="D55" s="23" t="s">
         <v>138</v>
       </c>
       <c r="E55" s="23" t="s">
-        <v>2385</v>
+        <v>2384</v>
       </c>
       <c r="F55" s="32">
         <v>175.0</v>
@@ -21292,28 +21266,28 @@
         <v>5.18</v>
       </c>
       <c r="O55" s="27" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="P55" s="27" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
       <c r="Q55" s="27" t="s">
+        <v>2341</v>
+      </c>
+      <c r="R55" s="27" t="s">
         <v>2342</v>
-      </c>
-      <c r="R55" s="27" t="s">
-        <v>2343</v>
       </c>
       <c r="S55" s="27" t="s">
         <v>432</v>
       </c>
       <c r="T55" s="27" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="U55" s="27" t="s">
         <v>308</v>
       </c>
       <c r="V55" s="27" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="W55" s="27"/>
       <c r="X55" s="27"/>
@@ -21330,19 +21304,19 @@
     </row>
     <row r="56" ht="14.25" customHeight="1">
       <c r="A56" s="23" t="s">
+        <v>2386</v>
+      </c>
+      <c r="B56" s="23" t="s">
         <v>2387</v>
       </c>
-      <c r="B56" s="23" t="s">
+      <c r="C56" s="23" t="s">
         <v>2388</v>
-      </c>
-      <c r="C56" s="23" t="s">
-        <v>2389</v>
       </c>
       <c r="D56" s="23" t="s">
         <v>138</v>
       </c>
       <c r="E56" s="23" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
       <c r="F56" s="32">
         <v>175.0</v>
@@ -21368,28 +21342,28 @@
         <v>3.05</v>
       </c>
       <c r="O56" s="27" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="P56" s="27" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
       <c r="Q56" s="27" t="s">
+        <v>2341</v>
+      </c>
+      <c r="R56" s="27" t="s">
         <v>2342</v>
-      </c>
-      <c r="R56" s="27" t="s">
-        <v>2343</v>
       </c>
       <c r="S56" s="27" t="s">
         <v>432</v>
       </c>
       <c r="T56" s="27" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="U56" s="27" t="s">
         <v>308</v>
       </c>
       <c r="V56" s="27" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="W56" s="27"/>
       <c r="X56" s="27"/>
@@ -21406,19 +21380,19 @@
     </row>
     <row r="57" ht="14.25" customHeight="1">
       <c r="A57" s="23" t="s">
+        <v>2390</v>
+      </c>
+      <c r="B57" s="23" t="s">
         <v>2391</v>
       </c>
-      <c r="B57" s="23" t="s">
+      <c r="C57" s="23" t="s">
         <v>2392</v>
-      </c>
-      <c r="C57" s="23" t="s">
-        <v>2393</v>
       </c>
       <c r="D57" s="23" t="s">
         <v>138</v>
       </c>
       <c r="E57" s="23" t="s">
-        <v>2394</v>
+        <v>2393</v>
       </c>
       <c r="F57" s="32">
         <v>150.0</v>
@@ -21444,28 +21418,28 @@
         <v>1.83</v>
       </c>
       <c r="O57" s="27" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="P57" s="27" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
       <c r="Q57" s="27" t="s">
+        <v>2341</v>
+      </c>
+      <c r="R57" s="27" t="s">
         <v>2342</v>
-      </c>
-      <c r="R57" s="27" t="s">
-        <v>2343</v>
       </c>
       <c r="S57" s="27" t="s">
         <v>432</v>
       </c>
       <c r="T57" s="27" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="U57" s="27" t="s">
         <v>308</v>
       </c>
       <c r="V57" s="27" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="W57" s="27"/>
       <c r="X57" s="27"/>
@@ -21482,19 +21456,19 @@
     </row>
     <row r="58" ht="14.25" customHeight="1">
       <c r="A58" s="23" t="s">
+        <v>2394</v>
+      </c>
+      <c r="B58" s="23" t="s">
         <v>2395</v>
       </c>
-      <c r="B58" s="23" t="s">
+      <c r="C58" s="23" t="s">
         <v>2396</v>
-      </c>
-      <c r="C58" s="23" t="s">
-        <v>2397</v>
       </c>
       <c r="D58" s="23" t="s">
         <v>138</v>
       </c>
       <c r="E58" s="23" t="s">
-        <v>2398</v>
+        <v>2397</v>
       </c>
       <c r="F58" s="32">
         <v>125.0</v>
@@ -21520,28 +21494,28 @@
         <v>5.18</v>
       </c>
       <c r="O58" s="27" t="s">
+        <v>2082</v>
+      </c>
+      <c r="P58" s="27" t="s">
         <v>2083</v>
       </c>
-      <c r="P58" s="27" t="s">
-        <v>2084</v>
-      </c>
       <c r="Q58" s="27" t="s">
+        <v>2341</v>
+      </c>
+      <c r="R58" s="27" t="s">
         <v>2342</v>
-      </c>
-      <c r="R58" s="27" t="s">
-        <v>2343</v>
       </c>
       <c r="S58" s="27" t="s">
         <v>432</v>
       </c>
       <c r="T58" s="27" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="U58" s="27" t="s">
         <v>308</v>
       </c>
       <c r="V58" s="27" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="W58" s="27"/>
       <c r="X58" s="27"/>
@@ -21558,19 +21532,19 @@
     </row>
     <row r="59" ht="14.25" customHeight="1">
       <c r="A59" s="23" t="s">
+        <v>2398</v>
+      </c>
+      <c r="B59" s="23" t="s">
         <v>2399</v>
       </c>
-      <c r="B59" s="23" t="s">
+      <c r="C59" s="23" t="s">
         <v>2400</v>
-      </c>
-      <c r="C59" s="23" t="s">
-        <v>2401</v>
       </c>
       <c r="D59" s="23" t="s">
         <v>138</v>
       </c>
       <c r="E59" s="23" t="s">
-        <v>2402</v>
+        <v>2401</v>
       </c>
       <c r="F59" s="32">
         <v>95.0</v>
@@ -21596,28 +21570,28 @@
         <v>3.66</v>
       </c>
       <c r="O59" s="27" t="s">
+        <v>2082</v>
+      </c>
+      <c r="P59" s="27" t="s">
         <v>2083</v>
       </c>
-      <c r="P59" s="27" t="s">
-        <v>2084</v>
-      </c>
       <c r="Q59" s="27" t="s">
+        <v>2341</v>
+      </c>
+      <c r="R59" s="27" t="s">
         <v>2342</v>
-      </c>
-      <c r="R59" s="27" t="s">
-        <v>2343</v>
       </c>
       <c r="S59" s="27" t="s">
         <v>432</v>
       </c>
       <c r="T59" s="27" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="U59" s="27" t="s">
         <v>308</v>
       </c>
       <c r="V59" s="27" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="W59" s="27"/>
       <c r="X59" s="27"/>
@@ -21634,19 +21608,19 @@
     </row>
     <row r="60" ht="14.25" customHeight="1">
       <c r="A60" s="23" t="s">
+        <v>2402</v>
+      </c>
+      <c r="B60" s="23" t="s">
         <v>2403</v>
       </c>
-      <c r="B60" s="23" t="s">
+      <c r="C60" s="23" t="s">
         <v>2404</v>
-      </c>
-      <c r="C60" s="23" t="s">
-        <v>2405</v>
       </c>
       <c r="D60" s="23" t="s">
         <v>138</v>
       </c>
       <c r="E60" s="23" t="s">
-        <v>2406</v>
+        <v>2405</v>
       </c>
       <c r="F60" s="32">
         <v>75.0</v>
@@ -21672,28 +21646,28 @@
         <v>1.83</v>
       </c>
       <c r="O60" s="27" t="s">
+        <v>2082</v>
+      </c>
+      <c r="P60" s="27" t="s">
         <v>2083</v>
       </c>
-      <c r="P60" s="27" t="s">
-        <v>2084</v>
-      </c>
       <c r="Q60" s="27" t="s">
+        <v>2341</v>
+      </c>
+      <c r="R60" s="27" t="s">
         <v>2342</v>
-      </c>
-      <c r="R60" s="27" t="s">
-        <v>2343</v>
       </c>
       <c r="S60" s="27" t="s">
         <v>432</v>
       </c>
       <c r="T60" s="27" t="s">
-        <v>2386</v>
+        <v>2385</v>
       </c>
       <c r="U60" s="27" t="s">
         <v>308</v>
       </c>
       <c r="V60" s="27" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="W60" s="27"/>
       <c r="X60" s="27"/>
@@ -21710,19 +21684,19 @@
     </row>
     <row r="61" ht="14.25" customHeight="1">
       <c r="A61" s="23" t="s">
+        <v>2406</v>
+      </c>
+      <c r="B61" s="23" t="s">
         <v>2407</v>
       </c>
-      <c r="B61" s="23" t="s">
+      <c r="C61" s="23" t="s">
         <v>2408</v>
-      </c>
-      <c r="C61" s="23" t="s">
-        <v>2409</v>
       </c>
       <c r="D61" s="23" t="s">
         <v>138</v>
       </c>
       <c r="E61" s="23" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="F61" s="32">
         <v>75.0</v>
@@ -21749,13 +21723,13 @@
         <v>232</v>
       </c>
       <c r="P61" s="27" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="Q61" s="27" t="s">
         <v>308</v>
       </c>
       <c r="R61" s="27" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="S61" s="23"/>
       <c r="T61" s="23"/>
@@ -21776,19 +21750,19 @@
     </row>
     <row r="62" ht="14.25" customHeight="1">
       <c r="A62" s="23" t="s">
+        <v>2409</v>
+      </c>
+      <c r="B62" s="23" t="s">
         <v>2410</v>
       </c>
-      <c r="B62" s="23" t="s">
+      <c r="C62" s="23" t="s">
         <v>2411</v>
-      </c>
-      <c r="C62" s="23" t="s">
-        <v>2412</v>
       </c>
       <c r="D62" s="23" t="s">
         <v>138</v>
       </c>
       <c r="E62" s="23" t="s">
-        <v>2413</v>
+        <v>2412</v>
       </c>
       <c r="F62" s="32">
         <v>75.0</v>
@@ -21815,13 +21789,13 @@
         <v>232</v>
       </c>
       <c r="P62" s="27" t="s">
-        <v>2234</v>
+        <v>2233</v>
       </c>
       <c r="Q62" s="27" t="s">
         <v>308</v>
       </c>
       <c r="R62" s="27" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="S62" s="23"/>
       <c r="T62" s="23"/>
@@ -21842,19 +21816,19 @@
     </row>
     <row r="63" ht="14.25" customHeight="1">
       <c r="A63" s="23" t="s">
+        <v>2413</v>
+      </c>
+      <c r="B63" s="23" t="s">
         <v>2414</v>
       </c>
-      <c r="B63" s="23" t="s">
+      <c r="C63" s="27" t="s">
         <v>2415</v>
-      </c>
-      <c r="C63" s="27" t="s">
-        <v>2416</v>
       </c>
       <c r="D63" s="23" t="s">
         <v>138</v>
       </c>
       <c r="E63" s="23" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
       <c r="F63" s="32">
         <v>95.0</v>
@@ -21878,16 +21852,16 @@
       </c>
       <c r="N63" s="25"/>
       <c r="O63" s="27" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="P63" s="27" t="s">
-        <v>2417</v>
+        <v>2416</v>
       </c>
       <c r="Q63" s="27" t="s">
         <v>308</v>
       </c>
       <c r="R63" s="27" t="s">
-        <v>2370</v>
+        <v>2369</v>
       </c>
       <c r="S63" s="23"/>
       <c r="T63" s="23"/>
@@ -21908,19 +21882,19 @@
     </row>
     <row r="64" ht="14.25" customHeight="1">
       <c r="A64" s="23" t="s">
+        <v>2417</v>
+      </c>
+      <c r="B64" s="23" t="s">
         <v>2418</v>
       </c>
-      <c r="B64" s="23" t="s">
+      <c r="C64" s="23" t="s">
         <v>2419</v>
-      </c>
-      <c r="C64" s="23" t="s">
-        <v>2420</v>
       </c>
       <c r="D64" s="23" t="s">
         <v>138</v>
       </c>
       <c r="E64" s="23" t="s">
-        <v>2421</v>
+        <v>2420</v>
       </c>
       <c r="F64" s="32">
         <v>45.0</v>
@@ -21944,16 +21918,16 @@
       </c>
       <c r="N64" s="25"/>
       <c r="O64" s="27" t="s">
-        <v>2422</v>
+        <v>2421</v>
       </c>
       <c r="P64" s="27" t="s">
         <v>1581</v>
       </c>
       <c r="Q64" s="27" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="R64" s="27" t="s">
-        <v>2423</v>
+        <v>2422</v>
       </c>
       <c r="S64" s="23"/>
       <c r="T64" s="23"/>
@@ -21974,19 +21948,19 @@
     </row>
     <row r="65" ht="14.25" customHeight="1">
       <c r="A65" s="23" t="s">
+        <v>2423</v>
+      </c>
+      <c r="B65" s="23" t="s">
         <v>2424</v>
       </c>
-      <c r="B65" s="23" t="s">
+      <c r="C65" s="27" t="s">
         <v>2425</v>
-      </c>
-      <c r="C65" s="27" t="s">
-        <v>2426</v>
       </c>
       <c r="D65" s="23" t="s">
         <v>138</v>
       </c>
       <c r="E65" s="23" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
       <c r="F65" s="32">
         <v>150.0</v>
@@ -22010,22 +21984,22 @@
       </c>
       <c r="N65" s="25"/>
       <c r="O65" s="27" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="P65" s="27" t="s">
+        <v>2427</v>
+      </c>
+      <c r="Q65" s="27" t="s">
+        <v>2040</v>
+      </c>
+      <c r="R65" s="27" t="s">
         <v>2428</v>
-      </c>
-      <c r="Q65" s="27" t="s">
-        <v>2041</v>
-      </c>
-      <c r="R65" s="27" t="s">
-        <v>2429</v>
       </c>
       <c r="S65" s="27" t="s">
         <v>781</v>
       </c>
       <c r="T65" s="27" t="s">
-        <v>2430</v>
+        <v>2429</v>
       </c>
       <c r="U65" s="27"/>
       <c r="V65" s="27"/>
@@ -22044,19 +22018,19 @@
     </row>
     <row r="66" ht="14.25" customHeight="1">
       <c r="A66" s="23" t="s">
+        <v>2430</v>
+      </c>
+      <c r="B66" s="23" t="s">
         <v>2431</v>
       </c>
-      <c r="B66" s="23" t="s">
+      <c r="C66" s="27" t="s">
         <v>2432</v>
-      </c>
-      <c r="C66" s="27" t="s">
-        <v>2433</v>
       </c>
       <c r="D66" s="23" t="s">
         <v>138</v>
       </c>
       <c r="E66" s="27" t="s">
-        <v>2434</v>
+        <v>2433</v>
       </c>
       <c r="F66" s="32">
         <v>75.0</v>
@@ -22080,16 +22054,16 @@
       </c>
       <c r="N66" s="25"/>
       <c r="O66" s="27" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="P66" s="27" t="s">
+        <v>2434</v>
+      </c>
+      <c r="Q66" s="27" t="s">
+        <v>2146</v>
+      </c>
+      <c r="R66" s="27" t="s">
         <v>2435</v>
-      </c>
-      <c r="Q66" s="27" t="s">
-        <v>2147</v>
-      </c>
-      <c r="R66" s="27" t="s">
-        <v>2436</v>
       </c>
       <c r="S66" s="23"/>
       <c r="T66" s="23"/>
@@ -22110,19 +22084,19 @@
     </row>
     <row r="67" ht="14.25" customHeight="1">
       <c r="A67" s="27" t="s">
+        <v>2436</v>
+      </c>
+      <c r="B67" s="27" t="s">
         <v>2437</v>
       </c>
-      <c r="B67" s="27" t="s">
+      <c r="C67" s="27" t="s">
         <v>2438</v>
-      </c>
-      <c r="C67" s="27" t="s">
-        <v>2439</v>
       </c>
       <c r="D67" s="23" t="s">
         <v>138</v>
       </c>
       <c r="E67" s="27" t="s">
-        <v>2440</v>
+        <v>2439</v>
       </c>
       <c r="F67" s="32">
         <v>350.0</v>
@@ -22146,28 +22120,28 @@
       </c>
       <c r="N67" s="25"/>
       <c r="O67" s="27" t="s">
+        <v>2082</v>
+      </c>
+      <c r="P67" s="27" t="s">
         <v>2083</v>
       </c>
-      <c r="P67" s="27" t="s">
-        <v>2084</v>
-      </c>
       <c r="Q67" s="27" t="s">
+        <v>2440</v>
+      </c>
+      <c r="R67" s="27" t="s">
         <v>2441</v>
       </c>
-      <c r="R67" s="27" t="s">
+      <c r="S67" s="27" t="s">
         <v>2442</v>
       </c>
-      <c r="S67" s="27" t="s">
+      <c r="T67" s="27" t="s">
         <v>2443</v>
-      </c>
-      <c r="T67" s="27" t="s">
-        <v>2444</v>
       </c>
       <c r="U67" s="27" t="s">
         <v>308</v>
       </c>
       <c r="V67" s="27" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="W67" s="27"/>
       <c r="X67" s="27"/>
@@ -22600,7 +22574,7 @@
         <v>55</v>
       </c>
       <c r="M1" s="18" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="N1" s="22" t="s">
         <v>179</v>
@@ -22665,19 +22639,19 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="23" t="s">
+        <v>2446</v>
+      </c>
+      <c r="B2" s="23" t="s">
         <v>2447</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="C2" s="27" t="s">
         <v>2448</v>
-      </c>
-      <c r="C2" s="27" t="s">
-        <v>2449</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>84</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>2450</v>
+        <v>2449</v>
       </c>
       <c r="F2" s="24">
         <v>5695.0</v>
@@ -22703,31 +22677,31 @@
         <v>292</v>
       </c>
       <c r="O2" s="27" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="P2" s="27" t="s">
         <v>232</v>
       </c>
       <c r="Q2" s="27" t="s">
+        <v>2451</v>
+      </c>
+      <c r="R2" s="27" t="s">
         <v>2452</v>
-      </c>
-      <c r="R2" s="27" t="s">
-        <v>2453</v>
       </c>
       <c r="S2" s="27" t="s">
         <v>403</v>
       </c>
       <c r="T2" s="27" t="s">
+        <v>2453</v>
+      </c>
+      <c r="U2" s="27" t="s">
         <v>2454</v>
       </c>
-      <c r="U2" s="27" t="s">
+      <c r="V2" s="27" t="s">
         <v>2455</v>
       </c>
-      <c r="V2" s="27" t="s">
+      <c r="W2" s="27" t="s">
         <v>2456</v>
-      </c>
-      <c r="W2" s="27" t="s">
-        <v>2457</v>
       </c>
       <c r="X2" s="27" t="s">
         <v>900</v>
@@ -22739,42 +22713,42 @@
         <v>498</v>
       </c>
       <c r="AA2" s="27" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="AB2" s="27" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="AC2" s="27" t="s">
+        <v>2457</v>
+      </c>
+      <c r="AD2" s="27" t="s">
         <v>2458</v>
       </c>
-      <c r="AD2" s="27" t="s">
+      <c r="AE2" s="27" t="s">
         <v>2459</v>
       </c>
-      <c r="AE2" s="27" t="s">
+      <c r="AF2" s="27" t="s">
         <v>2460</v>
       </c>
-      <c r="AF2" s="27" t="s">
+      <c r="AG2" s="27" t="s">
         <v>2461</v>
-      </c>
-      <c r="AG2" s="27" t="s">
-        <v>2462</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="23" t="s">
+        <v>2462</v>
+      </c>
+      <c r="B3" s="23" t="s">
         <v>2463</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="C3" s="27" t="s">
         <v>2464</v>
-      </c>
-      <c r="C3" s="27" t="s">
-        <v>2465</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>114</v>
       </c>
       <c r="E3" s="27" t="s">
-        <v>2466</v>
+        <v>2465</v>
       </c>
       <c r="F3" s="25">
         <v>70000.0</v>
@@ -22794,37 +22768,37 @@
         <v>113</v>
       </c>
       <c r="M3" s="23" t="s">
-        <v>2467</v>
+        <v>2466</v>
       </c>
       <c r="N3" s="27" t="s">
         <v>881</v>
       </c>
       <c r="O3" s="27" t="s">
-        <v>2468</v>
+        <v>2467</v>
       </c>
       <c r="P3" s="27" t="s">
         <v>232</v>
       </c>
       <c r="Q3" s="27" t="s">
-        <v>2469</v>
+        <v>2468</v>
       </c>
       <c r="R3" s="27" t="s">
         <v>885</v>
       </c>
       <c r="S3" s="27" t="s">
-        <v>2470</v>
+        <v>2469</v>
       </c>
       <c r="T3" s="27" t="s">
         <v>543</v>
       </c>
       <c r="U3" s="27" t="s">
-        <v>2471</v>
+        <v>2470</v>
       </c>
       <c r="V3" s="27" t="s">
         <v>491</v>
       </c>
       <c r="W3" s="27" t="s">
-        <v>2472</v>
+        <v>2471</v>
       </c>
       <c r="X3" s="27"/>
       <c r="Y3" s="27"/>
@@ -22839,19 +22813,19 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="23" t="s">
+        <v>2472</v>
+      </c>
+      <c r="B4" s="23" t="s">
         <v>2473</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="C4" s="27" t="s">
         <v>2474</v>
-      </c>
-      <c r="C4" s="27" t="s">
-        <v>2475</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>114</v>
       </c>
       <c r="E4" s="27" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="F4" s="25">
         <v>46200.0</v>
@@ -22871,37 +22845,37 @@
         <v>113</v>
       </c>
       <c r="M4" s="27" t="s">
-        <v>2467</v>
+        <v>2466</v>
       </c>
       <c r="N4" s="27" t="s">
         <v>881</v>
       </c>
       <c r="O4" s="27" t="s">
-        <v>2468</v>
+        <v>2467</v>
       </c>
       <c r="P4" s="27" t="s">
         <v>232</v>
       </c>
       <c r="Q4" s="27" t="s">
-        <v>2477</v>
+        <v>2476</v>
       </c>
       <c r="R4" s="27" t="s">
         <v>885</v>
       </c>
       <c r="S4" s="27" t="s">
-        <v>2470</v>
+        <v>2469</v>
       </c>
       <c r="T4" s="27" t="s">
         <v>543</v>
       </c>
       <c r="U4" s="27" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
       <c r="V4" s="27" t="s">
         <v>491</v>
       </c>
       <c r="W4" s="27" t="s">
-        <v>2472</v>
+        <v>2471</v>
       </c>
       <c r="X4" s="27"/>
       <c r="Y4" s="27"/>
@@ -22916,19 +22890,19 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="23" t="s">
+        <v>2478</v>
+      </c>
+      <c r="B5" s="23" t="s">
         <v>2479</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="C5" s="23" t="s">
         <v>2480</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>2481</v>
       </c>
       <c r="D5" s="23" t="s">
         <v>114</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>2482</v>
+        <v>2481</v>
       </c>
       <c r="F5" s="25">
         <v>31000.0</v>
@@ -22948,80 +22922,80 @@
         <v>113</v>
       </c>
       <c r="M5" s="23" t="s">
-        <v>2467</v>
+        <v>2466</v>
       </c>
       <c r="N5" s="27" t="s">
         <v>292</v>
       </c>
       <c r="O5" s="27" t="s">
+        <v>2482</v>
+      </c>
+      <c r="P5" s="27" t="s">
         <v>2483</v>
       </c>
-      <c r="P5" s="27" t="s">
+      <c r="Q5" s="27" t="s">
         <v>2484</v>
-      </c>
-      <c r="Q5" s="27" t="s">
-        <v>2485</v>
       </c>
       <c r="R5" s="27" t="s">
         <v>881</v>
       </c>
       <c r="S5" s="27" t="s">
+        <v>2485</v>
+      </c>
+      <c r="T5" s="27" t="s">
         <v>2486</v>
       </c>
-      <c r="T5" s="27" t="s">
+      <c r="U5" s="27" t="s">
         <v>2487</v>
       </c>
-      <c r="U5" s="27" t="s">
+      <c r="V5" s="27" t="s">
         <v>2488</v>
       </c>
-      <c r="V5" s="27" t="s">
+      <c r="W5" s="27" t="s">
         <v>2489</v>
       </c>
-      <c r="W5" s="27" t="s">
+      <c r="X5" s="27" t="s">
         <v>2490</v>
       </c>
-      <c r="X5" s="27" t="s">
+      <c r="Y5" s="27" t="s">
         <v>2491</v>
       </c>
-      <c r="Y5" s="27" t="s">
+      <c r="Z5" s="27" t="s">
         <v>2492</v>
       </c>
-      <c r="Z5" s="27" t="s">
+      <c r="AA5" s="27" t="s">
         <v>2493</v>
-      </c>
-      <c r="AA5" s="27" t="s">
-        <v>2494</v>
       </c>
       <c r="AB5" s="27" t="s">
         <v>885</v>
       </c>
       <c r="AC5" s="27" t="s">
-        <v>2495</v>
+        <v>2494</v>
       </c>
       <c r="AD5" s="27" t="s">
         <v>473</v>
       </c>
       <c r="AE5" s="27" t="s">
-        <v>2496</v>
+        <v>2495</v>
       </c>
       <c r="AF5" s="27"/>
       <c r="AG5" s="27"/>
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="23" t="s">
+        <v>2496</v>
+      </c>
+      <c r="B6" s="23" t="s">
         <v>2497</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="C6" s="23" t="s">
         <v>2498</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>2499</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>114</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>2482</v>
+        <v>2481</v>
       </c>
       <c r="F6" s="25">
         <v>17000.0</v>
@@ -23041,80 +23015,80 @@
         <v>113</v>
       </c>
       <c r="M6" s="23" t="s">
-        <v>2467</v>
+        <v>2466</v>
       </c>
       <c r="N6" s="27" t="s">
         <v>292</v>
       </c>
       <c r="O6" s="27" t="s">
+        <v>2482</v>
+      </c>
+      <c r="P6" s="27" t="s">
         <v>2483</v>
       </c>
-      <c r="P6" s="27" t="s">
+      <c r="Q6" s="27" t="s">
         <v>2484</v>
-      </c>
-      <c r="Q6" s="27" t="s">
-        <v>2485</v>
       </c>
       <c r="R6" s="27" t="s">
         <v>881</v>
       </c>
       <c r="S6" s="27" t="s">
+        <v>2499</v>
+      </c>
+      <c r="T6" s="27" t="s">
+        <v>2486</v>
+      </c>
+      <c r="U6" s="27" t="s">
         <v>2500</v>
       </c>
-      <c r="T6" s="27" t="s">
-        <v>2487</v>
-      </c>
-      <c r="U6" s="27" t="s">
+      <c r="V6" s="27" t="s">
+        <v>2488</v>
+      </c>
+      <c r="W6" s="27" t="s">
         <v>2501</v>
       </c>
-      <c r="V6" s="27" t="s">
-        <v>2489</v>
-      </c>
-      <c r="W6" s="27" t="s">
+      <c r="X6" s="27" t="s">
+        <v>2490</v>
+      </c>
+      <c r="Y6" s="27" t="s">
         <v>2502</v>
       </c>
-      <c r="X6" s="27" t="s">
-        <v>2491</v>
-      </c>
-      <c r="Y6" s="27" t="s">
+      <c r="Z6" s="27" t="s">
+        <v>2492</v>
+      </c>
+      <c r="AA6" s="27" t="s">
         <v>2503</v>
-      </c>
-      <c r="Z6" s="27" t="s">
-        <v>2493</v>
-      </c>
-      <c r="AA6" s="27" t="s">
-        <v>2504</v>
       </c>
       <c r="AB6" s="27" t="s">
         <v>885</v>
       </c>
       <c r="AC6" s="27" t="s">
-        <v>2495</v>
+        <v>2494</v>
       </c>
       <c r="AD6" s="27" t="s">
+        <v>2504</v>
+      </c>
+      <c r="AE6" s="27" t="s">
         <v>2505</v>
-      </c>
-      <c r="AE6" s="27" t="s">
-        <v>2506</v>
       </c>
       <c r="AF6" s="27"/>
       <c r="AG6" s="27"/>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="27" t="s">
+        <v>2506</v>
+      </c>
+      <c r="B7" s="27" t="s">
         <v>2507</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="C7" s="27" t="s">
         <v>2508</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>2509</v>
       </c>
       <c r="D7" s="27" t="s">
         <v>138</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="F7" s="24">
         <v>3395.0</v>
@@ -23140,31 +23114,31 @@
         <v>292</v>
       </c>
       <c r="O7" s="27" t="s">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="P7" s="27" t="s">
         <v>85</v>
       </c>
       <c r="Q7" s="27" t="s">
+        <v>2511</v>
+      </c>
+      <c r="R7" s="27" t="s">
+        <v>1646</v>
+      </c>
+      <c r="S7" s="27" t="s">
         <v>2512</v>
-      </c>
-      <c r="R7" s="27" t="s">
-        <v>1647</v>
-      </c>
-      <c r="S7" s="27" t="s">
-        <v>2513</v>
       </c>
       <c r="T7" s="27" t="s">
         <v>885</v>
       </c>
       <c r="U7" s="27" t="s">
+        <v>2513</v>
+      </c>
+      <c r="V7" s="27" t="s">
+        <v>2143</v>
+      </c>
+      <c r="W7" s="27" t="s">
         <v>2514</v>
-      </c>
-      <c r="V7" s="27" t="s">
-        <v>2144</v>
-      </c>
-      <c r="W7" s="27" t="s">
-        <v>2515</v>
       </c>
       <c r="X7" s="27"/>
       <c r="Y7" s="27"/>
@@ -23178,20 +23152,20 @@
       <c r="AG7" s="23"/>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="53" t="s">
+      <c r="A8" s="52" t="s">
+        <v>2515</v>
+      </c>
+      <c r="B8" s="27" t="s">
         <v>2516</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="C8" s="27" t="s">
         <v>2517</v>
-      </c>
-      <c r="C8" s="27" t="s">
-        <v>2518</v>
       </c>
       <c r="D8" s="27" t="s">
         <v>144</v>
       </c>
       <c r="E8" s="27" t="s">
-        <v>2519</v>
+        <v>2518</v>
       </c>
       <c r="F8" s="24">
         <v>3195.0</v>
@@ -23214,13 +23188,13 @@
         <v>70</v>
       </c>
       <c r="N8" s="27" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="O8" s="27" t="s">
-        <v>2520</v>
+        <v>2519</v>
       </c>
       <c r="P8" s="27" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
       <c r="Q8" s="27" t="s">
         <v>403</v>
@@ -23229,7 +23203,7 @@
         <v>294</v>
       </c>
       <c r="S8" s="27" t="s">
-        <v>2521</v>
+        <v>2520</v>
       </c>
       <c r="T8" s="27" t="s">
         <v>204</v>
@@ -23241,25 +23215,25 @@
         <v>498</v>
       </c>
       <c r="W8" s="27" t="s">
+        <v>2521</v>
+      </c>
+      <c r="X8" s="27" t="s">
         <v>2522</v>
       </c>
-      <c r="X8" s="27" t="s">
+      <c r="Y8" s="27" t="s">
         <v>2523</v>
-      </c>
-      <c r="Y8" s="27" t="s">
-        <v>2524</v>
       </c>
       <c r="Z8" s="27" t="s">
         <v>208</v>
       </c>
       <c r="AA8" s="27" t="s">
+        <v>2524</v>
+      </c>
+      <c r="AB8" s="27" t="s">
         <v>2525</v>
       </c>
-      <c r="AB8" s="27" t="s">
+      <c r="AC8" s="27" t="s">
         <v>2526</v>
-      </c>
-      <c r="AC8" s="27" t="s">
-        <v>2527</v>
       </c>
       <c r="AD8" s="27"/>
       <c r="AE8" s="27"/>
@@ -23267,20 +23241,20 @@
       <c r="AG8" s="27"/>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="53" t="s">
+      <c r="A9" s="52" t="s">
+        <v>2527</v>
+      </c>
+      <c r="B9" s="27" t="s">
         <v>2528</v>
       </c>
-      <c r="B9" s="27" t="s">
+      <c r="C9" s="27" t="s">
         <v>2529</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>2530</v>
       </c>
       <c r="D9" s="27" t="s">
         <v>144</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>2531</v>
+        <v>2530</v>
       </c>
       <c r="F9" s="24">
         <v>2895.0</v>
@@ -23303,13 +23277,13 @@
         <v>70</v>
       </c>
       <c r="N9" s="27" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="O9" s="27" t="s">
-        <v>2520</v>
+        <v>2519</v>
       </c>
       <c r="P9" s="27" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
       <c r="Q9" s="27" t="s">
         <v>403</v>
@@ -23318,7 +23292,7 @@
         <v>294</v>
       </c>
       <c r="S9" s="27" t="s">
-        <v>2532</v>
+        <v>2531</v>
       </c>
       <c r="T9" s="27" t="s">
         <v>204</v>
@@ -23330,25 +23304,25 @@
         <v>498</v>
       </c>
       <c r="W9" s="27" t="s">
-        <v>2522</v>
+        <v>2521</v>
       </c>
       <c r="X9" s="27" t="s">
         <v>531</v>
       </c>
       <c r="Y9" s="27" t="s">
-        <v>2533</v>
+        <v>2532</v>
       </c>
       <c r="Z9" s="27" t="s">
         <v>208</v>
       </c>
       <c r="AA9" s="27" t="s">
-        <v>2534</v>
+        <v>2533</v>
       </c>
       <c r="AB9" s="27" t="s">
+        <v>2525</v>
+      </c>
+      <c r="AC9" s="27" t="s">
         <v>2526</v>
-      </c>
-      <c r="AC9" s="27" t="s">
-        <v>2527</v>
       </c>
       <c r="AD9" s="27"/>
       <c r="AE9" s="27"/>
@@ -23356,20 +23330,20 @@
       <c r="AG9" s="27"/>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="53" t="s">
+      <c r="A10" s="52" t="s">
+        <v>2534</v>
+      </c>
+      <c r="B10" s="27" t="s">
         <v>2535</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="C10" s="27" t="s">
         <v>2536</v>
-      </c>
-      <c r="C10" s="27" t="s">
-        <v>2537</v>
       </c>
       <c r="D10" s="27" t="s">
         <v>84</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>2538</v>
+        <v>2537</v>
       </c>
       <c r="F10" s="24">
         <v>5995.0</v>
@@ -23395,55 +23369,55 @@
         <v>292</v>
       </c>
       <c r="O10" s="27" t="s">
+        <v>2538</v>
+      </c>
+      <c r="P10" s="27" t="s">
+        <v>2102</v>
+      </c>
+      <c r="Q10" s="27" t="s">
         <v>2539</v>
       </c>
-      <c r="P10" s="27" t="s">
-        <v>2103</v>
-      </c>
-      <c r="Q10" s="27" t="s">
-        <v>2540</v>
-      </c>
       <c r="R10" s="27" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
       <c r="S10" s="27" t="s">
         <v>375</v>
       </c>
       <c r="T10" s="27" t="s">
+        <v>2540</v>
+      </c>
+      <c r="U10" s="27" t="s">
         <v>2541</v>
       </c>
-      <c r="U10" s="27" t="s">
+      <c r="V10" s="27" t="s">
+        <v>1735</v>
+      </c>
+      <c r="W10" s="27" t="s">
         <v>2542</v>
-      </c>
-      <c r="V10" s="27" t="s">
-        <v>1736</v>
-      </c>
-      <c r="W10" s="27" t="s">
-        <v>2543</v>
       </c>
       <c r="X10" s="27" t="s">
         <v>232</v>
       </c>
       <c r="Y10" s="27" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
       <c r="Z10" s="27" t="s">
         <v>341</v>
       </c>
       <c r="AA10" s="27" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="AB10" s="27" t="s">
         <v>206</v>
       </c>
       <c r="AC10" s="27" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="AD10" s="27" t="s">
         <v>781</v>
       </c>
       <c r="AE10" s="27" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
       <c r="AF10" s="27" t="s">
         <v>204</v>
@@ -23453,20 +23427,20 @@
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="53" t="s">
+      <c r="A11" s="52" t="s">
+        <v>2547</v>
+      </c>
+      <c r="B11" s="27" t="s">
         <v>2548</v>
       </c>
-      <c r="B11" s="27" t="s">
+      <c r="C11" s="27" t="s">
         <v>2549</v>
-      </c>
-      <c r="C11" s="27" t="s">
-        <v>2550</v>
       </c>
       <c r="D11" s="27" t="s">
         <v>84</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>2551</v>
+        <v>2550</v>
       </c>
       <c r="F11" s="24">
         <v>3995.0</v>
@@ -23492,74 +23466,74 @@
         <v>292</v>
       </c>
       <c r="O11" s="27" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
       <c r="P11" s="27" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="Q11" s="27" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
       <c r="R11" s="27" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
       <c r="S11" s="27" t="s">
         <v>394</v>
       </c>
       <c r="T11" s="27" t="s">
+        <v>2540</v>
+      </c>
+      <c r="U11" s="27" t="s">
         <v>2541</v>
       </c>
-      <c r="U11" s="27" t="s">
-        <v>2542</v>
-      </c>
       <c r="V11" s="27" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="W11" s="27" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
       <c r="X11" s="27" t="s">
         <v>232</v>
       </c>
       <c r="Y11" s="27" t="s">
-        <v>2554</v>
+        <v>2553</v>
       </c>
       <c r="Z11" s="27" t="s">
         <v>341</v>
       </c>
       <c r="AA11" s="27" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="AB11" s="27" t="s">
         <v>206</v>
       </c>
       <c r="AC11" s="27" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="AD11" s="27" t="s">
         <v>781</v>
       </c>
       <c r="AE11" s="27" t="s">
-        <v>2556</v>
+        <v>2555</v>
       </c>
       <c r="AF11" s="23"/>
       <c r="AG11" s="23"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="52" t="s">
+        <v>2556</v>
+      </c>
+      <c r="B12" s="27" t="s">
         <v>2557</v>
       </c>
-      <c r="B12" s="27" t="s">
+      <c r="C12" s="27" t="s">
         <v>2558</v>
-      </c>
-      <c r="C12" s="27" t="s">
-        <v>2559</v>
       </c>
       <c r="D12" s="27" t="s">
         <v>84</v>
       </c>
       <c r="E12" s="27" t="s">
-        <v>2560</v>
+        <v>2559</v>
       </c>
       <c r="F12" s="24">
         <v>5495.0</v>
@@ -23585,22 +23559,22 @@
         <v>292</v>
       </c>
       <c r="O12" s="27" t="s">
-        <v>2561</v>
+        <v>2560</v>
       </c>
       <c r="P12" s="27" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="Q12" s="27" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
       <c r="R12" s="27" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
       <c r="S12" s="27" t="s">
         <v>258</v>
       </c>
       <c r="T12" s="27" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="U12" s="27" t="s">
         <v>1489</v>
@@ -23609,54 +23583,54 @@
         <v>498</v>
       </c>
       <c r="W12" s="27" t="s">
-        <v>2562</v>
+        <v>2561</v>
       </c>
       <c r="X12" s="27" t="s">
         <v>232</v>
       </c>
       <c r="Y12" s="27" t="s">
-        <v>2563</v>
+        <v>2562</v>
       </c>
       <c r="Z12" s="27" t="s">
         <v>341</v>
       </c>
       <c r="AA12" s="27" t="s">
-        <v>2564</v>
+        <v>2563</v>
       </c>
       <c r="AB12" s="27" t="s">
         <v>294</v>
       </c>
       <c r="AC12" s="27" t="s">
-        <v>2565</v>
+        <v>2564</v>
       </c>
       <c r="AD12" s="27" t="s">
         <v>885</v>
       </c>
       <c r="AE12" s="27" t="s">
-        <v>2566</v>
+        <v>2565</v>
       </c>
       <c r="AF12" s="27" t="s">
         <v>781</v>
       </c>
       <c r="AG12" s="27" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="52" t="s">
+        <v>2567</v>
+      </c>
+      <c r="B13" s="27" t="s">
         <v>2568</v>
       </c>
-      <c r="B13" s="27" t="s">
+      <c r="C13" s="27" t="s">
         <v>2569</v>
-      </c>
-      <c r="C13" s="27" t="s">
-        <v>2570</v>
       </c>
       <c r="D13" s="27" t="s">
         <v>84</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>2571</v>
+        <v>2570</v>
       </c>
       <c r="F13" s="24">
         <v>2695.0</v>
@@ -23679,52 +23653,52 @@
         <v>70</v>
       </c>
       <c r="N13" s="27" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="O13" s="27" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
       <c r="P13" s="27" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
       <c r="Q13" s="27" t="s">
         <v>403</v>
       </c>
       <c r="R13" s="27" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="S13" s="27" t="s">
         <v>1489</v>
       </c>
       <c r="T13" s="27" t="s">
-        <v>2541</v>
+        <v>2540</v>
       </c>
       <c r="U13" s="27" t="s">
-        <v>2572</v>
+        <v>2571</v>
       </c>
       <c r="V13" s="27" t="s">
         <v>498</v>
       </c>
       <c r="W13" s="27" t="s">
-        <v>2573</v>
+        <v>2572</v>
       </c>
       <c r="X13" s="27" t="s">
         <v>232</v>
       </c>
       <c r="Y13" s="27" t="s">
-        <v>2574</v>
+        <v>2573</v>
       </c>
       <c r="Z13" s="27" t="s">
         <v>341</v>
       </c>
       <c r="AA13" s="27" t="s">
-        <v>2575</v>
+        <v>2574</v>
       </c>
       <c r="AB13" s="27" t="s">
         <v>781</v>
       </c>
       <c r="AC13" s="27" t="s">
-        <v>2576</v>
+        <v>2575</v>
       </c>
       <c r="AD13" s="27" t="s">
         <v>308</v>
@@ -23736,20 +23710,20 @@
       <c r="AG13" s="27"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="53" t="s">
+      <c r="A14" s="52" t="s">
+        <v>2576</v>
+      </c>
+      <c r="B14" s="27" t="s">
         <v>2577</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="C14" s="27" t="s">
         <v>2578</v>
-      </c>
-      <c r="C14" s="27" t="s">
-        <v>2579</v>
       </c>
       <c r="D14" s="27" t="s">
         <v>84</v>
       </c>
       <c r="E14" s="27" t="s">
-        <v>2580</v>
+        <v>2579</v>
       </c>
       <c r="F14" s="24">
         <v>7995.0</v>
@@ -23775,74 +23749,74 @@
         <v>292</v>
       </c>
       <c r="O14" s="27" t="s">
-        <v>2581</v>
+        <v>2580</v>
       </c>
       <c r="P14" s="27" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="Q14" s="27" t="s">
-        <v>2520</v>
+        <v>2519</v>
       </c>
       <c r="R14" s="27" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
       <c r="S14" s="27" t="s">
         <v>403</v>
       </c>
       <c r="T14" s="27" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="U14" s="27" t="s">
         <v>1489</v>
       </c>
       <c r="V14" s="27" t="s">
-        <v>2541</v>
+        <v>2540</v>
       </c>
       <c r="W14" s="27" t="s">
-        <v>2572</v>
+        <v>2571</v>
       </c>
       <c r="X14" s="27" t="s">
         <v>498</v>
       </c>
       <c r="Y14" s="27" t="s">
-        <v>2582</v>
+        <v>2581</v>
       </c>
       <c r="Z14" s="27" t="s">
         <v>232</v>
       </c>
       <c r="AA14" s="27" t="s">
-        <v>2583</v>
+        <v>2582</v>
       </c>
       <c r="AB14" s="27" t="s">
         <v>206</v>
       </c>
       <c r="AC14" s="27" t="s">
-        <v>2584</v>
+        <v>2583</v>
       </c>
       <c r="AD14" s="27" t="s">
         <v>885</v>
       </c>
       <c r="AE14" s="27" t="s">
-        <v>2585</v>
+        <v>2584</v>
       </c>
       <c r="AF14" s="27"/>
       <c r="AG14" s="27"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="53" t="s">
+      <c r="A15" s="52" t="s">
+        <v>2585</v>
+      </c>
+      <c r="B15" s="27" t="s">
         <v>2586</v>
       </c>
-      <c r="B15" s="27" t="s">
+      <c r="C15" s="27" t="s">
         <v>2587</v>
-      </c>
-      <c r="C15" s="27" t="s">
-        <v>2588</v>
       </c>
       <c r="D15" s="27" t="s">
         <v>84</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>2589</v>
+        <v>2588</v>
       </c>
       <c r="F15" s="24">
         <v>1795.0</v>
@@ -23865,28 +23839,28 @@
         <v>85</v>
       </c>
       <c r="N15" s="27" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="O15" s="27" t="s">
+        <v>2589</v>
+      </c>
+      <c r="P15" s="27" t="s">
         <v>2590</v>
       </c>
-      <c r="P15" s="27" t="s">
+      <c r="Q15" s="27" t="s">
         <v>2591</v>
       </c>
-      <c r="Q15" s="27" t="s">
+      <c r="R15" s="27" t="s">
+        <v>2483</v>
+      </c>
+      <c r="S15" s="27" t="s">
         <v>2592</v>
-      </c>
-      <c r="R15" s="27" t="s">
-        <v>2484</v>
-      </c>
-      <c r="S15" s="27" t="s">
-        <v>2593</v>
       </c>
       <c r="T15" s="27" t="s">
         <v>900</v>
       </c>
       <c r="U15" s="27" t="s">
-        <v>2594</v>
+        <v>2593</v>
       </c>
       <c r="V15" s="27"/>
       <c r="W15" s="27"/>
@@ -41945,7 +41919,9 @@
       <c r="U19" s="27" t="s">
         <v>1222</v>
       </c>
-      <c r="V19" s="52"/>
+      <c r="V19" s="48" t="s">
+        <v>1345</v>
+      </c>
       <c r="W19" s="27" t="s">
         <v>1250</v>
       </c>
@@ -42125,45 +42101,43 @@
         <v>1382</v>
       </c>
       <c r="U21" s="27" t="s">
-        <v>1222</v>
-      </c>
-      <c r="V21" s="52"/>
+        <v>1383</v>
+      </c>
+      <c r="V21" s="27" t="s">
+        <v>1384</v>
+      </c>
       <c r="W21" s="27" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="X21" s="27" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="Y21" s="27" t="s">
-        <v>1385</v>
+        <v>1250</v>
       </c>
       <c r="Z21" s="27" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="AA21" s="27" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="AB21" s="27" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="AC21" s="27" t="s">
-        <v>1252</v>
+        <v>891</v>
       </c>
       <c r="AD21" s="27" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="AE21" s="27" t="s">
-        <v>891</v>
+        <v>308</v>
       </c>
       <c r="AF21" s="27" t="s">
-        <v>1389</v>
-      </c>
-      <c r="AG21" s="27" t="s">
-        <v>308</v>
-      </c>
-      <c r="AH21" s="27" t="s">
         <v>1390</v>
       </c>
+      <c r="AG21" s="27"/>
+      <c r="AH21" s="27"/>
       <c r="AI21" s="27"/>
       <c r="AJ21" s="27"/>
     </row>
@@ -42225,45 +42199,43 @@
         <v>1398</v>
       </c>
       <c r="U22" s="27" t="s">
-        <v>1222</v>
-      </c>
-      <c r="V22" s="52"/>
+        <v>1383</v>
+      </c>
+      <c r="V22" s="27" t="s">
+        <v>1399</v>
+      </c>
       <c r="W22" s="27" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="X22" s="27" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="Y22" s="27" t="s">
-        <v>1385</v>
+        <v>1252</v>
       </c>
       <c r="Z22" s="27" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="AA22" s="27" t="s">
-        <v>1252</v>
+        <v>1402</v>
       </c>
       <c r="AB22" s="27" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="AC22" s="27" t="s">
-        <v>1402</v>
+        <v>891</v>
       </c>
       <c r="AD22" s="27" t="s">
-        <v>1403</v>
+        <v>1389</v>
       </c>
       <c r="AE22" s="27" t="s">
-        <v>891</v>
+        <v>308</v>
       </c>
       <c r="AF22" s="27" t="s">
-        <v>1389</v>
-      </c>
-      <c r="AG22" s="27" t="s">
-        <v>308</v>
-      </c>
-      <c r="AH22" s="27" t="s">
         <v>1390</v>
       </c>
+      <c r="AG22" s="27"/>
+      <c r="AH22" s="27"/>
       <c r="AI22" s="27"/>
       <c r="AJ22" s="27"/>
     </row>
@@ -42325,39 +42297,37 @@
         <v>1382</v>
       </c>
       <c r="U23" s="27" t="s">
-        <v>1222</v>
-      </c>
-      <c r="V23" s="52"/>
+        <v>1385</v>
+      </c>
+      <c r="V23" s="27" t="s">
+        <v>1386</v>
+      </c>
       <c r="W23" s="27" t="s">
-        <v>1385</v>
+        <v>1250</v>
       </c>
       <c r="X23" s="27" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="Y23" s="27" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="Z23" s="27" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="AA23" s="27" t="s">
-        <v>1252</v>
+        <v>891</v>
       </c>
       <c r="AB23" s="27" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="AC23" s="27" t="s">
-        <v>891</v>
+        <v>308</v>
       </c>
       <c r="AD23" s="27" t="s">
-        <v>1389</v>
-      </c>
-      <c r="AE23" s="27" t="s">
-        <v>308</v>
-      </c>
-      <c r="AF23" s="27" t="s">
         <v>1390</v>
       </c>
+      <c r="AE23" s="23"/>
+      <c r="AF23" s="23"/>
       <c r="AG23" s="23"/>
       <c r="AH23" s="23"/>
       <c r="AI23" s="23"/>
@@ -42421,45 +42391,43 @@
         <v>1382</v>
       </c>
       <c r="U24" s="27" t="s">
-        <v>1222</v>
-      </c>
-      <c r="V24" s="52"/>
+        <v>1383</v>
+      </c>
+      <c r="V24" s="27" t="s">
+        <v>1415</v>
+      </c>
       <c r="W24" s="27" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="X24" s="27" t="s">
-        <v>1415</v>
+        <v>1386</v>
       </c>
       <c r="Y24" s="27" t="s">
-        <v>1385</v>
+        <v>1250</v>
       </c>
       <c r="Z24" s="27" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="AA24" s="27" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="AB24" s="27" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="AC24" s="27" t="s">
-        <v>1252</v>
+        <v>891</v>
       </c>
       <c r="AD24" s="27" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="AE24" s="27" t="s">
-        <v>891</v>
+        <v>308</v>
       </c>
       <c r="AF24" s="27" t="s">
-        <v>1389</v>
-      </c>
-      <c r="AG24" s="27" t="s">
-        <v>308</v>
-      </c>
-      <c r="AH24" s="27" t="s">
         <v>1390</v>
       </c>
+      <c r="AG24" s="27"/>
+      <c r="AH24" s="27"/>
       <c r="AI24" s="27"/>
       <c r="AJ24" s="27"/>
     </row>
@@ -42521,33 +42489,31 @@
         <v>1423</v>
       </c>
       <c r="U25" s="27" t="s">
-        <v>1222</v>
-      </c>
-      <c r="V25" s="52"/>
+        <v>1383</v>
+      </c>
+      <c r="V25" s="27" t="s">
+        <v>1399</v>
+      </c>
       <c r="W25" s="27" t="s">
-        <v>1383</v>
+        <v>1293</v>
       </c>
       <c r="X25" s="27" t="s">
-        <v>1399</v>
+        <v>1424</v>
       </c>
       <c r="Y25" s="27" t="s">
-        <v>1293</v>
+        <v>1425</v>
       </c>
       <c r="Z25" s="27" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="AA25" s="27" t="s">
-        <v>1425</v>
+        <v>1366</v>
       </c>
       <c r="AB25" s="27" t="s">
-        <v>1426</v>
-      </c>
-      <c r="AC25" s="27" t="s">
-        <v>1366</v>
-      </c>
-      <c r="AD25" s="27" t="s">
         <v>1427</v>
       </c>
+      <c r="AC25" s="23"/>
+      <c r="AD25" s="23"/>
       <c r="AE25" s="23"/>
       <c r="AF25" s="23"/>
       <c r="AG25" s="23"/>
@@ -42613,33 +42579,31 @@
         <v>1423</v>
       </c>
       <c r="U26" s="27" t="s">
-        <v>1222</v>
-      </c>
-      <c r="V26" s="52"/>
+        <v>1383</v>
+      </c>
+      <c r="V26" s="27" t="s">
+        <v>1399</v>
+      </c>
       <c r="W26" s="27" t="s">
-        <v>1383</v>
+        <v>1425</v>
       </c>
       <c r="X26" s="27" t="s">
-        <v>1399</v>
+        <v>1426</v>
       </c>
       <c r="Y26" s="27" t="s">
-        <v>1425</v>
+        <v>473</v>
       </c>
       <c r="Z26" s="27" t="s">
-        <v>1426</v>
+        <v>1433</v>
       </c>
       <c r="AA26" s="27" t="s">
-        <v>473</v>
+        <v>1434</v>
       </c>
       <c r="AB26" s="27" t="s">
-        <v>1433</v>
-      </c>
-      <c r="AC26" s="27" t="s">
-        <v>1434</v>
-      </c>
-      <c r="AD26" s="27" t="s">
         <v>1435</v>
       </c>
+      <c r="AC26" s="23"/>
+      <c r="AD26" s="23"/>
       <c r="AE26" s="23"/>
       <c r="AF26" s="23"/>
       <c r="AG26" s="23"/>
@@ -43143,45 +43107,43 @@
         <v>1476</v>
       </c>
       <c r="U32" s="27" t="s">
-        <v>1222</v>
-      </c>
-      <c r="V32" s="52"/>
+        <v>1383</v>
+      </c>
+      <c r="V32" s="27" t="s">
+        <v>1399</v>
+      </c>
       <c r="W32" s="27" t="s">
-        <v>1383</v>
+        <v>1293</v>
       </c>
       <c r="X32" s="27" t="s">
-        <v>1399</v>
+        <v>1477</v>
       </c>
       <c r="Y32" s="27" t="s">
-        <v>1293</v>
+        <v>1250</v>
       </c>
       <c r="Z32" s="27" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="AA32" s="27" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="AB32" s="27" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="AC32" s="27" t="s">
-        <v>1252</v>
+        <v>473</v>
       </c>
       <c r="AD32" s="27" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="AE32" s="27" t="s">
-        <v>473</v>
+        <v>891</v>
       </c>
       <c r="AF32" s="27" t="s">
-        <v>1480</v>
-      </c>
-      <c r="AG32" s="27" t="s">
-        <v>891</v>
-      </c>
-      <c r="AH32" s="27" t="s">
         <v>1481</v>
       </c>
+      <c r="AG32" s="27"/>
+      <c r="AH32" s="27"/>
       <c r="AI32" s="27"/>
       <c r="AJ32" s="27"/>
     </row>
@@ -43243,35 +43205,33 @@
         <v>1476</v>
       </c>
       <c r="U33" s="27" t="s">
-        <v>1222</v>
-      </c>
-      <c r="V33" s="52"/>
+        <v>1383</v>
+      </c>
+      <c r="V33" s="27" t="s">
+        <v>1489</v>
+      </c>
       <c r="W33" s="27" t="s">
-        <v>1383</v>
+        <v>308</v>
       </c>
       <c r="X33" s="27" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="Y33" s="27" t="s">
-        <v>308</v>
+        <v>1491</v>
       </c>
       <c r="Z33" s="27" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="AA33" s="27" t="s">
-        <v>1491</v>
+        <v>300</v>
       </c>
       <c r="AB33" s="27" t="s">
-        <v>1492</v>
-      </c>
-      <c r="AC33" s="27" t="s">
-        <v>300</v>
-      </c>
-      <c r="AD33" s="27" t="s">
         <v>1493</v>
       </c>
-      <c r="AE33" s="27"/>
-      <c r="AF33" s="27"/>
+      <c r="AC33" s="27"/>
+      <c r="AD33" s="27"/>
+      <c r="AE33" s="23"/>
+      <c r="AF33" s="23"/>
       <c r="AG33" s="23"/>
       <c r="AH33" s="23"/>
       <c r="AI33" s="23"/>
@@ -43335,45 +43295,43 @@
         <v>1500</v>
       </c>
       <c r="U34" s="27" t="s">
-        <v>1222</v>
-      </c>
-      <c r="V34" s="52"/>
+        <v>1501</v>
+      </c>
+      <c r="V34" s="27" t="s">
+        <v>1502</v>
+      </c>
       <c r="W34" s="27" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="X34" s="27" t="s">
-        <v>1502</v>
+        <v>1504</v>
       </c>
       <c r="Y34" s="27" t="s">
-        <v>1503</v>
+        <v>1252</v>
       </c>
       <c r="Z34" s="27" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="AA34" s="27" t="s">
-        <v>1252</v>
+        <v>1506</v>
       </c>
       <c r="AB34" s="27" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="AC34" s="27" t="s">
-        <v>1506</v>
+        <v>900</v>
       </c>
       <c r="AD34" s="27" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="AE34" s="27" t="s">
-        <v>900</v>
+        <v>891</v>
       </c>
       <c r="AF34" s="27" t="s">
-        <v>1508</v>
-      </c>
-      <c r="AG34" s="27" t="s">
-        <v>891</v>
-      </c>
-      <c r="AH34" s="27" t="s">
         <v>1509</v>
       </c>
+      <c r="AG34" s="27"/>
+      <c r="AH34" s="27"/>
       <c r="AI34" s="27"/>
       <c r="AJ34" s="27"/>
     </row>
@@ -43435,35 +43393,33 @@
         <v>1515</v>
       </c>
       <c r="U35" s="27" t="s">
-        <v>1222</v>
-      </c>
-      <c r="V35" s="52"/>
+        <v>900</v>
+      </c>
+      <c r="V35" s="27" t="s">
+        <v>901</v>
+      </c>
       <c r="W35" s="27" t="s">
-        <v>900</v>
+        <v>1293</v>
       </c>
       <c r="X35" s="27" t="s">
-        <v>901</v>
+        <v>1424</v>
       </c>
       <c r="Y35" s="27" t="s">
-        <v>1293</v>
+        <v>491</v>
       </c>
       <c r="Z35" s="27" t="s">
-        <v>1424</v>
+        <v>1516</v>
       </c>
       <c r="AA35" s="27" t="s">
-        <v>491</v>
+        <v>1366</v>
       </c>
       <c r="AB35" s="27" t="s">
-        <v>1516</v>
-      </c>
-      <c r="AC35" s="27" t="s">
-        <v>1366</v>
-      </c>
-      <c r="AD35" s="27" t="s">
         <v>1517</v>
       </c>
-      <c r="AE35" s="27"/>
-      <c r="AF35" s="27"/>
+      <c r="AC35" s="27"/>
+      <c r="AD35" s="27"/>
+      <c r="AE35" s="23"/>
+      <c r="AF35" s="23"/>
       <c r="AG35" s="23"/>
       <c r="AH35" s="23"/>
       <c r="AI35" s="23"/>
@@ -43527,39 +43483,37 @@
         <v>1515</v>
       </c>
       <c r="U36" s="27" t="s">
-        <v>1222</v>
-      </c>
-      <c r="V36" s="52"/>
+        <v>900</v>
+      </c>
+      <c r="V36" s="27" t="s">
+        <v>901</v>
+      </c>
       <c r="W36" s="27" t="s">
-        <v>900</v>
+        <v>491</v>
       </c>
       <c r="X36" s="27" t="s">
-        <v>901</v>
+        <v>1516</v>
       </c>
       <c r="Y36" s="27" t="s">
-        <v>491</v>
+        <v>1506</v>
       </c>
       <c r="Z36" s="27" t="s">
-        <v>1516</v>
+        <v>1524</v>
       </c>
       <c r="AA36" s="27" t="s">
-        <v>1506</v>
+        <v>501</v>
       </c>
       <c r="AB36" s="27" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="AC36" s="27" t="s">
-        <v>501</v>
+        <v>341</v>
       </c>
       <c r="AD36" s="27" t="s">
-        <v>1525</v>
-      </c>
-      <c r="AE36" s="27" t="s">
-        <v>341</v>
-      </c>
-      <c r="AF36" s="27" t="s">
         <v>1526</v>
       </c>
+      <c r="AE36" s="23"/>
+      <c r="AF36" s="23"/>
       <c r="AG36" s="23"/>
       <c r="AH36" s="23"/>
       <c r="AI36" s="23"/>
@@ -43623,21 +43577,19 @@
         <v>1533</v>
       </c>
       <c r="U37" s="27" t="s">
-        <v>1222</v>
-      </c>
-      <c r="V37" s="52"/>
+        <v>1534</v>
+      </c>
+      <c r="V37" s="27" t="s">
+        <v>394</v>
+      </c>
       <c r="W37" s="27" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="X37" s="27" t="s">
-        <v>394</v>
-      </c>
-      <c r="Y37" s="27" t="s">
-        <v>1535</v>
-      </c>
-      <c r="Z37" s="27" t="s">
         <v>1536</v>
       </c>
+      <c r="Y37" s="23"/>
+      <c r="Z37" s="23"/>
       <c r="AA37" s="23"/>
       <c r="AB37" s="23"/>
       <c r="AC37" s="23"/>
@@ -43707,45 +43659,43 @@
         <v>1544</v>
       </c>
       <c r="U38" s="27" t="s">
-        <v>1222</v>
-      </c>
-      <c r="V38" s="52"/>
+        <v>1503</v>
+      </c>
+      <c r="V38" s="27" t="s">
+        <v>1545</v>
+      </c>
       <c r="W38" s="27" t="s">
-        <v>1503</v>
+        <v>1546</v>
       </c>
       <c r="X38" s="27" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
       <c r="Y38" s="27" t="s">
-        <v>1546</v>
+        <v>1535</v>
       </c>
       <c r="Z38" s="27" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="AA38" s="27" t="s">
-        <v>1535</v>
+        <v>1506</v>
       </c>
       <c r="AB38" s="27" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="AC38" s="27" t="s">
-        <v>1506</v>
+        <v>1550</v>
       </c>
       <c r="AD38" s="27" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="AE38" s="27" t="s">
-        <v>1550</v>
+        <v>206</v>
       </c>
       <c r="AF38" s="27" t="s">
-        <v>1551</v>
-      </c>
-      <c r="AG38" s="27" t="s">
-        <v>206</v>
-      </c>
-      <c r="AH38" s="27" t="s">
         <v>1552</v>
       </c>
+      <c r="AG38" s="27"/>
+      <c r="AH38" s="27"/>
       <c r="AI38" s="27"/>
       <c r="AJ38" s="27"/>
     </row>
@@ -44163,7 +44113,7 @@
       <c r="O43" s="46" t="s">
         <v>1591</v>
       </c>
-      <c r="P43" s="53" t="s">
+      <c r="P43" s="52" t="s">
         <v>1592</v>
       </c>
       <c r="Q43" s="27" t="s">
@@ -44257,7 +44207,7 @@
       <c r="O44" s="46" t="s">
         <v>1486</v>
       </c>
-      <c r="P44" s="53" t="s">
+      <c r="P44" s="52" t="s">
         <v>1598</v>
       </c>
       <c r="Q44" s="27" t="s">
@@ -44276,7 +44226,7 @@
         <v>1222</v>
       </c>
       <c r="V44" s="48" t="s">
-        <v>1599</v>
+        <v>1558</v>
       </c>
       <c r="W44" s="27" t="s">
         <v>1534</v>
@@ -44300,7 +44250,7 @@
         <v>1572</v>
       </c>
       <c r="AD44" s="27" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="AE44" s="23"/>
       <c r="AF44" s="23"/>
@@ -44311,13 +44261,13 @@
     </row>
     <row r="45" ht="14.25" customHeight="1">
       <c r="A45" s="23" t="s">
+        <v>1600</v>
+      </c>
+      <c r="B45" s="23" t="s">
         <v>1601</v>
       </c>
-      <c r="B45" s="23" t="s">
+      <c r="C45" s="27" t="s">
         <v>1602</v>
-      </c>
-      <c r="C45" s="27" t="s">
-        <v>1603</v>
       </c>
       <c r="D45" s="23" t="s">
         <v>114</v>
@@ -44364,13 +44314,13 @@
         <v>551</v>
       </c>
       <c r="T45" s="27" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="U45" s="27" t="s">
         <v>1222</v>
       </c>
       <c r="V45" s="48" t="s">
-        <v>1599</v>
+        <v>1558</v>
       </c>
       <c r="W45" s="27" t="s">
         <v>1534</v>
@@ -44382,7 +44332,7 @@
         <v>1535</v>
       </c>
       <c r="Z45" s="27" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="AA45" s="27" t="s">
         <v>1348</v>
@@ -44405,13 +44355,13 @@
     </row>
     <row r="46" ht="14.25" customHeight="1">
       <c r="A46" s="23" t="s">
+        <v>1605</v>
+      </c>
+      <c r="B46" s="23" t="s">
         <v>1606</v>
       </c>
-      <c r="B46" s="23" t="s">
+      <c r="C46" s="27" t="s">
         <v>1607</v>
-      </c>
-      <c r="C46" s="27" t="s">
-        <v>1608</v>
       </c>
       <c r="D46" s="23" t="s">
         <v>114</v>
@@ -44458,7 +44408,7 @@
         <v>551</v>
       </c>
       <c r="T46" s="27" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="U46" s="27" t="s">
         <v>1222</v>
@@ -44476,7 +44426,7 @@
         <v>1535</v>
       </c>
       <c r="Z46" s="27" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="AA46" s="27" t="s">
         <v>1348</v>
@@ -44488,7 +44438,7 @@
         <v>1572</v>
       </c>
       <c r="AD46" s="27" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="AE46" s="23"/>
       <c r="AF46" s="23"/>
@@ -44499,19 +44449,19 @@
     </row>
     <row r="47" ht="14.25" customHeight="1">
       <c r="A47" s="23" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B47" s="23" t="s">
         <v>1610</v>
       </c>
-      <c r="B47" s="23" t="s">
+      <c r="C47" s="23" t="s">
         <v>1611</v>
-      </c>
-      <c r="C47" s="23" t="s">
-        <v>1612</v>
       </c>
       <c r="D47" s="23" t="s">
         <v>114</v>
       </c>
       <c r="E47" s="23" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="F47" s="32">
         <v>14495.0</v>
@@ -44537,81 +44487,79 @@
         <v>76</v>
       </c>
       <c r="O47" s="51" t="s">
+        <v>1613</v>
+      </c>
+      <c r="P47" s="47" t="s">
         <v>1614</v>
-      </c>
-      <c r="P47" s="47" t="s">
-        <v>1615</v>
       </c>
       <c r="Q47" s="27" t="s">
         <v>208</v>
       </c>
       <c r="R47" s="27" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="S47" s="27" t="s">
         <v>551</v>
       </c>
       <c r="T47" s="27" t="s">
+        <v>1616</v>
+      </c>
+      <c r="U47" s="27" t="s">
+        <v>1534</v>
+      </c>
+      <c r="V47" s="27" t="s">
+        <v>337</v>
+      </c>
+      <c r="W47" s="27" t="s">
         <v>1617</v>
       </c>
-      <c r="U47" s="27" t="s">
-        <v>1222</v>
-      </c>
-      <c r="V47" s="23"/>
-      <c r="W47" s="27" t="s">
-        <v>1534</v>
-      </c>
       <c r="X47" s="27" t="s">
-        <v>337</v>
+        <v>1618</v>
       </c>
       <c r="Y47" s="27" t="s">
-        <v>1618</v>
+        <v>491</v>
       </c>
       <c r="Z47" s="27" t="s">
         <v>1619</v>
       </c>
       <c r="AA47" s="27" t="s">
-        <v>491</v>
+        <v>1250</v>
       </c>
       <c r="AB47" s="27" t="s">
         <v>1620</v>
       </c>
       <c r="AC47" s="27" t="s">
-        <v>1250</v>
+        <v>1550</v>
       </c>
       <c r="AD47" s="27" t="s">
         <v>1621</v>
       </c>
       <c r="AE47" s="27" t="s">
-        <v>1550</v>
+        <v>1506</v>
       </c>
       <c r="AF47" s="27" t="s">
         <v>1622</v>
       </c>
-      <c r="AG47" s="27" t="s">
-        <v>1506</v>
-      </c>
-      <c r="AH47" s="27" t="s">
-        <v>1623</v>
-      </c>
+      <c r="AG47" s="27"/>
+      <c r="AH47" s="27"/>
       <c r="AI47" s="27"/>
       <c r="AJ47" s="27"/>
     </row>
     <row r="48" ht="14.25" customHeight="1">
       <c r="A48" s="23" t="s">
+        <v>1623</v>
+      </c>
+      <c r="B48" s="23" t="s">
         <v>1624</v>
       </c>
-      <c r="B48" s="23" t="s">
+      <c r="C48" s="23" t="s">
         <v>1625</v>
-      </c>
-      <c r="C48" s="23" t="s">
-        <v>1626</v>
       </c>
       <c r="D48" s="23" t="s">
         <v>114</v>
       </c>
       <c r="E48" s="23" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="F48" s="32">
         <v>8495.0</v>
@@ -44655,39 +44603,37 @@
         <v>1567</v>
       </c>
       <c r="U48" s="27" t="s">
-        <v>1222</v>
-      </c>
-      <c r="V48" s="23"/>
+        <v>1534</v>
+      </c>
+      <c r="V48" s="27" t="s">
+        <v>1569</v>
+      </c>
       <c r="W48" s="27" t="s">
-        <v>1534</v>
+        <v>491</v>
       </c>
       <c r="X48" s="27" t="s">
-        <v>1569</v>
+        <v>1626</v>
       </c>
       <c r="Y48" s="27" t="s">
-        <v>491</v>
+        <v>1250</v>
       </c>
       <c r="Z48" s="27" t="s">
-        <v>1627</v>
+        <v>1620</v>
       </c>
       <c r="AA48" s="27" t="s">
-        <v>1250</v>
+        <v>1550</v>
       </c>
       <c r="AB48" s="27" t="s">
         <v>1621</v>
       </c>
       <c r="AC48" s="27" t="s">
-        <v>1550</v>
+        <v>1506</v>
       </c>
       <c r="AD48" s="27" t="s">
         <v>1622</v>
       </c>
-      <c r="AE48" s="27" t="s">
-        <v>1506</v>
-      </c>
-      <c r="AF48" s="27" t="s">
-        <v>1623</v>
-      </c>
+      <c r="AE48" s="23"/>
+      <c r="AF48" s="23"/>
       <c r="AG48" s="23"/>
       <c r="AH48" s="23"/>
       <c r="AI48" s="23"/>
@@ -44695,19 +44641,19 @@
     </row>
     <row r="49" ht="14.25" customHeight="1">
       <c r="A49" s="23" t="s">
+        <v>1627</v>
+      </c>
+      <c r="B49" s="23" t="s">
         <v>1628</v>
       </c>
-      <c r="B49" s="23" t="s">
+      <c r="C49" s="23" t="s">
         <v>1629</v>
-      </c>
-      <c r="C49" s="23" t="s">
-        <v>1630</v>
       </c>
       <c r="D49" s="23" t="s">
         <v>114</v>
       </c>
       <c r="E49" s="23" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="F49" s="32">
         <v>5295.0</v>
@@ -44751,21 +44697,19 @@
         <v>1578</v>
       </c>
       <c r="U49" s="27" t="s">
-        <v>1222</v>
-      </c>
-      <c r="V49" s="23"/>
+        <v>491</v>
+      </c>
+      <c r="V49" s="27" t="s">
+        <v>1631</v>
+      </c>
       <c r="W49" s="27" t="s">
-        <v>491</v>
+        <v>1550</v>
       </c>
       <c r="X49" s="27" t="s">
-        <v>1632</v>
-      </c>
-      <c r="Y49" s="27" t="s">
-        <v>1550</v>
-      </c>
-      <c r="Z49" s="27" t="s">
-        <v>1622</v>
-      </c>
+        <v>1621</v>
+      </c>
+      <c r="Y49" s="23"/>
+      <c r="Z49" s="23"/>
       <c r="AA49" s="23"/>
       <c r="AB49" s="23"/>
       <c r="AC49" s="23"/>
@@ -44779,19 +44723,19 @@
     </row>
     <row r="50" ht="14.25" customHeight="1">
       <c r="A50" s="23" t="s">
+        <v>1632</v>
+      </c>
+      <c r="B50" s="23" t="s">
         <v>1633</v>
       </c>
-      <c r="B50" s="23" t="s">
+      <c r="C50" s="23" t="s">
         <v>1634</v>
-      </c>
-      <c r="C50" s="23" t="s">
-        <v>1635</v>
       </c>
       <c r="D50" s="23" t="s">
         <v>114</v>
       </c>
       <c r="E50" s="23" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="F50" s="32">
         <v>5295.0</v>
@@ -44819,7 +44763,7 @@
       <c r="O50" s="46" t="s">
         <v>1497</v>
       </c>
-      <c r="P50" s="53" t="s">
+      <c r="P50" s="52" t="s">
         <v>1586</v>
       </c>
       <c r="Q50" s="27" t="s">
@@ -44832,24 +44776,22 @@
         <v>551</v>
       </c>
       <c r="T50" s="27" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="U50" s="27" t="s">
-        <v>1222</v>
-      </c>
-      <c r="V50" s="23"/>
+        <v>491</v>
+      </c>
+      <c r="V50" s="27" t="s">
+        <v>1636</v>
+      </c>
       <c r="W50" s="27" t="s">
-        <v>491</v>
+        <v>1550</v>
       </c>
       <c r="X50" s="27" t="s">
-        <v>1637</v>
-      </c>
-      <c r="Y50" s="27" t="s">
-        <v>1550</v>
-      </c>
-      <c r="Z50" s="27" t="s">
-        <v>1622</v>
-      </c>
+        <v>1621</v>
+      </c>
+      <c r="Y50" s="23"/>
+      <c r="Z50" s="23"/>
       <c r="AA50" s="23"/>
       <c r="AB50" s="23"/>
       <c r="AC50" s="23"/>
@@ -45296,19 +45238,19 @@
         <v>62</v>
       </c>
       <c r="N1" s="18" t="s">
+        <v>1637</v>
+      </c>
+      <c r="O1" s="18" t="s">
         <v>1638</v>
       </c>
-      <c r="O1" s="18" t="s">
+      <c r="P1" s="18" t="s">
         <v>1639</v>
       </c>
-      <c r="P1" s="18" t="s">
+      <c r="Q1" s="18" t="s">
         <v>1640</v>
       </c>
-      <c r="Q1" s="18" t="s">
+      <c r="R1" s="21" t="s">
         <v>1641</v>
-      </c>
-      <c r="R1" s="21" t="s">
-        <v>1642</v>
       </c>
       <c r="S1" s="22" t="s">
         <v>179</v>
@@ -45373,19 +45315,19 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="23" t="s">
+        <v>1642</v>
+      </c>
+      <c r="B2" s="23" t="s">
         <v>1643</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="C2" s="23" t="s">
         <v>1644</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>1645</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>99</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="F2" s="32">
         <v>1895.0</v>
@@ -45423,46 +45365,46 @@
         <v>2.0</v>
       </c>
       <c r="S2" s="27" t="s">
+        <v>1646</v>
+      </c>
+      <c r="T2" s="27" t="s">
         <v>1647</v>
       </c>
-      <c r="T2" s="27" t="s">
+      <c r="U2" s="27" t="s">
         <v>1648</v>
       </c>
-      <c r="U2" s="27" t="s">
+      <c r="V2" s="27" t="s">
         <v>1649</v>
       </c>
-      <c r="V2" s="27" t="s">
+      <c r="W2" s="27" t="s">
         <v>1650</v>
       </c>
-      <c r="W2" s="27" t="s">
+      <c r="X2" s="27" t="s">
         <v>1651</v>
       </c>
-      <c r="X2" s="27" t="s">
+      <c r="Y2" s="27" t="s">
         <v>1652</v>
       </c>
-      <c r="Y2" s="27" t="s">
+      <c r="Z2" s="27" t="s">
         <v>1653</v>
       </c>
-      <c r="Z2" s="27" t="s">
+      <c r="AA2" s="27" t="s">
         <v>1654</v>
       </c>
-      <c r="AA2" s="27" t="s">
+      <c r="AB2" s="27" t="s">
         <v>1655</v>
       </c>
-      <c r="AB2" s="27" t="s">
+      <c r="AC2" s="27" t="s">
         <v>1656</v>
       </c>
-      <c r="AC2" s="27" t="s">
+      <c r="AD2" s="27" t="s">
         <v>1657</v>
       </c>
-      <c r="AD2" s="27" t="s">
+      <c r="AE2" s="27" t="s">
         <v>1658</v>
       </c>
-      <c r="AE2" s="27" t="s">
+      <c r="AF2" s="27" t="s">
         <v>1659</v>
-      </c>
-      <c r="AF2" s="27" t="s">
-        <v>1660</v>
       </c>
       <c r="AG2" s="23"/>
       <c r="AH2" s="23"/>
@@ -45473,19 +45415,19 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="23" t="s">
+        <v>1660</v>
+      </c>
+      <c r="B3" s="23" t="s">
         <v>1661</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="C3" s="23" t="s">
         <v>1662</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>1663</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>99</v>
       </c>
       <c r="E3" s="23" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="F3" s="32">
         <v>2575.0</v>
@@ -45523,46 +45465,46 @@
         <v>2.0</v>
       </c>
       <c r="S3" s="27" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="T3" s="27" t="s">
+        <v>1664</v>
+      </c>
+      <c r="U3" s="27" t="s">
+        <v>1648</v>
+      </c>
+      <c r="V3" s="27" t="s">
+        <v>1649</v>
+      </c>
+      <c r="W3" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="X3" s="27" t="s">
         <v>1665</v>
       </c>
-      <c r="U3" s="27" t="s">
-        <v>1649</v>
-      </c>
-      <c r="V3" s="27" t="s">
-        <v>1650</v>
-      </c>
-      <c r="W3" s="27" t="s">
-        <v>1651</v>
-      </c>
-      <c r="X3" s="27" t="s">
+      <c r="Y3" s="27" t="s">
+        <v>1652</v>
+      </c>
+      <c r="Z3" s="27" t="s">
         <v>1666</v>
       </c>
-      <c r="Y3" s="27" t="s">
-        <v>1653</v>
-      </c>
-      <c r="Z3" s="27" t="s">
+      <c r="AA3" s="27" t="s">
         <v>1667</v>
       </c>
-      <c r="AA3" s="27" t="s">
+      <c r="AB3" s="27" t="s">
         <v>1668</v>
       </c>
-      <c r="AB3" s="27" t="s">
+      <c r="AC3" s="27" t="s">
         <v>1669</v>
       </c>
-      <c r="AC3" s="27" t="s">
+      <c r="AD3" s="27" t="s">
         <v>1670</v>
       </c>
-      <c r="AD3" s="27" t="s">
+      <c r="AE3" s="27" t="s">
         <v>1671</v>
       </c>
-      <c r="AE3" s="27" t="s">
+      <c r="AF3" s="27" t="s">
         <v>1672</v>
-      </c>
-      <c r="AF3" s="27" t="s">
-        <v>1673</v>
       </c>
       <c r="AG3" s="23"/>
       <c r="AH3" s="23"/>
@@ -45573,19 +45515,19 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="23" t="s">
+        <v>1673</v>
+      </c>
+      <c r="B4" s="23" t="s">
         <v>1674</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="C4" s="23" t="s">
         <v>1675</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>1676</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>99</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="F4" s="32">
         <v>4695.0</v>
@@ -45623,46 +45565,46 @@
         <v>4.0</v>
       </c>
       <c r="S4" s="27" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="T4" s="27" t="s">
+        <v>1677</v>
+      </c>
+      <c r="U4" s="27" t="s">
+        <v>1648</v>
+      </c>
+      <c r="V4" s="27" t="s">
         <v>1678</v>
       </c>
-      <c r="U4" s="27" t="s">
-        <v>1649</v>
-      </c>
-      <c r="V4" s="27" t="s">
+      <c r="W4" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="X4" s="27" t="s">
         <v>1679</v>
       </c>
-      <c r="W4" s="27" t="s">
-        <v>1651</v>
-      </c>
-      <c r="X4" s="27" t="s">
+      <c r="Y4" s="27" t="s">
+        <v>1652</v>
+      </c>
+      <c r="Z4" s="27" t="s">
         <v>1680</v>
       </c>
-      <c r="Y4" s="27" t="s">
-        <v>1653</v>
-      </c>
-      <c r="Z4" s="27" t="s">
+      <c r="AA4" s="27" t="s">
         <v>1681</v>
       </c>
-      <c r="AA4" s="27" t="s">
+      <c r="AB4" s="27" t="s">
         <v>1682</v>
       </c>
-      <c r="AB4" s="27" t="s">
+      <c r="AC4" s="27" t="s">
+        <v>1671</v>
+      </c>
+      <c r="AD4" s="27" t="s">
         <v>1683</v>
       </c>
-      <c r="AC4" s="27" t="s">
-        <v>1672</v>
-      </c>
-      <c r="AD4" s="27" t="s">
+      <c r="AE4" s="27" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AF4" s="27" t="s">
         <v>1684</v>
-      </c>
-      <c r="AE4" s="27" t="s">
-        <v>1668</v>
-      </c>
-      <c r="AF4" s="27" t="s">
-        <v>1685</v>
       </c>
       <c r="AG4" s="23"/>
       <c r="AH4" s="23"/>
@@ -45673,19 +45615,19 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="23" t="s">
+        <v>1685</v>
+      </c>
+      <c r="B5" s="23" t="s">
         <v>1686</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="C5" s="23" t="s">
         <v>1687</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>1688</v>
       </c>
       <c r="D5" s="23" t="s">
         <v>99</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="F5" s="32">
         <v>3815.0</v>
@@ -45723,40 +45665,40 @@
         <v>4.0</v>
       </c>
       <c r="S5" s="27" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="T5" s="27" t="s">
+        <v>1689</v>
+      </c>
+      <c r="U5" s="27" t="s">
+        <v>1648</v>
+      </c>
+      <c r="V5" s="27" t="s">
+        <v>1649</v>
+      </c>
+      <c r="W5" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="X5" s="27" t="s">
+        <v>1679</v>
+      </c>
+      <c r="Y5" s="27" t="s">
+        <v>1652</v>
+      </c>
+      <c r="Z5" s="27" t="s">
         <v>1690</v>
       </c>
-      <c r="U5" s="27" t="s">
-        <v>1649</v>
-      </c>
-      <c r="V5" s="27" t="s">
-        <v>1650</v>
-      </c>
-      <c r="W5" s="27" t="s">
-        <v>1651</v>
-      </c>
-      <c r="X5" s="27" t="s">
-        <v>1680</v>
-      </c>
-      <c r="Y5" s="27" t="s">
-        <v>1653</v>
-      </c>
-      <c r="Z5" s="27" t="s">
+      <c r="AA5" s="27" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AB5" s="27" t="s">
         <v>1691</v>
       </c>
-      <c r="AA5" s="27" t="s">
-        <v>1668</v>
-      </c>
-      <c r="AB5" s="27" t="s">
+      <c r="AC5" s="27" t="s">
+        <v>1669</v>
+      </c>
+      <c r="AD5" s="27" t="s">
         <v>1692</v>
-      </c>
-      <c r="AC5" s="27" t="s">
-        <v>1670</v>
-      </c>
-      <c r="AD5" s="27" t="s">
-        <v>1693</v>
       </c>
       <c r="AE5" s="23"/>
       <c r="AF5" s="23"/>
@@ -45769,19 +45711,19 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="23" t="s">
+        <v>1693</v>
+      </c>
+      <c r="B6" s="23" t="s">
         <v>1694</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="C6" s="23" t="s">
         <v>1695</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>1696</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>99</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="F6" s="32">
         <v>4895.0</v>
@@ -45819,40 +45761,40 @@
         <v>4.0</v>
       </c>
       <c r="S6" s="27" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="T6" s="27" t="s">
+        <v>1697</v>
+      </c>
+      <c r="U6" s="27" t="s">
+        <v>1648</v>
+      </c>
+      <c r="V6" s="27" t="s">
+        <v>1649</v>
+      </c>
+      <c r="W6" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="X6" s="27" t="s">
+        <v>1679</v>
+      </c>
+      <c r="Y6" s="27" t="s">
+        <v>1652</v>
+      </c>
+      <c r="Z6" s="27" t="s">
         <v>1698</v>
       </c>
-      <c r="U6" s="27" t="s">
-        <v>1649</v>
-      </c>
-      <c r="V6" s="27" t="s">
-        <v>1650</v>
-      </c>
-      <c r="W6" s="27" t="s">
-        <v>1651</v>
-      </c>
-      <c r="X6" s="27" t="s">
-        <v>1680</v>
-      </c>
-      <c r="Y6" s="27" t="s">
-        <v>1653</v>
-      </c>
-      <c r="Z6" s="27" t="s">
+      <c r="AA6" s="27" t="s">
+        <v>1667</v>
+      </c>
+      <c r="AB6" s="27" t="s">
         <v>1699</v>
       </c>
-      <c r="AA6" s="27" t="s">
-        <v>1668</v>
-      </c>
-      <c r="AB6" s="27" t="s">
+      <c r="AC6" s="27" t="s">
         <v>1700</v>
       </c>
-      <c r="AC6" s="27" t="s">
+      <c r="AD6" s="27" t="s">
         <v>1701</v>
-      </c>
-      <c r="AD6" s="27" t="s">
-        <v>1702</v>
       </c>
       <c r="AE6" s="23"/>
       <c r="AF6" s="23"/>
@@ -45865,19 +45807,19 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="23" t="s">
+        <v>1702</v>
+      </c>
+      <c r="B7" s="23" t="s">
         <v>1703</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="C7" s="27" t="s">
         <v>1704</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>1705</v>
       </c>
       <c r="D7" s="23" t="s">
         <v>99</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="F7" s="32">
         <v>9750.0</v>
@@ -45915,52 +45857,52 @@
         <v>4.0</v>
       </c>
       <c r="S7" s="27" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="T7" s="27" t="s">
+        <v>1706</v>
+      </c>
+      <c r="U7" s="27" t="s">
+        <v>1648</v>
+      </c>
+      <c r="V7" s="27" t="s">
         <v>1707</v>
       </c>
-      <c r="U7" s="27" t="s">
-        <v>1649</v>
-      </c>
-      <c r="V7" s="27" t="s">
+      <c r="W7" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="X7" s="27" t="s">
+        <v>1679</v>
+      </c>
+      <c r="Y7" s="27" t="s">
+        <v>1652</v>
+      </c>
+      <c r="Z7" s="27" t="s">
         <v>1708</v>
       </c>
-      <c r="W7" s="27" t="s">
-        <v>1651</v>
-      </c>
-      <c r="X7" s="27" t="s">
-        <v>1680</v>
-      </c>
-      <c r="Y7" s="27" t="s">
-        <v>1653</v>
-      </c>
-      <c r="Z7" s="27" t="s">
+      <c r="AA7" s="27" t="s">
+        <v>1681</v>
+      </c>
+      <c r="AB7" s="27" t="s">
         <v>1709</v>
       </c>
-      <c r="AA7" s="27" t="s">
-        <v>1682</v>
-      </c>
-      <c r="AB7" s="27" t="s">
+      <c r="AC7" s="27" t="s">
         <v>1710</v>
       </c>
-      <c r="AC7" s="27" t="s">
+      <c r="AD7" s="27" t="s">
         <v>1711</v>
       </c>
-      <c r="AD7" s="27" t="s">
+      <c r="AE7" s="27" t="s">
         <v>1712</v>
       </c>
-      <c r="AE7" s="27" t="s">
+      <c r="AF7" s="27" t="s">
         <v>1713</v>
       </c>
-      <c r="AF7" s="27" t="s">
+      <c r="AG7" s="27" t="s">
         <v>1714</v>
       </c>
-      <c r="AG7" s="27" t="s">
+      <c r="AH7" s="27" t="s">
         <v>1715</v>
-      </c>
-      <c r="AH7" s="27" t="s">
-        <v>1716</v>
       </c>
       <c r="AI7" s="23"/>
       <c r="AJ7" s="23"/>
@@ -45969,19 +45911,19 @@
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="23" t="s">
+        <v>1716</v>
+      </c>
+      <c r="B8" s="23" t="s">
         <v>1717</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="C8" s="23" t="s">
         <v>1718</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>1719</v>
       </c>
       <c r="D8" s="23" t="s">
         <v>99</v>
       </c>
       <c r="E8" s="27" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="F8" s="32">
         <v>4495.0</v>
@@ -46019,46 +45961,46 @@
         <v>4.0</v>
       </c>
       <c r="S8" s="27" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="T8" s="27" t="s">
+        <v>1720</v>
+      </c>
+      <c r="U8" s="27" t="s">
+        <v>1648</v>
+      </c>
+      <c r="V8" s="27" t="s">
+        <v>1649</v>
+      </c>
+      <c r="W8" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="X8" s="27" t="s">
+        <v>1679</v>
+      </c>
+      <c r="Y8" s="27" t="s">
+        <v>1652</v>
+      </c>
+      <c r="Z8" s="27" t="s">
         <v>1721</v>
       </c>
-      <c r="U8" s="27" t="s">
-        <v>1649</v>
-      </c>
-      <c r="V8" s="27" t="s">
-        <v>1650</v>
-      </c>
-      <c r="W8" s="27" t="s">
-        <v>1651</v>
-      </c>
-      <c r="X8" s="27" t="s">
-        <v>1680</v>
-      </c>
-      <c r="Y8" s="27" t="s">
-        <v>1653</v>
-      </c>
-      <c r="Z8" s="27" t="s">
+      <c r="AA8" s="27" t="s">
         <v>1722</v>
       </c>
-      <c r="AA8" s="27" t="s">
+      <c r="AB8" s="27" t="s">
         <v>1723</v>
       </c>
-      <c r="AB8" s="27" t="s">
+      <c r="AC8" s="27" t="s">
         <v>1724</v>
       </c>
-      <c r="AC8" s="27" t="s">
+      <c r="AD8" s="27" t="s">
         <v>1725</v>
       </c>
-      <c r="AD8" s="27" t="s">
+      <c r="AE8" s="27" t="s">
+        <v>1669</v>
+      </c>
+      <c r="AF8" s="27" t="s">
         <v>1726</v>
-      </c>
-      <c r="AE8" s="27" t="s">
-        <v>1670</v>
-      </c>
-      <c r="AF8" s="27" t="s">
-        <v>1727</v>
       </c>
       <c r="AG8" s="23"/>
       <c r="AH8" s="23"/>
@@ -46069,19 +46011,19 @@
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="23" t="s">
+        <v>1727</v>
+      </c>
+      <c r="B9" s="23" t="s">
         <v>1728</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="C9" s="23" t="s">
         <v>1729</v>
-      </c>
-      <c r="C9" s="23" t="s">
-        <v>1730</v>
       </c>
       <c r="D9" s="23" t="s">
         <v>99</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="F9" s="32">
         <v>795.0</v>
@@ -46119,52 +46061,52 @@
         <v>2.0</v>
       </c>
       <c r="S9" s="27" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="T9" s="27" t="s">
+        <v>1731</v>
+      </c>
+      <c r="U9" s="27" t="s">
+        <v>1648</v>
+      </c>
+      <c r="V9" s="27" t="s">
         <v>1732</v>
       </c>
-      <c r="U9" s="27" t="s">
-        <v>1649</v>
-      </c>
-      <c r="V9" s="27" t="s">
+      <c r="W9" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="X9" s="27" t="s">
         <v>1733</v>
       </c>
-      <c r="W9" s="27" t="s">
-        <v>1651</v>
-      </c>
-      <c r="X9" s="27" t="s">
+      <c r="Y9" s="27" t="s">
+        <v>1652</v>
+      </c>
+      <c r="Z9" s="27" t="s">
         <v>1734</v>
       </c>
-      <c r="Y9" s="27" t="s">
-        <v>1653</v>
-      </c>
-      <c r="Z9" s="27" t="s">
+      <c r="AA9" s="27" t="s">
         <v>1735</v>
       </c>
-      <c r="AA9" s="27" t="s">
+      <c r="AB9" s="27" t="s">
         <v>1736</v>
       </c>
-      <c r="AB9" s="27" t="s">
+      <c r="AC9" s="27" t="s">
+        <v>1656</v>
+      </c>
+      <c r="AD9" s="27" t="s">
+        <v>1657</v>
+      </c>
+      <c r="AE9" s="27" t="s">
         <v>1737</v>
       </c>
-      <c r="AC9" s="27" t="s">
-        <v>1657</v>
-      </c>
-      <c r="AD9" s="27" t="s">
-        <v>1658</v>
-      </c>
-      <c r="AE9" s="27" t="s">
+      <c r="AF9" s="27" t="s">
         <v>1738</v>
       </c>
-      <c r="AF9" s="27" t="s">
+      <c r="AG9" s="27" t="s">
         <v>1739</v>
       </c>
-      <c r="AG9" s="27" t="s">
+      <c r="AH9" s="27" t="s">
         <v>1740</v>
-      </c>
-      <c r="AH9" s="27" t="s">
-        <v>1741</v>
       </c>
       <c r="AI9" s="23"/>
       <c r="AJ9" s="23"/>
@@ -46173,19 +46115,19 @@
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="23" t="s">
+        <v>1741</v>
+      </c>
+      <c r="B10" s="23" t="s">
         <v>1742</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="C10" s="23" t="s">
         <v>1743</v>
-      </c>
-      <c r="C10" s="23" t="s">
-        <v>1744</v>
       </c>
       <c r="D10" s="23" t="s">
         <v>99</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="F10" s="32">
         <v>995.0</v>
@@ -46223,52 +46165,52 @@
         <v>2.0</v>
       </c>
       <c r="S10" s="27" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="T10" s="27" t="s">
+        <v>1745</v>
+      </c>
+      <c r="U10" s="27" t="s">
+        <v>1648</v>
+      </c>
+      <c r="V10" s="27" t="s">
+        <v>1649</v>
+      </c>
+      <c r="W10" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="X10" s="27" t="s">
         <v>1746</v>
       </c>
-      <c r="U10" s="27" t="s">
-        <v>1649</v>
-      </c>
-      <c r="V10" s="27" t="s">
-        <v>1650</v>
-      </c>
-      <c r="W10" s="27" t="s">
-        <v>1651</v>
-      </c>
-      <c r="X10" s="27" t="s">
+      <c r="Y10" s="27" t="s">
+        <v>1652</v>
+      </c>
+      <c r="Z10" s="27" t="s">
         <v>1747</v>
       </c>
-      <c r="Y10" s="27" t="s">
-        <v>1653</v>
-      </c>
-      <c r="Z10" s="27" t="s">
+      <c r="AA10" s="27" t="s">
         <v>1748</v>
       </c>
-      <c r="AA10" s="27" t="s">
+      <c r="AB10" s="27" t="s">
         <v>1749</v>
       </c>
-      <c r="AB10" s="27" t="s">
+      <c r="AC10" s="27" t="s">
         <v>1750</v>
       </c>
-      <c r="AC10" s="27" t="s">
+      <c r="AD10" s="27" t="s">
         <v>1751</v>
       </c>
-      <c r="AD10" s="27" t="s">
+      <c r="AE10" s="27" t="s">
         <v>1752</v>
       </c>
-      <c r="AE10" s="27" t="s">
+      <c r="AF10" s="27" t="s">
         <v>1753</v>
       </c>
-      <c r="AF10" s="27" t="s">
-        <v>1754</v>
-      </c>
       <c r="AG10" s="27" t="s">
+        <v>1656</v>
+      </c>
+      <c r="AH10" s="27" t="s">
         <v>1657</v>
-      </c>
-      <c r="AH10" s="27" t="s">
-        <v>1658</v>
       </c>
       <c r="AI10" s="23"/>
       <c r="AJ10" s="23"/>
@@ -46277,19 +46219,19 @@
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="23" t="s">
+        <v>1754</v>
+      </c>
+      <c r="B11" s="23" t="s">
         <v>1755</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="C11" s="23" t="s">
         <v>1756</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>1757</v>
       </c>
       <c r="D11" s="23" t="s">
         <v>99</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="F11" s="32">
         <v>1395.0</v>
@@ -46327,52 +46269,52 @@
         <v>3.0</v>
       </c>
       <c r="S11" s="27" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="T11" s="27" t="s">
+        <v>1758</v>
+      </c>
+      <c r="U11" s="27" t="s">
+        <v>1648</v>
+      </c>
+      <c r="V11" s="27" t="s">
+        <v>1649</v>
+      </c>
+      <c r="W11" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="X11" s="27" t="s">
+        <v>1746</v>
+      </c>
+      <c r="Y11" s="27" t="s">
+        <v>1652</v>
+      </c>
+      <c r="Z11" s="27" t="s">
+        <v>1747</v>
+      </c>
+      <c r="AA11" s="27" t="s">
         <v>1759</v>
       </c>
-      <c r="U11" s="27" t="s">
-        <v>1649</v>
-      </c>
-      <c r="V11" s="27" t="s">
-        <v>1650</v>
-      </c>
-      <c r="W11" s="27" t="s">
-        <v>1651</v>
-      </c>
-      <c r="X11" s="27" t="s">
-        <v>1747</v>
-      </c>
-      <c r="Y11" s="27" t="s">
-        <v>1653</v>
-      </c>
-      <c r="Z11" s="27" t="s">
+      <c r="AB11" s="27" t="s">
+        <v>1760</v>
+      </c>
+      <c r="AC11" s="27" t="s">
         <v>1748</v>
       </c>
-      <c r="AA11" s="27" t="s">
-        <v>1760</v>
-      </c>
-      <c r="AB11" s="27" t="s">
-        <v>1761</v>
-      </c>
-      <c r="AC11" s="27" t="s">
+      <c r="AD11" s="27" t="s">
         <v>1749</v>
-      </c>
-      <c r="AD11" s="27" t="s">
-        <v>1750</v>
       </c>
       <c r="AE11" s="27" t="s">
         <v>292</v>
       </c>
       <c r="AF11" s="27" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="AG11" s="27" t="s">
         <v>473</v>
       </c>
       <c r="AH11" s="27" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="AI11" s="23"/>
       <c r="AJ11" s="23"/>
@@ -46381,19 +46323,19 @@
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="23" t="s">
+        <v>1763</v>
+      </c>
+      <c r="B12" s="23" t="s">
         <v>1764</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="C12" s="23" t="s">
         <v>1765</v>
-      </c>
-      <c r="C12" s="23" t="s">
-        <v>1766</v>
       </c>
       <c r="D12" s="23" t="s">
         <v>99</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="F12" s="32">
         <v>1295.0</v>
@@ -46431,46 +46373,46 @@
         <v>2.0</v>
       </c>
       <c r="S12" s="27" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="T12" s="27" t="s">
+        <v>1767</v>
+      </c>
+      <c r="U12" s="27" t="s">
+        <v>1648</v>
+      </c>
+      <c r="V12" s="27" t="s">
+        <v>1649</v>
+      </c>
+      <c r="W12" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="X12" s="27" t="s">
+        <v>1746</v>
+      </c>
+      <c r="Y12" s="27" t="s">
+        <v>1652</v>
+      </c>
+      <c r="Z12" s="27" t="s">
         <v>1768</v>
       </c>
-      <c r="U12" s="27" t="s">
-        <v>1649</v>
-      </c>
-      <c r="V12" s="27" t="s">
-        <v>1650</v>
-      </c>
-      <c r="W12" s="27" t="s">
-        <v>1651</v>
-      </c>
-      <c r="X12" s="27" t="s">
-        <v>1747</v>
-      </c>
-      <c r="Y12" s="27" t="s">
-        <v>1653</v>
-      </c>
-      <c r="Z12" s="27" t="s">
-        <v>1769</v>
-      </c>
       <c r="AA12" s="27" t="s">
+        <v>1748</v>
+      </c>
+      <c r="AB12" s="27" t="s">
         <v>1749</v>
       </c>
-      <c r="AB12" s="27" t="s">
+      <c r="AC12" s="27" t="s">
         <v>1750</v>
       </c>
-      <c r="AC12" s="27" t="s">
+      <c r="AD12" s="27" t="s">
         <v>1751</v>
       </c>
-      <c r="AD12" s="27" t="s">
-        <v>1752</v>
-      </c>
       <c r="AE12" s="27" t="s">
+        <v>1656</v>
+      </c>
+      <c r="AF12" s="27" t="s">
         <v>1657</v>
-      </c>
-      <c r="AF12" s="27" t="s">
-        <v>1658</v>
       </c>
       <c r="AG12" s="23"/>
       <c r="AH12" s="23"/>
@@ -46481,19 +46423,19 @@
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="23" t="s">
+        <v>1769</v>
+      </c>
+      <c r="B13" s="23" t="s">
         <v>1770</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="C13" s="23" t="s">
         <v>1771</v>
-      </c>
-      <c r="C13" s="23" t="s">
-        <v>1772</v>
       </c>
       <c r="D13" s="23" t="s">
         <v>99</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="F13" s="32">
         <v>1395.0</v>
@@ -46527,56 +46469,56 @@
       <c r="Q13" s="36">
         <v>2.0</v>
       </c>
-      <c r="R13" s="54">
+      <c r="R13" s="53">
         <v>2.0</v>
       </c>
       <c r="S13" s="27" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="T13" s="27" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="U13" s="27" t="s">
+        <v>1648</v>
+      </c>
+      <c r="V13" s="27" t="s">
         <v>1649</v>
       </c>
-      <c r="V13" s="27" t="s">
+      <c r="W13" s="27" t="s">
         <v>1650</v>
       </c>
-      <c r="W13" s="27" t="s">
-        <v>1651</v>
-      </c>
       <c r="X13" s="27" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="Y13" s="27" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="Z13" s="27" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="AA13" s="27" t="s">
+        <v>1748</v>
+      </c>
+      <c r="AB13" s="27" t="s">
         <v>1749</v>
       </c>
-      <c r="AB13" s="27" t="s">
+      <c r="AC13" s="27" t="s">
         <v>1750</v>
       </c>
-      <c r="AC13" s="27" t="s">
-        <v>1751</v>
-      </c>
       <c r="AD13" s="27" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="AE13" s="27" t="s">
         <v>292</v>
       </c>
       <c r="AF13" s="27" t="s">
+        <v>1774</v>
+      </c>
+      <c r="AG13" s="27" t="s">
+        <v>1656</v>
+      </c>
+      <c r="AH13" s="27" t="s">
         <v>1775</v>
-      </c>
-      <c r="AG13" s="27" t="s">
-        <v>1657</v>
-      </c>
-      <c r="AH13" s="27" t="s">
-        <v>1776</v>
       </c>
       <c r="AI13" s="23"/>
       <c r="AJ13" s="23"/>
@@ -46585,19 +46527,19 @@
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="23" t="s">
+        <v>1776</v>
+      </c>
+      <c r="B14" s="23" t="s">
         <v>1777</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="C14" s="23" t="s">
         <v>1778</v>
-      </c>
-      <c r="C14" s="23" t="s">
-        <v>1779</v>
       </c>
       <c r="D14" s="23" t="s">
         <v>114</v>
       </c>
       <c r="E14" s="27" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="F14" s="32">
         <v>7995.0</v>
@@ -46635,40 +46577,40 @@
         <v>2.0</v>
       </c>
       <c r="S14" s="27" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="T14" s="27" t="s">
+        <v>1780</v>
+      </c>
+      <c r="U14" s="27" t="s">
+        <v>1648</v>
+      </c>
+      <c r="V14" s="27" t="s">
         <v>1781</v>
       </c>
-      <c r="U14" s="27" t="s">
-        <v>1649</v>
-      </c>
-      <c r="V14" s="27" t="s">
+      <c r="W14" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="X14" s="27" t="s">
         <v>1782</v>
       </c>
-      <c r="W14" s="27" t="s">
-        <v>1651</v>
-      </c>
-      <c r="X14" s="27" t="s">
+      <c r="Y14" s="27" t="s">
+        <v>1652</v>
+      </c>
+      <c r="Z14" s="27" t="s">
         <v>1783</v>
       </c>
-      <c r="Y14" s="27" t="s">
-        <v>1653</v>
-      </c>
-      <c r="Z14" s="27" t="s">
+      <c r="AA14" s="27" t="s">
+        <v>1656</v>
+      </c>
+      <c r="AB14" s="27" t="s">
         <v>1784</v>
       </c>
-      <c r="AA14" s="27" t="s">
-        <v>1657</v>
-      </c>
-      <c r="AB14" s="27" t="s">
+      <c r="AC14" s="27" t="s">
+        <v>1654</v>
+      </c>
+      <c r="AD14" s="27" t="s">
         <v>1785</v>
-      </c>
-      <c r="AC14" s="27" t="s">
-        <v>1655</v>
-      </c>
-      <c r="AD14" s="27" t="s">
-        <v>1786</v>
       </c>
       <c r="AE14" s="27"/>
       <c r="AF14" s="27"/>
@@ -46681,19 +46623,19 @@
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="23" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B15" s="23" t="s">
         <v>1787</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="C15" s="27" t="s">
         <v>1788</v>
-      </c>
-      <c r="C15" s="27" t="s">
-        <v>1789</v>
       </c>
       <c r="D15" s="23" t="s">
         <v>114</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="F15" s="32">
         <v>9995.0</v>
@@ -46731,77 +46673,77 @@
         <v>4.0</v>
       </c>
       <c r="S15" s="27" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="T15" s="27" t="s">
+        <v>1790</v>
+      </c>
+      <c r="U15" s="27" t="s">
+        <v>1648</v>
+      </c>
+      <c r="V15" s="27" t="s">
         <v>1791</v>
       </c>
-      <c r="U15" s="27" t="s">
-        <v>1649</v>
-      </c>
-      <c r="V15" s="27" t="s">
+      <c r="W15" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="X15" s="27" t="s">
         <v>1792</v>
       </c>
-      <c r="W15" s="27" t="s">
-        <v>1651</v>
-      </c>
-      <c r="X15" s="27" t="s">
+      <c r="Y15" s="27" t="s">
+        <v>1652</v>
+      </c>
+      <c r="Z15" s="27" t="s">
         <v>1793</v>
       </c>
-      <c r="Y15" s="27" t="s">
-        <v>1653</v>
-      </c>
-      <c r="Z15" s="27" t="s">
+      <c r="AA15" s="27" t="s">
+        <v>1656</v>
+      </c>
+      <c r="AB15" s="27" t="s">
         <v>1794</v>
       </c>
-      <c r="AA15" s="27" t="s">
-        <v>1657</v>
-      </c>
-      <c r="AB15" s="27" t="s">
+      <c r="AC15" s="27" t="s">
+        <v>1750</v>
+      </c>
+      <c r="AD15" s="27" t="s">
         <v>1795</v>
-      </c>
-      <c r="AC15" s="27" t="s">
-        <v>1751</v>
-      </c>
-      <c r="AD15" s="27" t="s">
-        <v>1796</v>
       </c>
       <c r="AE15" s="27" t="s">
         <v>501</v>
       </c>
       <c r="AF15" s="27" t="s">
+        <v>1796</v>
+      </c>
+      <c r="AG15" s="27" t="s">
         <v>1797</v>
       </c>
-      <c r="AG15" s="27" t="s">
+      <c r="AH15" s="27" t="s">
         <v>1798</v>
       </c>
-      <c r="AH15" s="27" t="s">
+      <c r="AI15" s="27" t="s">
         <v>1799</v>
       </c>
-      <c r="AI15" s="27" t="s">
+      <c r="AJ15" s="27" t="s">
         <v>1800</v>
-      </c>
-      <c r="AJ15" s="27" t="s">
-        <v>1801</v>
       </c>
       <c r="AK15" s="23"/>
       <c r="AL15" s="23"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="27" t="s">
+        <v>1801</v>
+      </c>
+      <c r="B16" s="27" t="s">
         <v>1802</v>
       </c>
-      <c r="B16" s="27" t="s">
+      <c r="C16" s="27" t="s">
         <v>1803</v>
-      </c>
-      <c r="C16" s="27" t="s">
-        <v>1804</v>
       </c>
       <c r="D16" s="27" t="s">
         <v>84</v>
       </c>
       <c r="E16" s="27" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="F16" s="24">
         <v>4795.0</v>
@@ -46835,42 +46777,42 @@
       <c r="Q16" s="34">
         <v>4.0</v>
       </c>
-      <c r="R16" s="54"/>
+      <c r="R16" s="53"/>
       <c r="S16" s="27" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="T16" s="27" t="s">
+        <v>1805</v>
+      </c>
+      <c r="U16" s="27" t="s">
+        <v>1648</v>
+      </c>
+      <c r="V16" s="27" t="s">
+        <v>1707</v>
+      </c>
+      <c r="W16" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="X16" s="27" t="s">
         <v>1806</v>
       </c>
-      <c r="U16" s="27" t="s">
-        <v>1649</v>
-      </c>
-      <c r="V16" s="27" t="s">
-        <v>1708</v>
-      </c>
-      <c r="W16" s="27" t="s">
-        <v>1651</v>
-      </c>
-      <c r="X16" s="27" t="s">
+      <c r="Y16" s="27" t="s">
+        <v>1652</v>
+      </c>
+      <c r="Z16" s="27" t="s">
         <v>1807</v>
       </c>
-      <c r="Y16" s="27" t="s">
-        <v>1653</v>
-      </c>
-      <c r="Z16" s="27" t="s">
+      <c r="AA16" s="27" t="s">
         <v>1808</v>
       </c>
-      <c r="AA16" s="27" t="s">
+      <c r="AB16" s="27" t="s">
         <v>1809</v>
       </c>
-      <c r="AB16" s="27" t="s">
+      <c r="AC16" s="27" t="s">
         <v>1810</v>
       </c>
-      <c r="AC16" s="27" t="s">
+      <c r="AD16" s="27" t="s">
         <v>1811</v>
-      </c>
-      <c r="AD16" s="27" t="s">
-        <v>1812</v>
       </c>
       <c r="AE16" s="27" t="s">
         <v>900</v>
@@ -46879,39 +46821,39 @@
         <v>901</v>
       </c>
       <c r="AG16" s="27" t="s">
+        <v>1812</v>
+      </c>
+      <c r="AH16" s="27" t="s">
         <v>1813</v>
       </c>
-      <c r="AH16" s="27" t="s">
+      <c r="AI16" s="27" t="s">
+        <v>1654</v>
+      </c>
+      <c r="AJ16" s="27" t="s">
         <v>1814</v>
-      </c>
-      <c r="AI16" s="27" t="s">
-        <v>1655</v>
-      </c>
-      <c r="AJ16" s="27" t="s">
-        <v>1815</v>
       </c>
       <c r="AK16" s="27" t="s">
         <v>489</v>
       </c>
       <c r="AL16" s="27" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="27" t="s">
+        <v>1816</v>
+      </c>
+      <c r="B17" s="27" t="s">
         <v>1817</v>
       </c>
-      <c r="B17" s="27" t="s">
+      <c r="C17" s="27" t="s">
         <v>1818</v>
-      </c>
-      <c r="C17" s="27" t="s">
-        <v>1819</v>
       </c>
       <c r="D17" s="27" t="s">
         <v>84</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="F17" s="24">
         <v>2795.0</v>
@@ -46947,58 +46889,58 @@
       </c>
       <c r="R17" s="33"/>
       <c r="S17" s="27" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="T17" s="27" t="s">
+        <v>1820</v>
+      </c>
+      <c r="U17" s="27" t="s">
+        <v>1648</v>
+      </c>
+      <c r="V17" s="27" t="s">
+        <v>1707</v>
+      </c>
+      <c r="W17" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="X17" s="27" t="s">
         <v>1821</v>
       </c>
-      <c r="U17" s="27" t="s">
-        <v>1649</v>
-      </c>
-      <c r="V17" s="27" t="s">
-        <v>1708</v>
-      </c>
-      <c r="W17" s="27" t="s">
-        <v>1651</v>
-      </c>
-      <c r="X17" s="27" t="s">
+      <c r="Y17" s="27" t="s">
+        <v>1652</v>
+      </c>
+      <c r="Z17" s="27" t="s">
         <v>1822</v>
-      </c>
-      <c r="Y17" s="27" t="s">
-        <v>1653</v>
-      </c>
-      <c r="Z17" s="27" t="s">
-        <v>1823</v>
       </c>
       <c r="AA17" s="27" t="s">
         <v>489</v>
       </c>
       <c r="AB17" s="27" t="s">
+        <v>1823</v>
+      </c>
+      <c r="AC17" s="27" t="s">
+        <v>1808</v>
+      </c>
+      <c r="AD17" s="27" t="s">
+        <v>1809</v>
+      </c>
+      <c r="AE17" s="27" t="s">
+        <v>1810</v>
+      </c>
+      <c r="AF17" s="27" t="s">
         <v>1824</v>
-      </c>
-      <c r="AC17" s="27" t="s">
-        <v>1809</v>
-      </c>
-      <c r="AD17" s="27" t="s">
-        <v>1810</v>
-      </c>
-      <c r="AE17" s="27" t="s">
-        <v>1811</v>
-      </c>
-      <c r="AF17" s="27" t="s">
-        <v>1825</v>
       </c>
       <c r="AG17" s="27" t="s">
         <v>1402</v>
       </c>
       <c r="AH17" s="27" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="AI17" s="27" t="s">
         <v>308</v>
       </c>
       <c r="AJ17" s="27" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="AK17" s="27"/>
       <c r="AL17" s="27"/>
@@ -47434,13 +47376,13 @@
         <v>1212</v>
       </c>
       <c r="O1" s="21" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="P1" s="21" t="s">
+        <v>1640</v>
+      </c>
+      <c r="Q1" s="21" t="s">
         <v>1641</v>
-      </c>
-      <c r="Q1" s="21" t="s">
-        <v>1642</v>
       </c>
       <c r="R1" s="22" t="s">
         <v>179</v>
@@ -47505,19 +47447,19 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="23" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B2" s="23" t="s">
         <v>1829</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="C2" s="23" t="s">
         <v>1830</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>1831</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>144</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="F2" s="32">
         <v>1095.0</v>
@@ -47536,10 +47478,10 @@
       <c r="L2" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="M2" s="55" t="s">
+      <c r="M2" s="54" t="s">
         <v>93</v>
       </c>
-      <c r="N2" s="56">
+      <c r="N2" s="55">
         <v>7.0</v>
       </c>
       <c r="O2" s="26"/>
@@ -47549,16 +47491,16 @@
         <v>885</v>
       </c>
       <c r="S2" s="27" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="T2" s="27" t="s">
         <v>300</v>
       </c>
       <c r="U2" s="27" t="s">
+        <v>1833</v>
+      </c>
+      <c r="V2" s="27" t="s">
         <v>1834</v>
-      </c>
-      <c r="V2" s="27" t="s">
-        <v>1835</v>
       </c>
       <c r="W2" s="27" t="s">
         <v>144</v>
@@ -47580,19 +47522,19 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="23" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B3" s="23" t="s">
         <v>1836</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="C3" s="23" t="s">
         <v>1837</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>1838</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>144</v>
       </c>
       <c r="E3" s="23" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="F3" s="32">
         <v>1095.0</v>
@@ -47628,13 +47570,13 @@
         <v>501</v>
       </c>
       <c r="S3" s="27" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="T3" s="27" t="s">
         <v>551</v>
       </c>
       <c r="U3" s="27" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="V3" s="23"/>
       <c r="W3" s="23"/>
@@ -47655,19 +47597,19 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="23" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B4" s="23" t="s">
         <v>1842</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="C4" s="23" t="s">
         <v>1843</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>1844</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>144</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="F4" s="32">
         <v>2795.0</v>
@@ -47696,10 +47638,10 @@
       <c r="P4" s="26"/>
       <c r="Q4" s="33"/>
       <c r="R4" s="27" t="s">
+        <v>1845</v>
+      </c>
+      <c r="S4" s="27" t="s">
         <v>1846</v>
-      </c>
-      <c r="S4" s="27" t="s">
-        <v>1847</v>
       </c>
       <c r="T4" s="27" t="s">
         <v>222</v>
@@ -47708,10 +47650,10 @@
         <v>281</v>
       </c>
       <c r="V4" s="27" t="s">
+        <v>1847</v>
+      </c>
+      <c r="W4" s="27" t="s">
         <v>1848</v>
-      </c>
-      <c r="W4" s="27" t="s">
-        <v>1849</v>
       </c>
       <c r="X4" s="23"/>
       <c r="Y4" s="23"/>
@@ -47730,19 +47672,19 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="23" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B5" s="23" t="s">
         <v>1850</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="C5" s="27" t="s">
         <v>1851</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>1852</v>
       </c>
       <c r="D5" s="23" t="s">
         <v>144</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="F5" s="32">
         <v>2195.0</v>
@@ -47771,16 +47713,16 @@
       <c r="P5" s="26"/>
       <c r="Q5" s="33"/>
       <c r="R5" s="27" t="s">
+        <v>1845</v>
+      </c>
+      <c r="S5" s="27" t="s">
         <v>1846</v>
       </c>
-      <c r="S5" s="27" t="s">
-        <v>1847</v>
-      </c>
       <c r="T5" s="27" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="U5" s="27" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="V5" s="27" t="s">
         <v>222</v>
@@ -47805,21 +47747,21 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="23" t="s">
+        <v>1854</v>
+      </c>
+      <c r="B6" s="23" t="s">
         <v>1855</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="C6" s="23" t="s">
         <v>1856</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>1857</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>84</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>1858</v>
-      </c>
-      <c r="F6" s="57">
+        <v>1857</v>
+      </c>
+      <c r="F6" s="56">
         <v>1750.0</v>
       </c>
       <c r="G6" s="25"/>
@@ -47846,12 +47788,12 @@
         <v>7.0</v>
       </c>
       <c r="P6" s="36"/>
-      <c r="Q6" s="54"/>
+      <c r="Q6" s="53"/>
       <c r="R6" s="27" t="s">
         <v>885</v>
       </c>
       <c r="S6" s="27" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="T6" s="27"/>
       <c r="U6" s="27"/>
@@ -47874,19 +47816,19 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="23" t="s">
+        <v>1859</v>
+      </c>
+      <c r="B7" s="23" t="s">
         <v>1860</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="C7" s="27" t="s">
         <v>1861</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>1862</v>
       </c>
       <c r="D7" s="23" t="s">
         <v>138</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="F7" s="32">
         <v>2495.0</v>
@@ -47918,19 +47860,19 @@
         <v>885</v>
       </c>
       <c r="S7" s="27" t="s">
+        <v>1863</v>
+      </c>
+      <c r="T7" s="27" t="s">
+        <v>1845</v>
+      </c>
+      <c r="U7" s="27" t="s">
         <v>1864</v>
-      </c>
-      <c r="T7" s="27" t="s">
-        <v>1846</v>
-      </c>
-      <c r="U7" s="27" t="s">
-        <v>1865</v>
       </c>
       <c r="V7" s="27" t="s">
         <v>300</v>
       </c>
       <c r="W7" s="27" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="X7" s="23"/>
       <c r="Y7" s="23"/>
@@ -47949,19 +47891,19 @@
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="23" t="s">
+        <v>1866</v>
+      </c>
+      <c r="B8" s="23" t="s">
         <v>1867</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="C8" s="23" t="s">
         <v>1868</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>1869</v>
       </c>
       <c r="D8" s="23" t="s">
         <v>138</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="F8" s="32">
         <v>2495.0</v>
@@ -47993,16 +47935,16 @@
         <v>885</v>
       </c>
       <c r="S8" s="27" t="s">
+        <v>1863</v>
+      </c>
+      <c r="T8" s="27" t="s">
+        <v>1845</v>
+      </c>
+      <c r="U8" s="27" t="s">
         <v>1864</v>
       </c>
-      <c r="T8" s="27" t="s">
-        <v>1846</v>
-      </c>
-      <c r="U8" s="27" t="s">
-        <v>1865</v>
-      </c>
       <c r="V8" s="27" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="W8" s="27" t="s">
         <v>138</v>
@@ -48024,21 +47966,21 @@
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="23" t="s">
+        <v>1870</v>
+      </c>
+      <c r="B9" s="23" t="s">
         <v>1871</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="C9" s="27" t="s">
         <v>1872</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>1873</v>
       </c>
       <c r="D9" s="23" t="s">
         <v>138</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>1874</v>
-      </c>
-      <c r="F9" s="57">
+        <v>1873</v>
+      </c>
+      <c r="F9" s="56">
         <v>1350.0</v>
       </c>
       <c r="G9" s="25"/>
@@ -48074,25 +48016,25 @@
         <v>501</v>
       </c>
       <c r="S9" s="27" t="s">
+        <v>1874</v>
+      </c>
+      <c r="T9" s="27" t="s">
         <v>1875</v>
       </c>
-      <c r="T9" s="27" t="s">
+      <c r="U9" s="31" t="s">
         <v>1876</v>
-      </c>
-      <c r="U9" s="31" t="s">
-        <v>1877</v>
       </c>
       <c r="V9" s="27" t="s">
         <v>1506</v>
       </c>
       <c r="W9" s="27" t="s">
+        <v>1877</v>
+      </c>
+      <c r="X9" s="27" t="s">
+        <v>1797</v>
+      </c>
+      <c r="Y9" s="27" t="s">
         <v>1878</v>
-      </c>
-      <c r="X9" s="27" t="s">
-        <v>1798</v>
-      </c>
-      <c r="Y9" s="27" t="s">
-        <v>1879</v>
       </c>
       <c r="Z9" s="27"/>
       <c r="AA9" s="27"/>
@@ -48109,21 +48051,21 @@
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="23" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B10" s="23" t="s">
         <v>1880</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="C10" s="23" t="s">
         <v>1881</v>
-      </c>
-      <c r="C10" s="23" t="s">
-        <v>1882</v>
       </c>
       <c r="D10" s="23" t="s">
         <v>138</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>1883</v>
-      </c>
-      <c r="F10" s="57">
+        <v>1882</v>
+      </c>
+      <c r="F10" s="56">
         <v>1250.0</v>
       </c>
       <c r="G10" s="25"/>
@@ -48159,25 +48101,25 @@
         <v>501</v>
       </c>
       <c r="S10" s="27" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="T10" s="27" t="s">
         <v>1506</v>
       </c>
       <c r="U10" s="31" t="s">
+        <v>1884</v>
+      </c>
+      <c r="V10" s="27" t="s">
+        <v>1875</v>
+      </c>
+      <c r="W10" s="27" t="s">
         <v>1885</v>
       </c>
-      <c r="V10" s="27" t="s">
-        <v>1876</v>
-      </c>
-      <c r="W10" s="27" t="s">
+      <c r="X10" s="27" t="s">
         <v>1886</v>
       </c>
-      <c r="X10" s="27" t="s">
+      <c r="Y10" s="27" t="s">
         <v>1887</v>
-      </c>
-      <c r="Y10" s="27" t="s">
-        <v>1888</v>
       </c>
       <c r="Z10" s="27"/>
       <c r="AA10" s="27"/>
@@ -48620,10 +48562,10 @@
         <v>55</v>
       </c>
       <c r="M1" s="18" t="s">
+        <v>1888</v>
+      </c>
+      <c r="N1" s="18" t="s">
         <v>1889</v>
-      </c>
-      <c r="N1" s="18" t="s">
-        <v>1890</v>
       </c>
       <c r="O1" s="18" t="s">
         <v>64</v>
@@ -48691,19 +48633,19 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="23" t="s">
+        <v>1890</v>
+      </c>
+      <c r="B2" s="23" t="s">
         <v>1891</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="C2" s="23" t="s">
         <v>1892</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>1893</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>151</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F2" s="25">
         <v>4200.0</v>
@@ -48722,50 +48664,50 @@
       <c r="L2" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="M2" s="58">
+      <c r="M2" s="57">
         <v>4.57</v>
       </c>
-      <c r="N2" s="58">
+      <c r="N2" s="57">
         <v>6.0</v>
       </c>
       <c r="O2" s="23" t="s">
         <v>110</v>
       </c>
       <c r="P2" s="27" t="s">
+        <v>1894</v>
+      </c>
+      <c r="Q2" s="27" t="s">
         <v>1895</v>
-      </c>
-      <c r="Q2" s="27" t="s">
-        <v>1896</v>
       </c>
       <c r="R2" s="27" t="s">
         <v>533</v>
       </c>
       <c r="S2" s="31" t="s">
+        <v>1896</v>
+      </c>
+      <c r="T2" s="27" t="s">
         <v>1897</v>
       </c>
-      <c r="T2" s="27" t="s">
+      <c r="U2" s="27" t="s">
         <v>1898</v>
       </c>
-      <c r="U2" s="27" t="s">
+      <c r="V2" s="27" t="s">
         <v>1899</v>
       </c>
-      <c r="V2" s="27" t="s">
+      <c r="W2" s="27" t="s">
         <v>1900</v>
-      </c>
-      <c r="W2" s="27" t="s">
-        <v>1901</v>
       </c>
       <c r="X2" s="27" t="s">
         <v>605</v>
       </c>
       <c r="Y2" s="27" t="s">
+        <v>1901</v>
+      </c>
+      <c r="Z2" s="27" t="s">
         <v>1902</v>
       </c>
-      <c r="Z2" s="27" t="s">
+      <c r="AA2" s="27" t="s">
         <v>1903</v>
-      </c>
-      <c r="AA2" s="27" t="s">
-        <v>1904</v>
       </c>
       <c r="AB2" s="27"/>
       <c r="AC2" s="27"/>
@@ -48778,19 +48720,19 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="23" t="s">
+        <v>1904</v>
+      </c>
+      <c r="B3" s="23" t="s">
         <v>1905</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="C3" s="23" t="s">
         <v>1906</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>1907</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>151</v>
       </c>
       <c r="E3" s="23" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="F3" s="25">
         <v>2400.0</v>
@@ -48809,38 +48751,38 @@
       <c r="L3" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="M3" s="58">
+      <c r="M3" s="57">
         <v>2.0</v>
       </c>
-      <c r="N3" s="58">
+      <c r="N3" s="57">
         <v>3.6</v>
       </c>
       <c r="O3" s="23" t="s">
         <v>110</v>
       </c>
       <c r="P3" s="27" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="Q3" s="31" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
       <c r="R3" s="27" t="s">
         <v>533</v>
       </c>
       <c r="S3" s="27" t="s">
+        <v>1909</v>
+      </c>
+      <c r="T3" s="27" t="s">
+        <v>1897</v>
+      </c>
+      <c r="U3" s="27" t="s">
         <v>1910</v>
-      </c>
-      <c r="T3" s="27" t="s">
-        <v>1898</v>
-      </c>
-      <c r="U3" s="27" t="s">
-        <v>1911</v>
       </c>
       <c r="V3" s="27" t="s">
         <v>891</v>
       </c>
       <c r="W3" s="27" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="X3" s="23"/>
       <c r="Y3" s="23"/>
@@ -48857,19 +48799,19 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="23" t="s">
+        <v>1912</v>
+      </c>
+      <c r="B4" s="23" t="s">
         <v>1913</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="C4" s="23" t="s">
         <v>1914</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>1915</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>151</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="F4" s="25">
         <v>1400.0</v>
@@ -48888,26 +48830,26 @@
       <c r="L4" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="M4" s="58">
+      <c r="M4" s="57">
         <v>1.3</v>
       </c>
-      <c r="N4" s="58">
+      <c r="N4" s="57">
         <v>4.7</v>
       </c>
       <c r="O4" s="23" t="s">
         <v>110</v>
       </c>
       <c r="P4" s="27" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="Q4" s="31" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="R4" s="27" t="s">
         <v>533</v>
       </c>
       <c r="S4" s="27" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="T4" s="23"/>
       <c r="U4" s="23"/>
@@ -48928,19 +48870,19 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="23" t="s">
+        <v>1918</v>
+      </c>
+      <c r="B5" s="23" t="s">
         <v>1919</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="C5" s="23" t="s">
         <v>1920</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>1921</v>
       </c>
       <c r="D5" s="23" t="s">
         <v>151</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="F5" s="25">
         <v>2000.0</v>
@@ -48959,38 +48901,38 @@
       <c r="L5" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="M5" s="58">
+      <c r="M5" s="57">
         <v>10.0</v>
       </c>
-      <c r="N5" s="58">
+      <c r="N5" s="57">
         <v>5.0</v>
       </c>
       <c r="O5" s="23" t="s">
         <v>110</v>
       </c>
       <c r="P5" s="27" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="Q5" s="27" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="R5" s="27" t="s">
         <v>533</v>
       </c>
       <c r="S5" s="27" t="s">
+        <v>1923</v>
+      </c>
+      <c r="T5" s="27" t="s">
         <v>1924</v>
       </c>
-      <c r="T5" s="27" t="s">
+      <c r="U5" s="27" t="s">
         <v>1925</v>
       </c>
-      <c r="U5" s="27" t="s">
+      <c r="V5" s="27" t="s">
         <v>1926</v>
       </c>
-      <c r="V5" s="27" t="s">
+      <c r="W5" s="27" t="s">
         <v>1927</v>
-      </c>
-      <c r="W5" s="27" t="s">
-        <v>1928</v>
       </c>
       <c r="X5" s="23"/>
       <c r="Y5" s="23"/>
@@ -49007,19 +48949,19 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="23" t="s">
+        <v>1928</v>
+      </c>
+      <c r="B6" s="23" t="s">
         <v>1929</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="C6" s="23" t="s">
         <v>1930</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>1931</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>151</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="F6" s="25">
         <v>1050.0</v>
@@ -49038,32 +48980,32 @@
       <c r="L6" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="M6" s="58">
+      <c r="M6" s="57">
         <v>4.5</v>
       </c>
-      <c r="N6" s="58">
+      <c r="N6" s="57">
         <v>1.0</v>
       </c>
       <c r="O6" s="23" t="s">
         <v>110</v>
       </c>
       <c r="P6" s="27" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="Q6" s="27" t="s">
+        <v>1932</v>
+      </c>
+      <c r="R6" s="27" t="s">
         <v>1933</v>
       </c>
-      <c r="R6" s="27" t="s">
+      <c r="S6" s="27" t="s">
         <v>1934</v>
       </c>
-      <c r="S6" s="27" t="s">
+      <c r="T6" s="27" t="s">
+        <v>1899</v>
+      </c>
+      <c r="U6" s="27" t="s">
         <v>1935</v>
-      </c>
-      <c r="T6" s="27" t="s">
-        <v>1900</v>
-      </c>
-      <c r="U6" s="27" t="s">
-        <v>1936</v>
       </c>
       <c r="V6" s="23"/>
       <c r="W6" s="23"/>
@@ -49082,19 +49024,19 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="23" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B7" s="23" t="s">
         <v>1937</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="C7" s="23" t="s">
         <v>1938</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>1939</v>
       </c>
       <c r="D7" s="23" t="s">
         <v>151</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="F7" s="25">
         <v>700.0</v>
@@ -49113,26 +49055,26 @@
       <c r="L7" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="M7" s="58">
+      <c r="M7" s="57">
         <v>8.0</v>
       </c>
-      <c r="N7" s="58">
+      <c r="N7" s="57">
         <v>3.0</v>
       </c>
       <c r="O7" s="23" t="s">
         <v>94</v>
       </c>
       <c r="P7" s="27" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="Q7" s="27" t="s">
+        <v>1940</v>
+      </c>
+      <c r="R7" s="27" t="s">
+        <v>1933</v>
+      </c>
+      <c r="S7" s="27" t="s">
         <v>1941</v>
-      </c>
-      <c r="R7" s="27" t="s">
-        <v>1934</v>
-      </c>
-      <c r="S7" s="27" t="s">
-        <v>1942</v>
       </c>
       <c r="T7" s="27"/>
       <c r="U7" s="27"/>
@@ -49153,19 +49095,19 @@
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="23" t="s">
+        <v>1942</v>
+      </c>
+      <c r="B8" s="23" t="s">
         <v>1943</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="C8" s="27" t="s">
         <v>1944</v>
-      </c>
-      <c r="C8" s="27" t="s">
-        <v>1945</v>
       </c>
       <c r="D8" s="23" t="s">
         <v>151</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="F8" s="25">
         <v>600.0</v>
@@ -49194,22 +49136,22 @@
         <v>94</v>
       </c>
       <c r="P8" s="27" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="Q8" s="27" t="s">
+        <v>1946</v>
+      </c>
+      <c r="R8" s="27" t="s">
+        <v>1933</v>
+      </c>
+      <c r="S8" s="27" t="s">
         <v>1947</v>
-      </c>
-      <c r="R8" s="27" t="s">
-        <v>1934</v>
-      </c>
-      <c r="S8" s="27" t="s">
-        <v>1948</v>
       </c>
       <c r="T8" s="27" t="s">
         <v>543</v>
       </c>
       <c r="U8" s="27" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="V8" s="23"/>
       <c r="W8" s="23"/>
@@ -49654,7 +49596,7 @@
         <v>65</v>
       </c>
       <c r="O1" s="21" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="P1" s="22" t="s">
         <v>179</v>
@@ -49719,19 +49661,19 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="39" t="s">
+        <v>1950</v>
+      </c>
+      <c r="B2" s="23" t="s">
         <v>1951</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="C2" s="23" t="s">
         <v>1952</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>1953</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>144</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="F2" s="32">
         <v>395.0</v>
@@ -49760,40 +49702,40 @@
         <v>1800.0</v>
       </c>
       <c r="P2" s="27" t="s">
+        <v>1954</v>
+      </c>
+      <c r="Q2" s="31" t="s">
         <v>1955</v>
       </c>
-      <c r="Q2" s="31" t="s">
+      <c r="R2" s="27" t="s">
         <v>1956</v>
       </c>
-      <c r="R2" s="27" t="s">
+      <c r="S2" s="31" t="s">
         <v>1957</v>
       </c>
-      <c r="S2" s="31" t="s">
+      <c r="T2" s="27" t="s">
         <v>1958</v>
       </c>
-      <c r="T2" s="27" t="s">
+      <c r="U2" s="31" t="s">
         <v>1959</v>
       </c>
-      <c r="U2" s="31" t="s">
+      <c r="V2" s="27" t="s">
         <v>1960</v>
       </c>
-      <c r="V2" s="27" t="s">
+      <c r="W2" s="31" t="s">
         <v>1961</v>
       </c>
-      <c r="W2" s="31" t="s">
+      <c r="X2" s="27" t="s">
         <v>1962</v>
       </c>
-      <c r="X2" s="27" t="s">
+      <c r="Y2" s="31" t="s">
         <v>1963</v>
       </c>
-      <c r="Y2" s="31" t="s">
+      <c r="Z2" s="27" t="s">
         <v>1964</v>
       </c>
-      <c r="Z2" s="27" t="s">
+      <c r="AA2" s="31" t="s">
         <v>1965</v>
-      </c>
-      <c r="AA2" s="31" t="s">
-        <v>1966</v>
       </c>
       <c r="AB2" s="23"/>
       <c r="AC2" s="23"/>
@@ -49806,19 +49748,19 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="23" t="s">
+        <v>1966</v>
+      </c>
+      <c r="B3" s="23" t="s">
         <v>1967</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="C3" s="23" t="s">
         <v>1968</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>1969</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>144</v>
       </c>
       <c r="E3" s="23" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="F3" s="32">
         <v>275.0</v>
@@ -49847,40 +49789,40 @@
         <v>1200.0</v>
       </c>
       <c r="P3" s="27" t="s">
+        <v>1954</v>
+      </c>
+      <c r="Q3" s="27" t="s">
         <v>1955</v>
       </c>
-      <c r="Q3" s="27" t="s">
+      <c r="R3" s="27" t="s">
         <v>1956</v>
       </c>
-      <c r="R3" s="27" t="s">
+      <c r="S3" s="27" t="s">
         <v>1957</v>
       </c>
-      <c r="S3" s="27" t="s">
+      <c r="T3" s="27" t="s">
         <v>1958</v>
       </c>
-      <c r="T3" s="27" t="s">
+      <c r="U3" s="27" t="s">
         <v>1959</v>
       </c>
-      <c r="U3" s="27" t="s">
+      <c r="V3" s="27" t="s">
         <v>1960</v>
       </c>
-      <c r="V3" s="27" t="s">
+      <c r="W3" s="27" t="s">
         <v>1961</v>
       </c>
-      <c r="W3" s="27" t="s">
+      <c r="X3" s="27" t="s">
         <v>1962</v>
       </c>
-      <c r="X3" s="27" t="s">
+      <c r="Y3" s="27" t="s">
         <v>1963</v>
       </c>
-      <c r="Y3" s="27" t="s">
+      <c r="Z3" s="27" t="s">
         <v>1964</v>
       </c>
-      <c r="Z3" s="27" t="s">
+      <c r="AA3" s="27" t="s">
         <v>1965</v>
-      </c>
-      <c r="AA3" s="27" t="s">
-        <v>1966</v>
       </c>
       <c r="AB3" s="23"/>
       <c r="AC3" s="23"/>
@@ -49893,19 +49835,19 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="23" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B4" s="23" t="s">
         <v>1971</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="C4" s="23" t="s">
         <v>1972</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>1973</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>144</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="F4" s="32">
         <v>495.0</v>
@@ -49935,7 +49877,7 @@
         <v>543</v>
       </c>
       <c r="Q4" s="27" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="R4" s="23"/>
       <c r="S4" s="23"/>
@@ -49958,19 +49900,19 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="23" t="s">
+        <v>1975</v>
+      </c>
+      <c r="B5" s="23" t="s">
         <v>1976</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="C5" s="23" t="s">
         <v>1977</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>1978</v>
       </c>
       <c r="D5" s="23" t="s">
         <v>144</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="F5" s="32">
         <v>295.0</v>
@@ -49999,40 +49941,40 @@
         <v>1800.0</v>
       </c>
       <c r="P5" s="27" t="s">
+        <v>1954</v>
+      </c>
+      <c r="Q5" s="27" t="s">
         <v>1955</v>
       </c>
-      <c r="Q5" s="27" t="s">
+      <c r="R5" s="27" t="s">
         <v>1956</v>
       </c>
-      <c r="R5" s="27" t="s">
+      <c r="S5" s="27" t="s">
         <v>1957</v>
       </c>
-      <c r="S5" s="27" t="s">
+      <c r="T5" s="27" t="s">
         <v>1958</v>
       </c>
-      <c r="T5" s="27" t="s">
+      <c r="U5" s="27" t="s">
         <v>1959</v>
       </c>
-      <c r="U5" s="27" t="s">
+      <c r="V5" s="27" t="s">
         <v>1960</v>
       </c>
-      <c r="V5" s="27" t="s">
+      <c r="W5" s="27" t="s">
         <v>1961</v>
       </c>
-      <c r="W5" s="27" t="s">
+      <c r="X5" s="27" t="s">
         <v>1962</v>
       </c>
-      <c r="X5" s="27" t="s">
+      <c r="Y5" s="27" t="s">
         <v>1963</v>
       </c>
-      <c r="Y5" s="27" t="s">
+      <c r="Z5" s="27" t="s">
         <v>1964</v>
       </c>
-      <c r="Z5" s="27" t="s">
+      <c r="AA5" s="27" t="s">
         <v>1965</v>
-      </c>
-      <c r="AA5" s="27" t="s">
-        <v>1966</v>
       </c>
       <c r="AB5" s="23"/>
       <c r="AC5" s="23"/>
@@ -50045,19 +49987,19 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="23" t="s">
+        <v>1979</v>
+      </c>
+      <c r="B6" s="23" t="s">
         <v>1980</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="C6" s="23" t="s">
         <v>1981</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>1982</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>144</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="F6" s="32">
         <v>195.0</v>
@@ -50086,40 +50028,40 @@
         <v>1200.0</v>
       </c>
       <c r="P6" s="27" t="s">
+        <v>1954</v>
+      </c>
+      <c r="Q6" s="27" t="s">
         <v>1955</v>
       </c>
-      <c r="Q6" s="27" t="s">
+      <c r="R6" s="27" t="s">
         <v>1956</v>
       </c>
-      <c r="R6" s="27" t="s">
+      <c r="S6" s="27" t="s">
         <v>1957</v>
       </c>
-      <c r="S6" s="27" t="s">
+      <c r="T6" s="27" t="s">
         <v>1958</v>
       </c>
-      <c r="T6" s="27" t="s">
+      <c r="U6" s="27" t="s">
         <v>1959</v>
       </c>
-      <c r="U6" s="27" t="s">
+      <c r="V6" s="27" t="s">
         <v>1960</v>
       </c>
-      <c r="V6" s="27" t="s">
+      <c r="W6" s="27" t="s">
         <v>1961</v>
       </c>
-      <c r="W6" s="27" t="s">
+      <c r="X6" s="27" t="s">
         <v>1962</v>
       </c>
-      <c r="X6" s="27" t="s">
+      <c r="Y6" s="27" t="s">
         <v>1963</v>
       </c>
-      <c r="Y6" s="27" t="s">
+      <c r="Z6" s="27" t="s">
         <v>1964</v>
       </c>
-      <c r="Z6" s="27" t="s">
+      <c r="AA6" s="27" t="s">
         <v>1965</v>
-      </c>
-      <c r="AA6" s="27" t="s">
-        <v>1966</v>
       </c>
       <c r="AB6" s="23"/>
       <c r="AC6" s="23"/>
@@ -50132,19 +50074,19 @@
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="A7" s="23" t="s">
+        <v>1983</v>
+      </c>
+      <c r="B7" s="23" t="s">
         <v>1984</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="C7" s="23" t="s">
         <v>1985</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>1986</v>
       </c>
       <c r="D7" s="23" t="s">
         <v>84</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="F7" s="32">
         <v>850.0</v>
@@ -50171,22 +50113,22 @@
       </c>
       <c r="O7" s="26"/>
       <c r="P7" s="27" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="Q7" s="31" t="s">
+        <v>1987</v>
+      </c>
+      <c r="R7" s="27" t="s">
         <v>1988</v>
       </c>
-      <c r="R7" s="27" t="s">
+      <c r="S7" s="27" t="s">
         <v>1989</v>
-      </c>
-      <c r="S7" s="27" t="s">
-        <v>1990</v>
       </c>
       <c r="T7" s="27" t="s">
         <v>781</v>
       </c>
       <c r="U7" s="27" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="V7" s="27" t="s">
         <v>308</v>
@@ -50209,19 +50151,19 @@
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="23" t="s">
+        <v>1991</v>
+      </c>
+      <c r="B8" s="23" t="s">
         <v>1992</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="C8" s="23" t="s">
         <v>1993</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>1994</v>
       </c>
       <c r="D8" s="23" t="s">
         <v>84</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="F8" s="32">
         <v>1795.0</v>
@@ -50248,46 +50190,46 @@
       </c>
       <c r="O8" s="26"/>
       <c r="P8" s="27" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="Q8" s="31" t="s">
+        <v>1995</v>
+      </c>
+      <c r="R8" s="27" t="s">
+        <v>1956</v>
+      </c>
+      <c r="S8" s="31" t="s">
         <v>1996</v>
       </c>
-      <c r="R8" s="27" t="s">
-        <v>1957</v>
-      </c>
-      <c r="S8" s="31" t="s">
+      <c r="T8" s="27" t="s">
+        <v>1958</v>
+      </c>
+      <c r="U8" s="31" t="s">
         <v>1997</v>
       </c>
-      <c r="T8" s="27" t="s">
-        <v>1959</v>
-      </c>
-      <c r="U8" s="31" t="s">
-        <v>1998</v>
-      </c>
       <c r="V8" s="27" t="s">
+        <v>1960</v>
+      </c>
+      <c r="W8" s="31" t="s">
         <v>1961</v>
-      </c>
-      <c r="W8" s="31" t="s">
-        <v>1962</v>
       </c>
       <c r="X8" s="27" t="s">
         <v>543</v>
       </c>
       <c r="Y8" s="31" t="s">
+        <v>1998</v>
+      </c>
+      <c r="Z8" s="27" t="s">
         <v>1999</v>
       </c>
-      <c r="Z8" s="27" t="s">
+      <c r="AA8" s="31" t="s">
         <v>2000</v>
       </c>
-      <c r="AA8" s="31" t="s">
+      <c r="AB8" s="27" t="s">
         <v>2001</v>
       </c>
-      <c r="AB8" s="27" t="s">
+      <c r="AC8" s="27" t="s">
         <v>2002</v>
-      </c>
-      <c r="AC8" s="27" t="s">
-        <v>2003</v>
       </c>
       <c r="AD8" s="27"/>
       <c r="AE8" s="27"/>
@@ -50301,16 +50243,16 @@
         <v>1492</v>
       </c>
       <c r="B9" s="23" t="s">
+        <v>2003</v>
+      </c>
+      <c r="C9" s="23" t="s">
         <v>2004</v>
-      </c>
-      <c r="C9" s="23" t="s">
-        <v>2005</v>
       </c>
       <c r="D9" s="23" t="s">
         <v>84</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="F9" s="32">
         <v>950.0</v>
@@ -50337,28 +50279,28 @@
       </c>
       <c r="O9" s="26"/>
       <c r="P9" s="27" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="Q9" s="31" t="s">
+        <v>2006</v>
+      </c>
+      <c r="R9" s="27" t="s">
+        <v>1956</v>
+      </c>
+      <c r="S9" s="31" t="s">
         <v>2007</v>
-      </c>
-      <c r="R9" s="27" t="s">
-        <v>1957</v>
-      </c>
-      <c r="S9" s="31" t="s">
-        <v>2008</v>
       </c>
       <c r="T9" s="27" t="s">
         <v>543</v>
       </c>
       <c r="U9" s="31" t="s">
+        <v>2008</v>
+      </c>
+      <c r="V9" s="27" t="s">
+        <v>2001</v>
+      </c>
+      <c r="W9" s="27" t="s">
         <v>2009</v>
-      </c>
-      <c r="V9" s="27" t="s">
-        <v>2002</v>
-      </c>
-      <c r="W9" s="27" t="s">
-        <v>2010</v>
       </c>
       <c r="X9" s="27"/>
       <c r="Y9" s="27"/>
@@ -50375,19 +50317,19 @@
     </row>
     <row r="10" ht="14.25" customHeight="1">
       <c r="A10" s="23" t="s">
+        <v>2010</v>
+      </c>
+      <c r="B10" s="23" t="s">
         <v>2011</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="C10" s="23" t="s">
         <v>2012</v>
-      </c>
-      <c r="C10" s="23" t="s">
-        <v>2013</v>
       </c>
       <c r="D10" s="23" t="s">
         <v>138</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="F10" s="32">
         <v>995.0</v>
@@ -50416,40 +50358,40 @@
         <v>1200.0</v>
       </c>
       <c r="P10" s="27" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="Q10" s="27" t="s">
+        <v>2014</v>
+      </c>
+      <c r="R10" s="27" t="s">
+        <v>1956</v>
+      </c>
+      <c r="S10" s="31" t="s">
         <v>2015</v>
       </c>
-      <c r="R10" s="27" t="s">
-        <v>1957</v>
-      </c>
-      <c r="S10" s="31" t="s">
+      <c r="T10" s="27" t="s">
+        <v>1958</v>
+      </c>
+      <c r="U10" s="31" t="s">
         <v>2016</v>
       </c>
-      <c r="T10" s="27" t="s">
-        <v>1959</v>
-      </c>
-      <c r="U10" s="31" t="s">
+      <c r="V10" s="27" t="s">
+        <v>1960</v>
+      </c>
+      <c r="W10" s="31" t="s">
         <v>2017</v>
-      </c>
-      <c r="V10" s="27" t="s">
-        <v>1961</v>
-      </c>
-      <c r="W10" s="31" t="s">
-        <v>2018</v>
       </c>
       <c r="X10" s="27" t="s">
         <v>543</v>
       </c>
       <c r="Y10" s="31" t="s">
+        <v>2018</v>
+      </c>
+      <c r="Z10" s="27" t="s">
+        <v>1999</v>
+      </c>
+      <c r="AA10" s="31" t="s">
         <v>2019</v>
-      </c>
-      <c r="Z10" s="27" t="s">
-        <v>2000</v>
-      </c>
-      <c r="AA10" s="31" t="s">
-        <v>2020</v>
       </c>
       <c r="AB10" s="23"/>
       <c r="AC10" s="23"/>
@@ -50462,19 +50404,19 @@
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="23" t="s">
+        <v>2020</v>
+      </c>
+      <c r="B11" s="23" t="s">
         <v>2021</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="C11" s="23" t="s">
         <v>2022</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>2023</v>
       </c>
       <c r="D11" s="23" t="s">
         <v>138</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="F11" s="32">
         <v>550.0</v>
@@ -50501,28 +50443,28 @@
       </c>
       <c r="O11" s="26"/>
       <c r="P11" s="27" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="Q11" s="27" t="s">
+        <v>2024</v>
+      </c>
+      <c r="R11" s="27" t="s">
+        <v>1956</v>
+      </c>
+      <c r="S11" s="31" t="s">
         <v>2025</v>
-      </c>
-      <c r="R11" s="27" t="s">
-        <v>1957</v>
-      </c>
-      <c r="S11" s="31" t="s">
-        <v>2026</v>
       </c>
       <c r="T11" s="27" t="s">
         <v>543</v>
       </c>
       <c r="U11" s="31" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="V11" s="27" t="s">
+        <v>2026</v>
+      </c>
+      <c r="W11" s="31" t="s">
         <v>2027</v>
-      </c>
-      <c r="W11" s="31" t="s">
-        <v>2028</v>
       </c>
       <c r="X11" s="27"/>
       <c r="Y11" s="27"/>

--- a/data/source/catalogo.xlsx
+++ b/data/source/catalogo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sonoro\SonoroWebPage\sonoro\data\source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2D209B5-E5D5-437E-8235-0832DBDF95A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D23F0865-CA38-40BC-84FD-FBCA6490CF7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="7" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INSTRUCCIONES" sheetId="1" r:id="rId1"/>
@@ -2671,695 +2671,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="S2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000029000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Sears México (tienda, no fabricante), https://www.sears.com.mx/producto/3706924/ecualizador-kbt-keqboom-5-bandas-4-canales-con-epicentro, consultado 2026-10-21. KBT no publica este modelo en su sitio.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="U2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-00002B000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Sears México (tienda, no fabricante), https://www.sears.com.mx/producto/3706924/ecualizador-kbt-keqboom-5-bandas-4-canales-con-epicentro, consultado 2026-10-21. Conserva el dato original «Refuerzo de graves ajustable».</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="W2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-00002D000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Sears México (tienda, no fabricante), https://www.sears.com.mx/producto/3706924/ecualizador-kbt-keqboom-5-bandas-4-canales-con-epicentro, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Y2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-00002F000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Sears México (tienda, no fabricante), https://www.sears.com.mx/producto/3706924/ecualizador-kbt-keqboom-5-bandas-4-canales-con-epicentro, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AA2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000031000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Sears México (tienda, no fabricante), https://www.sears.com.mx/producto/3706924/ecualizador-kbt-keqboom-5-bandas-4-canales-con-epicentro, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AC2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000033000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Sears México (tienda, no fabricante), https://www.sears.com.mx/producto/3706924/ecualizador-kbt-keqboom-5-bandas-4-canales-con-epicentro, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AE2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000035000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Sears México (tienda, no fabricante), https://www.sears.com.mx/producto/3706924/ecualizador-kbt-keqboom-5-bandas-4-canales-con-epicentro, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AG2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000037000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Sears México (tienda, no fabricante), 17.8 x 10.5 x 2.54 cm convertido a mm; la fuente no indica el orden de las medidas, https://www.sears.com.mx/producto/3706924/ecualizador-kbt-keqboom-5-bandas-4-canales-con-epicentro, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="S3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000039000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: KBT Electronics, https://kbtelectronics.com/ecualizador-grafico-de-7-bandas-crossover-keqs-7/, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="W3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-00003C000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: KBT Electronics, https://kbtelectronics.com/ecualizador-grafico-de-7-bandas-crossover-keqs-7/, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Y3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-00003E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: KBT Electronics, https://kbtelectronics.com/ecualizador-grafico-de-7-bandas-crossover-keqs-7/, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AA3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000040000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: KBT Electronics, 7″ ancho × 4-1/4″ largo × 1″ alto convertido a mm, https://kbtelectronics.com/ecualizador-grafico-de-7-bandas-crossover-keqs-7/, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="U4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000044000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: KBT Electronics, https://kbtelectronics.com/descargas/ (apps Android e iOS listadas para este modelo), consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="W4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000046000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Logistar (distribuidor KBT, no fabricante), https://logistar.mx/procesador-de-senal-digital-sgt-48dsphf/, consultado 2026-10-21. Solo menciona 4 canales de entrada y rango dinámico de la entrada RCA; si tiene entrada de alto nivel, agrégala.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Y4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000048000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Logistar (distribuidor KBT, no fabricante), https://logistar.mx/procesador-de-senal-digital-sgt-48dsphf/, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AA4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-00004A000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Logistar (distribuidor KBT, no fabricante), https://logistar.mx/procesador-de-senal-digital-sgt-48dsphf/, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AC4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-00004C000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Logistar (distribuidor KBT, no fabricante), https://logistar.mx/procesador-de-senal-digital-sgt-48dsphf/, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AE4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-00004D000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Logistar (distribuidor KBT, no fabricante), https://logistar.mx/procesador-de-senal-digital-sgt-48dsphf/, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AG4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-00004E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Logistar (distribuidor KBT, no fabricante), https://logistar.mx/procesador-de-senal-digital-sgt-48dsphf/, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AI4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-00004F000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Logistar (distribuidor KBT, no fabricante), https://logistar.mx/procesador-de-senal-digital-sgt-48dsphf/, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="U5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000013000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Sin ficha del fabricante en línea. Confirmar con KBT si hay controles físicos. Revisión 2026-10-21: la página de descargas de KBT (https://kbtelectronics.com/descargas/) solo lista app Android para este modelo; confirmar si también existe versión iOS.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="W5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000016000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Sin ficha del fabricante en línea. Dato tomado del nombre y descripción del catálogo (4 entradas y 8 salidas); falta confirmar el tipo de conector (RCA / alto nivel).</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="S6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000026000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Memphis Audio, manual EQL7, https://manuals.plus/memphis-audio/eql7-7-band-graphic-equalizer-manual, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="U6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000028000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Memphis Audio, manual EQL7, https://manuals.plus/memphis-audio/eql7-7-band-graphic-equalizer-manual; Sonic Electronix (tienda), https://www.sonicelectronix.com/item-186779-Memphis-EQL7.html, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="W6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-00002A000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Sonic Electronix (tienda), https://www.sonicelectronix.com/item-186779-Memphis-EQL7.html (2 pares RCA); Memphis Audio, manual EQL7, https://manuals.plus/memphis-audio/eql7-7-band-graphic-equalizer-manual (sensibilidad), consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Y6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-00002C000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Memphis Audio, manual EQL7, https://manuals.plus/memphis-audio/eql7-7-band-graphic-equalizer-manual, consultado 2026-10-21. Nota: el manual lo describe como paramétrico; el catálogo lo tiene como gráfico (columna tipo_ecualizador).</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AA6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-00002E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Memphis Audio, manual EQL7, https://manuals.plus/memphis-audio/eql7-7-band-graphic-equalizer-manual, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AC6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000030000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Memphis Audio, manual EQL7, https://manuals.plus/memphis-audio/eql7-7-band-graphic-equalizer-manual, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AE6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000032000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Sonic Electronix (tienda), https://www.sonicelectronix.com/item-186779-Memphis-EQL7.html, consultado 2026-10-21. El manual indica 110 dB con referencia de 1 V.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AG6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000034000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Memphis Audio, manual EQL7, https://manuals.plus/memphis-audio/eql7-7-band-graphic-equalizer-manual, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AI6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000036000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Memphis Audio, manual EQL7, https://manuals.plus/memphis-audio/eql7-7-band-graphic-equalizer-manual, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="U7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000038000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Cerwin-Vega, https://cerwinvega.com/products/cvdsp66lcd-dsp-lcd-display-6ch-in-6ch-out, consultado 2026-10-21. Conserva el dato original «Pantalla LCD integrada».</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="W7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-00003A000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Cerwin-Vega, https://cerwinvega.com/products/cvdsp66lcd-dsp-lcd-display-6ch-in-6ch-out, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Y7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-00003B000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Cerwin-Vega, https://cerwinvega.com/products/cvdsp66lcd-dsp-lcd-display-6ch-in-6ch-out, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AA7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-00003D000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Cerwin-Vega, https://cerwinvega.com/products/cvdsp66lcd-dsp-lcd-display-6ch-in-6ch-out, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AC7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-00003F000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Cerwin-Vega, https://cerwinvega.com/products/cvdsp66lcd-dsp-lcd-display-6ch-in-6ch-out, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AE7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000041000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Cerwin-Vega, https://cerwinvega.com/products/cvdsp66lcd-dsp-lcd-display-6ch-in-6ch-out, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="U8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000042000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Cerwin-Vega, ficha técnica CVDSP88, https://cdn.shopify.com/s/files/1/0645/1711/1988/files/CVDSP88.pdf?v=1730878317, consultado 2026-10-21. La página del producto (cerwinvega.com/products/8-in-8-out-dsp-cvdsp88) indica solo Windows.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="W8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000043000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Cerwin-Vega, https://cerwinvega.com/products/8-in-8-out-dsp-cvdsp88, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Y8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000045000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Cerwin-Vega, https://cerwinvega.com/products/8-in-8-out-dsp-cvdsp88, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AA8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000047000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Cerwin-Vega, https://cerwinvega.com/products/8-in-8-out-dsp-cvdsp88, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AC8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000049000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Cerwin-Vega, https://cerwinvega.com/products/8-in-8-out-dsp-cvdsp88, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AE8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-00004B000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Cerwin-Vega, https://cerwinvega.com/products/8-in-8-out-dsp-cvdsp88, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="S9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-00000C000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Sonic Electronix (tienda), https://www.sonicelectronix.com/item-227087-Cerwin-Vega-EQP850.html, consultado 2026-10-21. Source: Cerwin-Vega, https://cerwinvega.com/products/5-band-pre-amp-with-bass-processors-eqp850, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="W9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000010000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Sonic Electronix (tienda), https://www.sonicelectronix.com/item-227087-Cerwin-Vega-EQP850.html, consultado 2026-10-21. Source: Cerwin-Vega, https://cerwinvega.com/products/5-band-pre-amp-with-bass-processors-eqp850, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Y9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000014000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Sonic Electronix (tienda), https://www.sonicelectronix.com/item-227087-Cerwin-Vega-EQP850.html, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AA9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000017000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Sonic Electronix (tienda), https://www.sonicelectronix.com/item-227087-Cerwin-Vega-EQP850.html, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AC9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000019000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Sonic Electronix (tienda), https://www.sonicelectronix.com/item-227087-Cerwin-Vega-EQP850.html, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AE9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-00001B000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Sonic Electronix (tienda), https://www.sonicelectronix.com/item-227087-Cerwin-Vega-EQP850.html, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AG9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-00001D000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Cerwin-Vega, manual de usuario EQP850 (leído por OCR), https://cdn.shopify.com/s/files/1/0645/1711/1988/files/EQP850_Owner_s_Manual.pdf?v=1715990234, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AI9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-00001F000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Cerwin-Vega, manual de usuario EQP850 (leído por OCR), https://cdn.shopify.com/s/files/1/0645/1711/1988/files/EQP850_Owner_s_Manual.pdf?v=1715990234, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="S10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000025000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Cerwin-Vega, https://cerwinvega.com/products/7-band-parametric-eq-with-auxiliary-input-eq780, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="W10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000027000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>Source: Cerwin-Vega, https://cerwinvega.com/products/7-band-parametric-eq-with-auxiliary-input-eq780, consultado 2026-10-21.</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -3552,7 +2863,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00000C000000}">
+    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00000D000000}">
       <text>
         <r>
           <rPr>
@@ -3569,7 +2880,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00000D000000}">
+    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00000E000000}">
       <text>
         <r>
           <rPr>
@@ -3586,7 +2897,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00000E000000}">
+    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000010000000}">
       <text>
         <r>
           <rPr>
@@ -3602,7 +2913,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00000F000000}">
+    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000011000000}">
       <text>
         <r>
           <rPr>
@@ -3621,7 +2932,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000010000000}">
+    <comment ref="R1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000012000000}">
       <text>
         <r>
           <rPr>
@@ -3640,7 +2951,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000011000000}">
+    <comment ref="T1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000014000000}">
       <text>
         <r>
           <rPr>
@@ -3659,7 +2970,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000012000000}">
+    <comment ref="V1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000016000000}">
       <text>
         <r>
           <rPr>
@@ -3678,7 +2989,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000013000000}">
+    <comment ref="X1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000018000000}">
       <text>
         <r>
           <rPr>
@@ -3697,7 +3008,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000014000000}">
+    <comment ref="Z1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00001A000000}">
       <text>
         <r>
           <rPr>
@@ -3716,7 +3027,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000015000000}">
+    <comment ref="AB1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00001B000000}">
       <text>
         <r>
           <rPr>
@@ -3735,7 +3046,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000016000000}">
+    <comment ref="AD1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00001C000000}">
       <text>
         <r>
           <rPr>
@@ -3754,7 +3065,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000017000000}">
+    <comment ref="AF1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00001E000000}">
       <text>
         <r>
           <rPr>
@@ -3773,7 +3084,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000018000000}">
+    <comment ref="AH1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00001F000000}">
       <text>
         <r>
           <rPr>
@@ -4252,7 +3563,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000002000000}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000003000000}">
       <text>
         <r>
           <rPr>
@@ -4269,7 +3580,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000003000000}">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000004000000}">
       <text>
         <r>
           <rPr>
@@ -4285,7 +3596,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000004000000}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000005000000}">
       <text>
         <r>
           <rPr>
@@ -4301,7 +3612,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000005000000}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000006000000}">
       <text>
         <r>
           <rPr>
@@ -4318,7 +3629,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000006000000}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000007000000}">
       <text>
         <r>
           <rPr>
@@ -4335,7 +3646,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000007000000}">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000008000000}">
       <text>
         <r>
           <rPr>
@@ -4351,7 +3662,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000008000000}">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -4367,7 +3678,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000009000000}">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -4383,7 +3694,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-00000A000000}">
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-00000D000000}">
       <text>
         <r>
           <rPr>
@@ -4399,7 +3710,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-00000B000000}">
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-00000E000000}">
       <text>
         <r>
           <rPr>
@@ -4416,7 +3727,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-00000C000000}">
+    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000010000000}">
       <text>
         <r>
           <rPr>
@@ -4433,7 +3744,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-00000D000000}">
+    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000011000000}">
       <text>
         <r>
           <rPr>
@@ -4449,7 +3760,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-00000E000000}">
+    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000012000000}">
       <text>
         <r>
           <rPr>
@@ -4468,7 +3779,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000010000000}">
+    <comment ref="Q1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000014000000}">
       <text>
         <r>
           <rPr>
@@ -4487,7 +3798,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000011000000}">
+    <comment ref="S1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000016000000}">
       <text>
         <r>
           <rPr>
@@ -4506,7 +3817,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000013000000}">
+    <comment ref="U1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000018000000}">
       <text>
         <r>
           <rPr>
@@ -4525,7 +3836,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000014000000}">
+    <comment ref="W1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000019000000}">
       <text>
         <r>
           <rPr>
@@ -4544,7 +3855,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000016000000}">
+    <comment ref="Y1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-00001B000000}">
       <text>
         <r>
           <rPr>
@@ -4563,7 +3874,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000017000000}">
+    <comment ref="AA1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-00001C000000}">
       <text>
         <r>
           <rPr>
@@ -4582,7 +3893,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000018000000}">
+    <comment ref="AC1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-00001D000000}">
       <text>
         <r>
           <rPr>
@@ -4601,7 +3912,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000019000000}">
+    <comment ref="AE1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-00001E000000}">
       <text>
         <r>
           <rPr>
@@ -4620,7 +3931,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-00001A000000}">
+    <comment ref="AG1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000020000000}">
       <text>
         <r>
           <rPr>
@@ -4636,76 +3947,6 @@
 Ej: Potencia máxima, Respuesta en frecuencia, Cono, Crossover.
 NO repitas aquí medida, impedancia, potencia RMS ni configuración:
 el importador las genera solo.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-00001C000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>REVISAR unidad de venta: KBT publica sus fundas trenzadas expandibles en rollo de 30.5 m, con temperatura de operación de -103 °F a 257 °F (-75 °C a 125 °C). Confirmar si el precio es por rollo o por metro.
-Fuente: KBT Electronics, https://kbtelectronics.com/protector-de-cable-trenzado-kexp-12/</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000015000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>REVISAR unidad de venta: KBT publica sus fundas trenzadas expandibles en rollo de 30.5 m, con temperatura de operación de -103 °F a 257 °F (-75 °C a 125 °C). Confirmar si el precio es por rollo o por metro.
-Fuente: KBT Electronics, https://kbtelectronics.com/protector-de-cable-trenzado-kexp-12/</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-00001B000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>REVISAR unidad de venta: KBT publica sus fundas trenzadas expandibles en rollo de 30.5 m, con temperatura de operación de -103 °F a 257 °F (-75 °C a 125 °C). Confirmar si el precio es por rollo o por metro.
-Fuente: KBT Electronics, https://kbtelectronics.com/protector-de-cable-trenzado-kexp-12/</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000012000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>REVISAR: No se encontró el KSM-8 en el catálogo de KBT. La serie KSM son adaptadores específicos por vehículo (p. ej. KSM-19 Nissan/Kia, KSM-39 Hyundai/Kia). El texto de 'Función' coincide con la descripción de otro producto (I.S. RING-PVC-6). Verificar modelo y vehículos compatibles.
-Fuente: https://kbtelectronics.com/adaptador-de-altavoces-ksm-19/ ; https://www.kemik.gt/is-alza-para-bocina-65pulgadas</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-00000F000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>REVISAR: El ETP-25 (25 pies) no aparece en la línea actual de Memphis (longitudes: 1.5, 3, 6, 7, 12, 17 y 21 pies); solo se encontró en listados agotados. Posiblemente descontinuado.
-Fuente: Memphis Audio, https://www.memphiscaraudio.com/car-audio/connection/ ; https://www.ebay.com/p/1706233557</t>
         </r>
       </text>
     </comment>
@@ -5117,7 +4358,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7897" uniqueCount="2665">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7953" uniqueCount="2694">
   <si>
     <t>SONORO — Catálogo 3.0</t>
   </si>
@@ -6919,7 +6160,7 @@
     <t>focal-165-ac</t>
   </si>
   <si>
-    <t>Bocinas coaxiales de 6.5" Access 165 AC</t>
+    <t>Bocinas coaxiales Access de 6.5" 165 AC</t>
   </si>
   <si>
     <t>Par de bocinas coaxiales de 6.5 pulgadas de 2 vías</t>
@@ -11074,7 +10315,13 @@
     <t>Pro Plus - Rollo de taller</t>
   </si>
   <si>
-    <t>Rollo de taller de tres capas con 6 metros cuadrados de cobertura</t>
+    <t>Rollo insonorizante de espuma, revestimiento de lámina y caucho butílico con 6 metros cuadrados de cobertura</t>
+  </si>
+  <si>
+    <t>Función</t>
+  </si>
+  <si>
+    <t>Detiene la vibración de los paneles y bloquea el ruido de rodaje en una sola pasada (butilo, foil y espuma de celda cerrada)</t>
   </si>
   <si>
     <t>Aplicación</t>
@@ -11104,19 +10351,31 @@
     <t>Espuma y butilo impermeables y resistentes al calor</t>
   </si>
   <si>
-    <t>CLASSIC BULK KIT</t>
-  </si>
-  <si>
-    <t>soundskins-classic-bulk-kit</t>
+    <t>Temperatura de servicio</t>
+  </si>
+  <si>
+    <t>-40 °C a 180 °C (-40 °F a 356 °F)</t>
+  </si>
+  <si>
+    <t>18.1 kg (40 lb)</t>
+  </si>
+  <si>
+    <t>CLASSIC BLACK</t>
+  </si>
+  <si>
+    <t>soundskins-classic-black-kit</t>
   </si>
   <si>
     <t>Classic - Rollo a granel</t>
   </si>
   <si>
-    <t>Rollo a granel de butilo y foil de una sola capa con 3.6 metros cuadrados de cobertura</t>
-  </si>
-  <si>
-    <t>Amortiguamiento en una sola capa, sin agregar peso excesivo</t>
+    <t>Rollo insonorizante a granel de caucho butílico y una capa de lámina con 3.6 metros cuadrados de cobertura</t>
+  </si>
+  <si>
+    <t>Amortiguamiento en una sola capa, sin agregar peso excesivo; detiene la vibración de la lámina metálica y reduce rechinidos y resonancia</t>
+  </si>
+  <si>
+    <t>Puertas, piso y cajuela de la mayoría de los autos, o buena parte de una camioneta tipo van</t>
   </si>
   <si>
     <t>Rollo continuo sobre tubo interior para desenrollado fácil</t>
@@ -11125,31 +10384,49 @@
     <t>23.6" × 236" (60 × 600 cm)</t>
   </si>
   <si>
+    <t>Composición</t>
+  </si>
+  <si>
+    <t>Butilo de caucho puro y foil de aluminio en relieve; sin rellenos reciclados</t>
+  </si>
+  <si>
     <t>Foil negro (Stealth Black)</t>
   </si>
   <si>
-    <t>CLASSIC LITE BK</t>
-  </si>
-  <si>
-    <t>soundskins-classic-lite-bk</t>
+    <t>13.6 kg (30 lb)</t>
+  </si>
+  <si>
+    <t>CLASSIC LITE BLACK</t>
+  </si>
+  <si>
+    <t>soundskins-classic-lite-black</t>
   </si>
   <si>
     <t>Classic Lite - Negro</t>
   </si>
   <si>
-    <t>Lámina insonorizante de perfil ultradelgado con 4.7 metros cuadrados de cobertura</t>
+    <t>Láminas insonorizantes de perfil ultradelgado con 4.7 metros cuadrados de cobertura</t>
+  </si>
+  <si>
+    <t>Amortigua el sonido y la vibración sin agregar mucho peso ni afectar el consumo de combustible</t>
   </si>
   <si>
     <t>Paneles donde el espacio o el peso son críticos</t>
   </si>
   <si>
-    <t>Kit de láminas</t>
-  </si>
-  <si>
-    <t>SSK HTSHLD</t>
-  </si>
-  <si>
-    <t>soundskins-ssk-htshld</t>
+    <t>47 láminas de 25 × 40 cm (9.84" × 15.75") por caja</t>
+  </si>
+  <si>
+    <t>Foil negro en relieve</t>
+  </si>
+  <si>
+    <t>10.4 kg (23 lb)</t>
+  </si>
+  <si>
+    <t>HEAT SHIELD</t>
+  </si>
+  <si>
+    <t>soundskins-ssk-heat-shield</t>
   </si>
   <si>
     <t>Heat Shield - Barrera térmica</t>
@@ -11158,52 +10435,70 @@
     <t>Manta de barrera térmica y acústica de doble capa para cofre y salpicadera</t>
   </si>
   <si>
-    <t>Uso fuera de la cabina: cofre, compartimiento del motor y salpicadera</t>
+    <t>Térmica: el foil refleja el calor radiante del motor, escape y sol. Acústica: la espuma de celda cerrada absorbe ruido de motor, llantas y escape</t>
+  </si>
+  <si>
+    <t>Uso fuera de la cabina: cofre, compartimiento del motor, pared de fuego (firewall) y salpicadera</t>
   </si>
   <si>
     <t>Manta en rollo</t>
   </si>
   <si>
-    <t>Función térmica</t>
-  </si>
-  <si>
-    <t>El foil refleja el calor radiante del motor, escape y sol</t>
-  </si>
-  <si>
-    <t>Función acústica</t>
-  </si>
-  <si>
-    <t>La espuma de celda cerrada absorbe ruido de motor, llantas y escape</t>
-  </si>
-  <si>
-    <t>SS PRO1</t>
-  </si>
-  <si>
-    <t>soundskins-ss-pro1</t>
-  </si>
-  <si>
-    <t>SoundSkins Pro - Lámina de tres capas</t>
-  </si>
-  <si>
-    <t>Lámina insonorizante de tres capas con 1 metro cuadrado de cobertura</t>
-  </si>
-  <si>
-    <t>Puertas y paneles individuales</t>
-  </si>
-  <si>
-    <t>Función</t>
+    <t>Dimensiones del rollo</t>
+  </si>
+  <si>
+    <t>39.4" × 196.9" (100 × 500 cm)</t>
+  </si>
+  <si>
+    <t>Temperatura máxima</t>
+  </si>
+  <si>
+    <t>249 °C (480 °F)</t>
+  </si>
+  <si>
+    <t>Valor R</t>
+  </si>
+  <si>
+    <t>4.10</t>
+  </si>
+  <si>
+    <t>4.5 kg (9.9 lb)</t>
+  </si>
+  <si>
+    <t>PRO DOOR KIT</t>
+  </si>
+  <si>
+    <t>soundskins-pro-door-kit</t>
+  </si>
+  <si>
+    <t>Pro Door Kit - Lámina de tres capas para dos puertas</t>
+  </si>
+  <si>
+    <t>Rollo insonorizante de caucho butílico, lámina metálica y espuma acústica con 1 metro cuadrado de cobertura</t>
   </si>
   <si>
     <t>Reduce vibraciones, aísla calor y minimiza resonancia en un solo material</t>
   </si>
   <si>
+    <t>Dos puertas de un sedán estándar (piel exterior y orificios de acceso) o paneles individuales</t>
+  </si>
+  <si>
+    <t>1 rollo de 11 pie² (≈1 m²), corte a medida</t>
+  </si>
+  <si>
     <t>Butilo de alto poder adhesivo</t>
   </si>
   <si>
-    <t>WAVY</t>
-  </si>
-  <si>
-    <t>soundskins-wavy</t>
+    <t>Espuma y butilo impermeables; resistente al calor</t>
+  </si>
+  <si>
+    <t>5.0 kg (11 lb)</t>
+  </si>
+  <si>
+    <t>WAVY FOAM</t>
+  </si>
+  <si>
+    <t>soundskins-wavy-foam</t>
   </si>
   <si>
     <t>Wavy - Espuma acústica de 8 mm</t>
@@ -11212,33 +10507,51 @@
     <t>Manta de espuma de celda cerrada de 8 mm para absorción acústica</t>
   </si>
   <si>
-    <t>Se coloca sobre la lámina de butilo como segunda capa</t>
-  </si>
-  <si>
     <t>Absorbe la onda trasera de las bocinas y el ruido dentro de cavidades</t>
   </si>
   <si>
-    <t>TAPE</t>
-  </si>
-  <si>
-    <t>soundskins-tape</t>
+    <t>Puertas, paneles de puerta, repisa trasera y tapa de cajuela; también sobre la lámina de butilo como segunda capa</t>
+  </si>
+  <si>
+    <t>1 rollo de espuma con respaldo adhesivo, corte a medida</t>
+  </si>
+  <si>
+    <t>23.6" × 196.9" (60 × 500 cm)</t>
+  </si>
+  <si>
+    <t>Respaldo adhesivo sensible a la presión</t>
+  </si>
+  <si>
+    <t>Impermeable; resiste moho, aceite, gasolina y clima extremo</t>
+  </si>
+  <si>
+    <t>1.8 kg (4 lb)</t>
+  </si>
+  <si>
+    <t>SILENT TAPE</t>
+  </si>
+  <si>
+    <t>soundskins-silent-tape</t>
   </si>
   <si>
     <t>Foam Tape - Cinta de espuma acústica</t>
   </si>
   <si>
-    <t>Juego de cuatro rollos de cinta de espuma de celda cerrada para eliminar rechinidos</t>
+    <t>Cinta de espuma de celda cerrada para eliminar rechinidos, vibraciones y brechas</t>
+  </si>
+  <si>
+    <t>Elimina rechinidos y vibraciones entre paneles</t>
   </si>
   <si>
     <t>Uniones de plásticos, clips de panel y contactos entre piezas</t>
   </si>
   <si>
-    <t>Elimina rechinidos y vibraciones entre paneles</t>
-  </si>
-  <si>
     <t>Cuatro rollos de 2", 1" y 0.5" de ancho</t>
   </si>
   <si>
+    <t>Impermeable, resistente al calor y retardante de llama</t>
+  </si>
+  <si>
     <t>capacidad_w</t>
   </si>
   <si>
@@ -12277,7 +11590,7 @@
     <t>6x9" (15 × 23 cm)</t>
   </si>
   <si>
-    <t>SPK RINGS V3</t>
+    <t>SPEAKER RINGS</t>
   </si>
   <si>
     <t>soundskins-spk-rings-v3</t>
@@ -12316,6 +11629,12 @@
     <t>Alcanza para 4 bocinas o más</t>
   </si>
   <si>
+    <t>Ancho de la tira</t>
+  </si>
+  <si>
+    <t>20 mm (0.78")</t>
+  </si>
+  <si>
     <t>SILENT STRIP</t>
   </si>
   <si>
@@ -12337,12 +11656,15 @@
     <t>Ancho</t>
   </si>
   <si>
-    <t>3/8" de ancho (también disponible en 1/2", 3/4" y 1")</t>
+    <t>3/8" de ancho (también disponible en 1/2", 3/4", 1" y 2")</t>
   </si>
   <si>
     <t>Resistente a la intemperie, temperatura y químicos</t>
   </si>
   <si>
+    <t>3 mm (0.12")</t>
+  </si>
+  <si>
     <t>ROLLER</t>
   </si>
   <si>
@@ -12355,10 +11677,7 @@
     <t>Rodillo de mano para adherir la lámina insonorizante a la superficie</t>
   </si>
   <si>
-    <t>Rodillo con mango</t>
-  </si>
-  <si>
-    <t>Uso</t>
+    <t>Rodillo de hule de poliuretano, madera y acero</t>
   </si>
   <si>
     <t>Presiona la lámina contra el metal para eliminar burbujas de aire</t>
@@ -12368,6 +11687,15 @@
   </si>
   <si>
     <t>Sin rodillo el butilo no adhiere completo y la lámina puede despegarse</t>
+  </si>
+  <si>
+    <t>17.5 × 3.6 × 3.6 cm (6.9" × 1.4" × 1.4")</t>
+  </si>
+  <si>
+    <t>139 g (4.9 oz)</t>
+  </si>
+  <si>
+    <t>Todo tipo de material insonorizante</t>
   </si>
   <si>
     <t>RFI-16</t>
@@ -14912,7 +14240,7 @@
         <v>67</v>
       </c>
       <c r="N1" s="18" t="s">
-        <v>2125</v>
+        <v>2149</v>
       </c>
       <c r="O1" s="19" t="s">
         <v>181</v>
@@ -14977,19 +14305,19 @@
     </row>
     <row r="2" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="20" t="s">
-        <v>2126</v>
+        <v>2150</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>2127</v>
+        <v>2151</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>2128</v>
+        <v>2152</v>
       </c>
       <c r="D2" s="20" t="s">
         <v>146</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>2129</v>
+        <v>2153</v>
       </c>
       <c r="F2" s="24">
         <v>395</v>
@@ -15016,13 +14344,13 @@
         <v>208</v>
       </c>
       <c r="P2" s="20" t="s">
-        <v>2130</v>
+        <v>2154</v>
       </c>
       <c r="Q2" s="20" t="s">
-        <v>2024</v>
+        <v>1986</v>
       </c>
       <c r="R2" s="20" t="s">
-        <v>2131</v>
+        <v>2155</v>
       </c>
       <c r="S2" s="20"/>
       <c r="T2" s="20"/>
@@ -15043,19 +14371,19 @@
     </row>
     <row r="3" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="20" t="s">
-        <v>2132</v>
+        <v>2156</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>2133</v>
+        <v>2157</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>2134</v>
+        <v>2158</v>
       </c>
       <c r="D3" s="20" t="s">
         <v>146</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>2135</v>
+        <v>2159</v>
       </c>
       <c r="F3" s="24">
         <v>195</v>
@@ -15082,13 +14410,13 @@
         <v>1578</v>
       </c>
       <c r="P3" s="20" t="s">
-        <v>2136</v>
+        <v>2160</v>
       </c>
       <c r="Q3" s="20" t="s">
-        <v>2137</v>
+        <v>2161</v>
       </c>
       <c r="R3" s="20" t="s">
-        <v>2138</v>
+        <v>2162</v>
       </c>
       <c r="S3" s="20"/>
       <c r="T3" s="20"/>
@@ -15109,19 +14437,19 @@
     </row>
     <row r="4" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="20" t="s">
-        <v>2139</v>
+        <v>2163</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>2140</v>
+        <v>2164</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>2141</v>
+        <v>2165</v>
       </c>
       <c r="D4" s="20" t="s">
         <v>146</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>2142</v>
+        <v>2166</v>
       </c>
       <c r="F4" s="24">
         <v>150</v>
@@ -15148,13 +14476,13 @@
         <v>1578</v>
       </c>
       <c r="P4" s="20" t="s">
-        <v>2136</v>
+        <v>2160</v>
       </c>
       <c r="Q4" s="20" t="s">
-        <v>2137</v>
+        <v>2161</v>
       </c>
       <c r="R4" s="20" t="s">
-        <v>2143</v>
+        <v>2167</v>
       </c>
       <c r="S4" s="20"/>
       <c r="T4" s="20"/>
@@ -15175,19 +14503,19 @@
     </row>
     <row r="5" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="20" t="s">
-        <v>2144</v>
+        <v>2168</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>2145</v>
+        <v>2169</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>2146</v>
+        <v>2170</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>146</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>2147</v>
+        <v>2171</v>
       </c>
       <c r="F5" s="24">
         <v>395</v>
@@ -15211,22 +14539,22 @@
       </c>
       <c r="N5" s="21"/>
       <c r="O5" s="20" t="s">
-        <v>2024</v>
+        <v>1986</v>
       </c>
       <c r="P5" s="20" t="s">
-        <v>2148</v>
+        <v>2172</v>
       </c>
       <c r="Q5" s="20" t="s">
         <v>1578</v>
       </c>
       <c r="R5" s="20" t="s">
-        <v>2149</v>
+        <v>2173</v>
       </c>
       <c r="S5" s="20" t="s">
-        <v>2137</v>
+        <v>2161</v>
       </c>
       <c r="T5" s="20" t="s">
-        <v>2150</v>
+        <v>2174</v>
       </c>
       <c r="U5" s="20"/>
       <c r="V5" s="20"/>
@@ -15245,19 +14573,19 @@
     </row>
     <row r="6" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="20" t="s">
-        <v>2151</v>
+        <v>2175</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>2152</v>
+        <v>2176</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>2153</v>
+        <v>2177</v>
       </c>
       <c r="D6" s="20" t="s">
         <v>146</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>2154</v>
+        <v>2178</v>
       </c>
       <c r="F6" s="24">
         <v>225</v>
@@ -15281,28 +14609,28 @@
       </c>
       <c r="N6" s="21"/>
       <c r="O6" s="20" t="s">
-        <v>2024</v>
+        <v>1986</v>
       </c>
       <c r="P6" s="20" t="s">
-        <v>2155</v>
+        <v>2179</v>
       </c>
       <c r="Q6" s="20" t="s">
-        <v>2156</v>
+        <v>2180</v>
       </c>
       <c r="R6" s="20" t="s">
-        <v>2157</v>
+        <v>2181</v>
       </c>
       <c r="S6" s="20" t="s">
-        <v>2137</v>
+        <v>2161</v>
       </c>
       <c r="T6" s="20" t="s">
-        <v>2158</v>
+        <v>2182</v>
       </c>
       <c r="U6" s="20" t="s">
         <v>936</v>
       </c>
       <c r="V6" s="20" t="s">
-        <v>2159</v>
+        <v>2183</v>
       </c>
       <c r="W6" s="20"/>
       <c r="X6" s="20"/>
@@ -15319,19 +14647,19 @@
     </row>
     <row r="7" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="20" t="s">
-        <v>2160</v>
+        <v>2184</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>2161</v>
+        <v>2185</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>2162</v>
+        <v>2186</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>146</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>2163</v>
+        <v>2187</v>
       </c>
       <c r="F7" s="24">
         <v>35</v>
@@ -15358,13 +14686,13 @@
         <v>208</v>
       </c>
       <c r="P7" s="20" t="s">
-        <v>2164</v>
+        <v>2188</v>
       </c>
       <c r="Q7" s="20" t="s">
         <v>235</v>
       </c>
       <c r="R7" s="20" t="s">
-        <v>2165</v>
+        <v>2189</v>
       </c>
       <c r="S7" s="20"/>
       <c r="T7" s="20"/>
@@ -15385,19 +14713,19 @@
     </row>
     <row r="8" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="20" t="s">
-        <v>2166</v>
+        <v>2190</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>2167</v>
+        <v>2191</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>2168</v>
+        <v>2192</v>
       </c>
       <c r="D8" s="20" t="s">
         <v>146</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>2169</v>
+        <v>2193</v>
       </c>
       <c r="F8" s="24">
         <v>35</v>
@@ -15424,13 +14752,13 @@
         <v>208</v>
       </c>
       <c r="P8" s="20" t="s">
-        <v>2164</v>
+        <v>2188</v>
       </c>
       <c r="Q8" s="20" t="s">
         <v>235</v>
       </c>
       <c r="R8" s="20" t="s">
-        <v>2170</v>
+        <v>2194</v>
       </c>
       <c r="S8" s="20"/>
       <c r="T8" s="20"/>
@@ -15451,19 +14779,19 @@
     </row>
     <row r="9" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="20" t="s">
-        <v>2171</v>
+        <v>2195</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>2172</v>
+        <v>2196</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>2173</v>
+        <v>2197</v>
       </c>
       <c r="D9" s="20" t="s">
         <v>146</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>2174</v>
+        <v>2198</v>
       </c>
       <c r="F9" s="24">
         <v>40</v>
@@ -15489,16 +14817,16 @@
         <v>1</v>
       </c>
       <c r="O9" s="20" t="s">
-        <v>2175</v>
+        <v>2199</v>
       </c>
       <c r="P9" s="20" t="s">
-        <v>2176</v>
+        <v>2200</v>
       </c>
       <c r="Q9" s="20" t="s">
         <v>208</v>
       </c>
       <c r="R9" s="20" t="s">
-        <v>2177</v>
+        <v>2201</v>
       </c>
       <c r="S9" s="20"/>
       <c r="T9" s="20"/>
@@ -15519,19 +14847,19 @@
     </row>
     <row r="10" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="20" t="s">
-        <v>2178</v>
+        <v>2202</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>2179</v>
+        <v>2203</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>2180</v>
+        <v>2204</v>
       </c>
       <c r="D10" s="20" t="s">
         <v>146</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>2181</v>
+        <v>2205</v>
       </c>
       <c r="F10" s="24">
         <v>50</v>
@@ -15557,16 +14885,16 @@
         <v>2</v>
       </c>
       <c r="O10" s="20" t="s">
-        <v>2175</v>
+        <v>2199</v>
       </c>
       <c r="P10" s="20" t="s">
-        <v>2176</v>
+        <v>2200</v>
       </c>
       <c r="Q10" s="20" t="s">
         <v>208</v>
       </c>
       <c r="R10" s="20" t="s">
-        <v>2177</v>
+        <v>2201</v>
       </c>
       <c r="S10" s="20"/>
       <c r="T10" s="20"/>
@@ -15587,19 +14915,19 @@
     </row>
     <row r="11" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="20" t="s">
-        <v>2182</v>
+        <v>2206</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>2183</v>
+        <v>2207</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>2184</v>
+        <v>2208</v>
       </c>
       <c r="D11" s="20" t="s">
         <v>146</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>2185</v>
+        <v>2209</v>
       </c>
       <c r="F11" s="24">
         <v>60</v>
@@ -15625,16 +14953,16 @@
         <v>3</v>
       </c>
       <c r="O11" s="20" t="s">
-        <v>2175</v>
+        <v>2199</v>
       </c>
       <c r="P11" s="20" t="s">
-        <v>2176</v>
+        <v>2200</v>
       </c>
       <c r="Q11" s="20" t="s">
         <v>208</v>
       </c>
       <c r="R11" s="20" t="s">
-        <v>2177</v>
+        <v>2201</v>
       </c>
       <c r="S11" s="20"/>
       <c r="T11" s="20"/>
@@ -15655,19 +14983,19 @@
     </row>
     <row r="12" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="20" t="s">
-        <v>2186</v>
+        <v>2210</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>2187</v>
+        <v>2211</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>2188</v>
+        <v>2212</v>
       </c>
       <c r="D12" s="20" t="s">
         <v>146</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>2189</v>
+        <v>2213</v>
       </c>
       <c r="F12" s="24">
         <v>70</v>
@@ -15693,16 +15021,16 @@
         <v>5</v>
       </c>
       <c r="O12" s="20" t="s">
-        <v>2175</v>
+        <v>2199</v>
       </c>
       <c r="P12" s="20" t="s">
-        <v>2176</v>
+        <v>2200</v>
       </c>
       <c r="Q12" s="20" t="s">
         <v>208</v>
       </c>
       <c r="R12" s="20" t="s">
-        <v>2177</v>
+        <v>2201</v>
       </c>
       <c r="S12" s="20"/>
       <c r="T12" s="20"/>
@@ -15723,19 +15051,19 @@
     </row>
     <row r="13" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="20" t="s">
-        <v>2190</v>
+        <v>2214</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>2191</v>
+        <v>2215</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>2192</v>
+        <v>2216</v>
       </c>
       <c r="D13" s="20" t="s">
         <v>146</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>2193</v>
+        <v>2217</v>
       </c>
       <c r="F13" s="24">
         <v>295</v>
@@ -15759,19 +15087,19 @@
       </c>
       <c r="N13" s="21"/>
       <c r="O13" s="20" t="s">
-        <v>2024</v>
+        <v>1986</v>
       </c>
       <c r="P13" s="20" t="s">
-        <v>2194</v>
+        <v>2218</v>
       </c>
       <c r="Q13" s="20" t="s">
-        <v>2195</v>
+        <v>2219</v>
       </c>
       <c r="R13" s="20" t="s">
         <v>164</v>
       </c>
       <c r="S13" s="20" t="s">
-        <v>2196</v>
+        <v>2220</v>
       </c>
       <c r="T13" s="20" t="s">
         <v>951</v>
@@ -15780,7 +15108,7 @@
         <v>936</v>
       </c>
       <c r="V13" s="20" t="s">
-        <v>2197</v>
+        <v>2221</v>
       </c>
       <c r="W13" s="20"/>
       <c r="X13" s="20"/>
@@ -15797,19 +15125,19 @@
     </row>
     <row r="14" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="20" t="s">
-        <v>2198</v>
+        <v>2222</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>2199</v>
+        <v>2223</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>2200</v>
+        <v>2224</v>
       </c>
       <c r="D14" s="20" t="s">
         <v>146</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>2201</v>
+        <v>2225</v>
       </c>
       <c r="F14" s="24">
         <v>250</v>
@@ -15833,19 +15161,19 @@
       </c>
       <c r="N14" s="21"/>
       <c r="O14" s="20" t="s">
-        <v>2024</v>
+        <v>1986</v>
       </c>
       <c r="P14" s="20" t="s">
-        <v>2194</v>
+        <v>2218</v>
       </c>
       <c r="Q14" s="20" t="s">
-        <v>2195</v>
+        <v>2219</v>
       </c>
       <c r="R14" s="20" t="s">
-        <v>2202</v>
+        <v>2226</v>
       </c>
       <c r="S14" s="20" t="s">
-        <v>2196</v>
+        <v>2220</v>
       </c>
       <c r="T14" s="20" t="s">
         <v>951</v>
@@ -15854,7 +15182,7 @@
         <v>936</v>
       </c>
       <c r="V14" s="20" t="s">
-        <v>2197</v>
+        <v>2221</v>
       </c>
       <c r="W14" s="20"/>
       <c r="X14" s="20"/>
@@ -15871,19 +15199,19 @@
     </row>
     <row r="15" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="20" t="s">
-        <v>2203</v>
+        <v>2227</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>2204</v>
+        <v>2228</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>2205</v>
+        <v>2229</v>
       </c>
       <c r="D15" s="20" t="s">
         <v>146</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>2206</v>
+        <v>2230</v>
       </c>
       <c r="F15" s="24">
         <v>225</v>
@@ -15907,19 +15235,19 @@
       </c>
       <c r="N15" s="21"/>
       <c r="O15" s="20" t="s">
-        <v>2024</v>
+        <v>1986</v>
       </c>
       <c r="P15" s="20" t="s">
-        <v>2194</v>
+        <v>2218</v>
       </c>
       <c r="Q15" s="20" t="s">
-        <v>2195</v>
+        <v>2219</v>
       </c>
       <c r="R15" s="20" t="s">
-        <v>2207</v>
+        <v>2231</v>
       </c>
       <c r="S15" s="20" t="s">
-        <v>2196</v>
+        <v>2220</v>
       </c>
       <c r="T15" s="20" t="s">
         <v>951</v>
@@ -15928,7 +15256,7 @@
         <v>936</v>
       </c>
       <c r="V15" s="20" t="s">
-        <v>2197</v>
+        <v>2221</v>
       </c>
       <c r="W15" s="20"/>
       <c r="X15" s="20"/>
@@ -15945,19 +15273,19 @@
     </row>
     <row r="16" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="20" t="s">
-        <v>2208</v>
+        <v>2232</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>2209</v>
+        <v>2233</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>2210</v>
+        <v>2234</v>
       </c>
       <c r="D16" s="20" t="s">
         <v>146</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>2211</v>
+        <v>2235</v>
       </c>
       <c r="F16" s="24">
         <v>50</v>
@@ -15981,13 +15309,13 @@
       </c>
       <c r="N16" s="21"/>
       <c r="O16" s="20" t="s">
-        <v>2086</v>
+        <v>2110</v>
       </c>
       <c r="P16" s="20" t="s">
-        <v>2212</v>
+        <v>2236</v>
       </c>
       <c r="Q16" s="20" t="s">
-        <v>2196</v>
+        <v>2220</v>
       </c>
       <c r="R16" s="20" t="s">
         <v>951</v>
@@ -16011,19 +15339,19 @@
     </row>
     <row r="17" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="20" t="s">
-        <v>2213</v>
+        <v>2237</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>2214</v>
+        <v>2238</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>2215</v>
+        <v>2239</v>
       </c>
       <c r="D17" s="20" t="s">
         <v>146</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>2216</v>
+        <v>2240</v>
       </c>
       <c r="F17" s="24">
         <v>275</v>
@@ -16047,28 +15375,28 @@
       </c>
       <c r="N17" s="21"/>
       <c r="O17" s="20" t="s">
-        <v>2086</v>
+        <v>2110</v>
       </c>
       <c r="P17" s="20" t="s">
-        <v>2217</v>
+        <v>2241</v>
       </c>
       <c r="Q17" s="20" t="s">
-        <v>2024</v>
+        <v>1986</v>
       </c>
       <c r="R17" s="20" t="s">
-        <v>2218</v>
+        <v>2242</v>
       </c>
       <c r="S17" s="20" t="s">
-        <v>2195</v>
+        <v>2219</v>
       </c>
       <c r="T17" s="20" t="s">
-        <v>2219</v>
+        <v>2243</v>
       </c>
       <c r="U17" s="20" t="s">
         <v>556</v>
       </c>
       <c r="V17" s="20" t="s">
-        <v>2220</v>
+        <v>2244</v>
       </c>
       <c r="W17" s="20"/>
       <c r="X17" s="20"/>
@@ -16085,19 +15413,19 @@
     </row>
     <row r="18" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="20" t="s">
-        <v>2221</v>
+        <v>2245</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>2222</v>
+        <v>2246</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>2223</v>
+        <v>2247</v>
       </c>
       <c r="D18" s="20" t="s">
         <v>146</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>2224</v>
+        <v>2248</v>
       </c>
       <c r="F18" s="24">
         <v>150</v>
@@ -16124,22 +15452,22 @@
         <v>210</v>
       </c>
       <c r="P18" s="20" t="s">
-        <v>2225</v>
+        <v>2249</v>
       </c>
       <c r="Q18" s="20" t="s">
-        <v>2086</v>
+        <v>2110</v>
       </c>
       <c r="R18" s="20" t="s">
-        <v>2226</v>
+        <v>2250</v>
       </c>
       <c r="S18" s="20" t="s">
-        <v>2024</v>
+        <v>1986</v>
       </c>
       <c r="T18" s="20" t="s">
-        <v>2227</v>
+        <v>2251</v>
       </c>
       <c r="U18" s="20" t="s">
-        <v>2196</v>
+        <v>2220</v>
       </c>
       <c r="V18" s="20" t="s">
         <v>951</v>
@@ -16159,19 +15487,19 @@
     </row>
     <row r="19" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="20" t="s">
-        <v>2228</v>
+        <v>2252</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>2229</v>
+        <v>2253</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>2230</v>
+        <v>2254</v>
       </c>
       <c r="D19" s="20" t="s">
         <v>146</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>2231</v>
+        <v>2255</v>
       </c>
       <c r="F19" s="24">
         <v>1995</v>
@@ -16195,28 +15523,28 @@
       </c>
       <c r="N19" s="21"/>
       <c r="O19" s="20" t="s">
-        <v>2086</v>
+        <v>2110</v>
       </c>
       <c r="P19" s="20" t="s">
-        <v>2232</v>
+        <v>2256</v>
       </c>
       <c r="Q19" s="20" t="s">
         <v>950</v>
       </c>
       <c r="R19" s="20" t="s">
-        <v>2233</v>
+        <v>2257</v>
       </c>
       <c r="S19" s="20" t="s">
         <v>298</v>
       </c>
       <c r="T19" s="20" t="s">
-        <v>2234</v>
+        <v>2258</v>
       </c>
       <c r="U19" s="20" t="s">
-        <v>2235</v>
+        <v>2259</v>
       </c>
       <c r="V19" s="20" t="s">
-        <v>2236</v>
+        <v>2260</v>
       </c>
       <c r="W19" s="20"/>
       <c r="X19" s="20"/>
@@ -16233,19 +15561,19 @@
     </row>
     <row r="20" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="20" t="s">
-        <v>2237</v>
+        <v>2261</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>2238</v>
+        <v>2262</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>2239</v>
+        <v>2263</v>
       </c>
       <c r="D20" s="20" t="s">
         <v>146</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>2240</v>
+        <v>2264</v>
       </c>
       <c r="F20" s="24">
         <v>1250</v>
@@ -16269,28 +15597,28 @@
       </c>
       <c r="N20" s="21"/>
       <c r="O20" s="20" t="s">
-        <v>2086</v>
+        <v>2110</v>
       </c>
       <c r="P20" s="20" t="s">
-        <v>2232</v>
+        <v>2256</v>
       </c>
       <c r="Q20" s="20" t="s">
         <v>950</v>
       </c>
       <c r="R20" s="20" t="s">
-        <v>2233</v>
+        <v>2257</v>
       </c>
       <c r="S20" s="20" t="s">
         <v>298</v>
       </c>
       <c r="T20" s="20" t="s">
-        <v>2241</v>
+        <v>2265</v>
       </c>
       <c r="U20" s="20" t="s">
-        <v>2235</v>
+        <v>2259</v>
       </c>
       <c r="V20" s="20" t="s">
-        <v>2236</v>
+        <v>2260</v>
       </c>
       <c r="W20" s="20"/>
       <c r="X20" s="20"/>
@@ -16307,19 +15635,19 @@
     </row>
     <row r="21" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="20" t="s">
-        <v>2242</v>
+        <v>2266</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>2243</v>
+        <v>2267</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>2244</v>
+        <v>2268</v>
       </c>
       <c r="D21" s="20" t="s">
         <v>146</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>2245</v>
+        <v>2269</v>
       </c>
       <c r="F21" s="24">
         <v>950</v>
@@ -16343,16 +15671,16 @@
       </c>
       <c r="N21" s="21"/>
       <c r="O21" s="20" t="s">
-        <v>2086</v>
+        <v>2110</v>
       </c>
       <c r="P21" s="20" t="s">
-        <v>2246</v>
+        <v>2270</v>
       </c>
       <c r="Q21" s="20" t="s">
         <v>298</v>
       </c>
       <c r="R21" s="20" t="s">
-        <v>2247</v>
+        <v>2271</v>
       </c>
       <c r="S21" s="20"/>
       <c r="T21" s="20"/>
@@ -16373,19 +15701,19 @@
     </row>
     <row r="22" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="20" t="s">
-        <v>2248</v>
+        <v>2272</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>2249</v>
+        <v>2273</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>2250</v>
+        <v>2274</v>
       </c>
       <c r="D22" s="20" t="s">
         <v>84</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>2251</v>
+        <v>2275</v>
       </c>
       <c r="F22" s="24">
         <v>1525</v>
@@ -16409,34 +15737,34 @@
       </c>
       <c r="N22" s="21"/>
       <c r="O22" s="20" t="s">
-        <v>2024</v>
+        <v>1986</v>
       </c>
       <c r="P22" s="20" t="s">
-        <v>2252</v>
+        <v>2276</v>
       </c>
       <c r="Q22" s="20" t="s">
         <v>936</v>
       </c>
       <c r="R22" s="20" t="s">
-        <v>2253</v>
+        <v>2277</v>
       </c>
       <c r="S22" s="20" t="s">
         <v>1864</v>
       </c>
       <c r="T22" s="20" t="s">
-        <v>2254</v>
+        <v>2278</v>
       </c>
       <c r="U22" s="20" t="s">
         <v>1716</v>
       </c>
       <c r="V22" s="20" t="s">
-        <v>2255</v>
+        <v>2279</v>
       </c>
       <c r="W22" s="20" t="s">
         <v>1578</v>
       </c>
       <c r="X22" s="20" t="s">
-        <v>2256</v>
+        <v>2280</v>
       </c>
       <c r="Y22" s="20"/>
       <c r="Z22" s="20"/>
@@ -16451,19 +15779,19 @@
     </row>
     <row r="23" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="20" t="s">
-        <v>2257</v>
+        <v>2281</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>2258</v>
+        <v>2282</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>2259</v>
+        <v>2283</v>
       </c>
       <c r="D23" s="20" t="s">
         <v>84</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>2260</v>
+        <v>2284</v>
       </c>
       <c r="F23" s="24">
         <v>1595</v>
@@ -16487,28 +15815,28 @@
       </c>
       <c r="N23" s="21"/>
       <c r="O23" s="20" t="s">
-        <v>2024</v>
+        <v>1986</v>
       </c>
       <c r="P23" s="20" t="s">
-        <v>2261</v>
+        <v>2285</v>
       </c>
       <c r="Q23" s="20" t="s">
-        <v>2262</v>
+        <v>2286</v>
       </c>
       <c r="R23" s="20" t="s">
-        <v>2263</v>
+        <v>2287</v>
       </c>
       <c r="S23" s="20" t="s">
         <v>936</v>
       </c>
       <c r="T23" s="20" t="s">
-        <v>2264</v>
+        <v>2288</v>
       </c>
       <c r="U23" s="20" t="s">
-        <v>2235</v>
+        <v>2259</v>
       </c>
       <c r="V23" s="20" t="s">
-        <v>2265</v>
+        <v>2289</v>
       </c>
       <c r="W23" s="20"/>
       <c r="X23" s="20"/>
@@ -16525,19 +15853,19 @@
     </row>
     <row r="24" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="20" t="s">
-        <v>2266</v>
+        <v>2290</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>2267</v>
+        <v>2291</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>2268</v>
+        <v>2292</v>
       </c>
       <c r="D24" s="20" t="s">
         <v>84</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>2269</v>
+        <v>2293</v>
       </c>
       <c r="F24" s="24">
         <v>1995</v>
@@ -16561,16 +15889,16 @@
       </c>
       <c r="N24" s="21"/>
       <c r="O24" s="20" t="s">
-        <v>2175</v>
+        <v>2199</v>
       </c>
       <c r="P24" s="20" t="s">
-        <v>2270</v>
+        <v>2294</v>
       </c>
       <c r="Q24" s="20" t="s">
         <v>936</v>
       </c>
       <c r="R24" s="20" t="s">
-        <v>2271</v>
+        <v>2295</v>
       </c>
       <c r="S24" s="20"/>
       <c r="T24" s="20"/>
@@ -16591,19 +15919,19 @@
     </row>
     <row r="25" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="20" t="s">
-        <v>2272</v>
+        <v>2296</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>2273</v>
+        <v>2297</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>2274</v>
+        <v>2298</v>
       </c>
       <c r="D25" s="20" t="s">
         <v>84</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>2275</v>
+        <v>2299</v>
       </c>
       <c r="F25" s="24">
         <v>350</v>
@@ -16632,31 +15960,31 @@
         <v>210</v>
       </c>
       <c r="P25" s="20" t="s">
-        <v>2276</v>
+        <v>2300</v>
       </c>
       <c r="Q25" s="20" t="s">
-        <v>2175</v>
+        <v>2199</v>
       </c>
       <c r="R25" s="20" t="s">
-        <v>2277</v>
+        <v>2301</v>
       </c>
       <c r="S25" s="20" t="s">
         <v>208</v>
       </c>
       <c r="T25" s="20" t="s">
-        <v>2278</v>
+        <v>2302</v>
       </c>
       <c r="U25" s="20" t="s">
-        <v>2279</v>
+        <v>2303</v>
       </c>
       <c r="V25" s="20" t="s">
-        <v>2280</v>
+        <v>2304</v>
       </c>
       <c r="W25" s="20" t="s">
-        <v>2281</v>
+        <v>2305</v>
       </c>
       <c r="X25" s="20" t="s">
-        <v>2282</v>
+        <v>2306</v>
       </c>
       <c r="Y25" s="20"/>
       <c r="Z25" s="20"/>
@@ -16671,19 +15999,19 @@
     </row>
     <row r="26" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="20" t="s">
-        <v>2283</v>
+        <v>2307</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>2284</v>
+        <v>2308</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>2285</v>
+        <v>2309</v>
       </c>
       <c r="D26" s="20" t="s">
         <v>84</v>
       </c>
       <c r="E26" s="20" t="s">
-        <v>2286</v>
+        <v>2310</v>
       </c>
       <c r="F26" s="24">
         <v>225</v>
@@ -16712,31 +16040,31 @@
         <v>210</v>
       </c>
       <c r="P26" s="20" t="s">
-        <v>2276</v>
+        <v>2300</v>
       </c>
       <c r="Q26" s="20" t="s">
-        <v>2175</v>
+        <v>2199</v>
       </c>
       <c r="R26" s="20" t="s">
-        <v>2176</v>
+        <v>2200</v>
       </c>
       <c r="S26" s="20" t="s">
         <v>208</v>
       </c>
       <c r="T26" s="20" t="s">
-        <v>2278</v>
+        <v>2302</v>
       </c>
       <c r="U26" s="20" t="s">
-        <v>2279</v>
+        <v>2303</v>
       </c>
       <c r="V26" s="20" t="s">
-        <v>2280</v>
+        <v>2304</v>
       </c>
       <c r="W26" s="20" t="s">
-        <v>2281</v>
+        <v>2305</v>
       </c>
       <c r="X26" s="20" t="s">
-        <v>2282</v>
+        <v>2306</v>
       </c>
       <c r="Y26" s="20"/>
       <c r="Z26" s="20"/>
@@ -16751,19 +16079,19 @@
     </row>
     <row r="27" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="20" t="s">
-        <v>2287</v>
+        <v>2311</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>2288</v>
+        <v>2312</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>2289</v>
+        <v>2313</v>
       </c>
       <c r="D27" s="20" t="s">
         <v>84</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>2290</v>
+        <v>2314</v>
       </c>
       <c r="F27" s="24">
         <v>265</v>
@@ -16792,31 +16120,31 @@
         <v>210</v>
       </c>
       <c r="P27" s="20" t="s">
-        <v>2276</v>
+        <v>2300</v>
       </c>
       <c r="Q27" s="20" t="s">
-        <v>2175</v>
+        <v>2199</v>
       </c>
       <c r="R27" s="20" t="s">
-        <v>2176</v>
+        <v>2200</v>
       </c>
       <c r="S27" s="20" t="s">
         <v>208</v>
       </c>
       <c r="T27" s="20" t="s">
-        <v>2278</v>
+        <v>2302</v>
       </c>
       <c r="U27" s="20" t="s">
-        <v>2279</v>
+        <v>2303</v>
       </c>
       <c r="V27" s="20" t="s">
-        <v>2280</v>
+        <v>2304</v>
       </c>
       <c r="W27" s="20" t="s">
-        <v>2281</v>
+        <v>2305</v>
       </c>
       <c r="X27" s="20" t="s">
-        <v>2282</v>
+        <v>2306</v>
       </c>
       <c r="Y27" s="20"/>
       <c r="Z27" s="20"/>
@@ -16831,19 +16159,19 @@
     </row>
     <row r="28" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="20" t="s">
-        <v>2291</v>
+        <v>2315</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>2292</v>
+        <v>2316</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>2293</v>
+        <v>2317</v>
       </c>
       <c r="D28" s="20" t="s">
         <v>84</v>
       </c>
       <c r="E28" s="20" t="s">
-        <v>2294</v>
+        <v>2318</v>
       </c>
       <c r="F28" s="24">
         <v>175</v>
@@ -16872,31 +16200,31 @@
         <v>210</v>
       </c>
       <c r="P28" s="20" t="s">
-        <v>2276</v>
+        <v>2300</v>
       </c>
       <c r="Q28" s="20" t="s">
-        <v>2175</v>
+        <v>2199</v>
       </c>
       <c r="R28" s="20" t="s">
-        <v>2176</v>
+        <v>2200</v>
       </c>
       <c r="S28" s="20" t="s">
         <v>208</v>
       </c>
       <c r="T28" s="20" t="s">
-        <v>2278</v>
+        <v>2302</v>
       </c>
       <c r="U28" s="20" t="s">
-        <v>2279</v>
+        <v>2303</v>
       </c>
       <c r="V28" s="20" t="s">
-        <v>2280</v>
+        <v>2304</v>
       </c>
       <c r="W28" s="20" t="s">
-        <v>2281</v>
+        <v>2305</v>
       </c>
       <c r="X28" s="20" t="s">
-        <v>2282</v>
+        <v>2306</v>
       </c>
       <c r="Y28" s="20"/>
       <c r="Z28" s="20"/>
@@ -16911,19 +16239,19 @@
     </row>
     <row r="29" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="20" t="s">
-        <v>2295</v>
+        <v>2319</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>2296</v>
+        <v>2320</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>2297</v>
+        <v>2321</v>
       </c>
       <c r="D29" s="20" t="s">
         <v>84</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>2298</v>
+        <v>2322</v>
       </c>
       <c r="F29" s="24">
         <v>150</v>
@@ -16952,31 +16280,31 @@
         <v>210</v>
       </c>
       <c r="P29" s="20" t="s">
-        <v>2276</v>
+        <v>2300</v>
       </c>
       <c r="Q29" s="20" t="s">
-        <v>2175</v>
+        <v>2199</v>
       </c>
       <c r="R29" s="20" t="s">
-        <v>2176</v>
+        <v>2200</v>
       </c>
       <c r="S29" s="20" t="s">
         <v>208</v>
       </c>
       <c r="T29" s="20" t="s">
-        <v>2278</v>
+        <v>2302</v>
       </c>
       <c r="U29" s="20" t="s">
-        <v>2279</v>
+        <v>2303</v>
       </c>
       <c r="V29" s="20" t="s">
-        <v>2280</v>
+        <v>2304</v>
       </c>
       <c r="W29" s="20" t="s">
-        <v>2281</v>
+        <v>2305</v>
       </c>
       <c r="X29" s="20" t="s">
-        <v>2282</v>
+        <v>2306</v>
       </c>
       <c r="Y29" s="20"/>
       <c r="Z29" s="20"/>
@@ -16991,19 +16319,19 @@
     </row>
     <row r="30" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="20" t="s">
-        <v>2299</v>
+        <v>2323</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>2300</v>
+        <v>2324</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>2301</v>
+        <v>2325</v>
       </c>
       <c r="D30" s="20" t="s">
         <v>84</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>2302</v>
+        <v>2326</v>
       </c>
       <c r="F30" s="24">
         <v>150</v>
@@ -17032,31 +16360,31 @@
         <v>210</v>
       </c>
       <c r="P30" s="20" t="s">
-        <v>2276</v>
+        <v>2300</v>
       </c>
       <c r="Q30" s="20" t="s">
-        <v>2175</v>
+        <v>2199</v>
       </c>
       <c r="R30" s="20" t="s">
-        <v>2176</v>
+        <v>2200</v>
       </c>
       <c r="S30" s="20" t="s">
         <v>208</v>
       </c>
       <c r="T30" s="20" t="s">
-        <v>2278</v>
+        <v>2302</v>
       </c>
       <c r="U30" s="20" t="s">
-        <v>2279</v>
+        <v>2303</v>
       </c>
       <c r="V30" s="20" t="s">
-        <v>2280</v>
+        <v>2304</v>
       </c>
       <c r="W30" s="20" t="s">
-        <v>2281</v>
+        <v>2305</v>
       </c>
       <c r="X30" s="20" t="s">
-        <v>2282</v>
+        <v>2306</v>
       </c>
       <c r="Y30" s="20"/>
       <c r="Z30" s="20"/>
@@ -17071,19 +16399,19 @@
     </row>
     <row r="31" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="20" t="s">
-        <v>2303</v>
+        <v>2327</v>
       </c>
       <c r="B31" s="20" t="s">
-        <v>2304</v>
+        <v>2328</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>2305</v>
+        <v>2329</v>
       </c>
       <c r="D31" s="20" t="s">
         <v>84</v>
       </c>
       <c r="E31" s="20" t="s">
-        <v>2306</v>
+        <v>2330</v>
       </c>
       <c r="F31" s="24">
         <v>95</v>
@@ -17110,19 +16438,19 @@
         <v>210</v>
       </c>
       <c r="P31" s="20" t="s">
-        <v>2307</v>
+        <v>2331</v>
       </c>
       <c r="Q31" s="20" t="s">
         <v>235</v>
       </c>
       <c r="R31" s="20" t="s">
-        <v>2308</v>
+        <v>2332</v>
       </c>
       <c r="S31" s="20" t="s">
-        <v>2279</v>
+        <v>2303</v>
       </c>
       <c r="T31" s="20" t="s">
-        <v>2309</v>
+        <v>2333</v>
       </c>
       <c r="U31" s="20"/>
       <c r="V31" s="20"/>
@@ -17141,19 +16469,19 @@
     </row>
     <row r="32" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="20" t="s">
-        <v>2310</v>
+        <v>2334</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>2311</v>
+        <v>2335</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>2312</v>
+        <v>2336</v>
       </c>
       <c r="D32" s="20" t="s">
         <v>84</v>
       </c>
       <c r="E32" s="20" t="s">
-        <v>2313</v>
+        <v>2337</v>
       </c>
       <c r="F32" s="24">
         <v>95</v>
@@ -17180,19 +16508,19 @@
         <v>210</v>
       </c>
       <c r="P32" s="20" t="s">
-        <v>2307</v>
+        <v>2331</v>
       </c>
       <c r="Q32" s="20" t="s">
         <v>235</v>
       </c>
       <c r="R32" s="20" t="s">
-        <v>2314</v>
+        <v>2338</v>
       </c>
       <c r="S32" s="20" t="s">
-        <v>2279</v>
+        <v>2303</v>
       </c>
       <c r="T32" s="20" t="s">
-        <v>2309</v>
+        <v>2333</v>
       </c>
       <c r="U32" s="20"/>
       <c r="V32" s="20"/>
@@ -17211,19 +16539,19 @@
     </row>
     <row r="33" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="20" t="s">
-        <v>2315</v>
+        <v>2339</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>2316</v>
+        <v>2340</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>2317</v>
+        <v>2341</v>
       </c>
       <c r="D33" s="20" t="s">
         <v>84</v>
       </c>
       <c r="E33" s="20" t="s">
-        <v>2318</v>
+        <v>2342</v>
       </c>
       <c r="F33" s="24">
         <v>650</v>
@@ -17252,37 +16580,37 @@
         <v>210</v>
       </c>
       <c r="P33" s="20" t="s">
-        <v>2319</v>
+        <v>2343</v>
       </c>
       <c r="Q33" s="20" t="s">
-        <v>2175</v>
+        <v>2199</v>
       </c>
       <c r="R33" s="20" t="s">
-        <v>2277</v>
+        <v>2301</v>
       </c>
       <c r="S33" s="20" t="s">
         <v>208</v>
       </c>
       <c r="T33" s="20" t="s">
-        <v>2320</v>
+        <v>2344</v>
       </c>
       <c r="U33" s="20" t="s">
-        <v>2279</v>
+        <v>2303</v>
       </c>
       <c r="V33" s="20" t="s">
-        <v>2321</v>
+        <v>2345</v>
       </c>
       <c r="W33" s="20" t="s">
-        <v>2281</v>
+        <v>2305</v>
       </c>
       <c r="X33" s="20" t="s">
-        <v>2322</v>
+        <v>2346</v>
       </c>
       <c r="Y33" s="20" t="s">
         <v>1862</v>
       </c>
       <c r="Z33" s="20" t="s">
-        <v>2323</v>
+        <v>2347</v>
       </c>
       <c r="AA33" s="20"/>
       <c r="AB33" s="20"/>
@@ -17295,19 +16623,19 @@
     </row>
     <row r="34" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="20" t="s">
-        <v>2324</v>
+        <v>2348</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>2325</v>
+        <v>2349</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>2326</v>
+        <v>2350</v>
       </c>
       <c r="D34" s="20" t="s">
         <v>84</v>
       </c>
       <c r="E34" s="20" t="s">
-        <v>2327</v>
+        <v>2351</v>
       </c>
       <c r="F34" s="24">
         <v>595</v>
@@ -17336,37 +16664,37 @@
         <v>210</v>
       </c>
       <c r="P34" s="20" t="s">
-        <v>2319</v>
+        <v>2343</v>
       </c>
       <c r="Q34" s="20" t="s">
-        <v>2175</v>
+        <v>2199</v>
       </c>
       <c r="R34" s="20" t="s">
-        <v>2277</v>
+        <v>2301</v>
       </c>
       <c r="S34" s="20" t="s">
         <v>208</v>
       </c>
       <c r="T34" s="20" t="s">
-        <v>2320</v>
+        <v>2344</v>
       </c>
       <c r="U34" s="20" t="s">
-        <v>2279</v>
+        <v>2303</v>
       </c>
       <c r="V34" s="20" t="s">
-        <v>2321</v>
+        <v>2345</v>
       </c>
       <c r="W34" s="20" t="s">
-        <v>2281</v>
+        <v>2305</v>
       </c>
       <c r="X34" s="20" t="s">
-        <v>2322</v>
+        <v>2346</v>
       </c>
       <c r="Y34" s="20" t="s">
         <v>1862</v>
       </c>
       <c r="Z34" s="20" t="s">
-        <v>2323</v>
+        <v>2347</v>
       </c>
       <c r="AA34" s="20"/>
       <c r="AB34" s="20"/>
@@ -17379,19 +16707,19 @@
     </row>
     <row r="35" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="20" t="s">
-        <v>2328</v>
+        <v>2352</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>2329</v>
+        <v>2353</v>
       </c>
       <c r="C35" s="20" t="s">
-        <v>2330</v>
+        <v>2354</v>
       </c>
       <c r="D35" s="20" t="s">
         <v>84</v>
       </c>
       <c r="E35" s="20" t="s">
-        <v>2331</v>
+        <v>2355</v>
       </c>
       <c r="F35" s="24">
         <v>325</v>
@@ -17420,37 +16748,37 @@
         <v>210</v>
       </c>
       <c r="P35" s="20" t="s">
-        <v>2319</v>
+        <v>2343</v>
       </c>
       <c r="Q35" s="20" t="s">
-        <v>2175</v>
+        <v>2199</v>
       </c>
       <c r="R35" s="20" t="s">
-        <v>2176</v>
+        <v>2200</v>
       </c>
       <c r="S35" s="20" t="s">
         <v>208</v>
       </c>
       <c r="T35" s="20" t="s">
-        <v>2320</v>
+        <v>2344</v>
       </c>
       <c r="U35" s="20" t="s">
-        <v>2279</v>
+        <v>2303</v>
       </c>
       <c r="V35" s="20" t="s">
-        <v>2321</v>
+        <v>2345</v>
       </c>
       <c r="W35" s="20" t="s">
-        <v>2281</v>
+        <v>2305</v>
       </c>
       <c r="X35" s="20" t="s">
-        <v>2322</v>
+        <v>2346</v>
       </c>
       <c r="Y35" s="20" t="s">
         <v>1862</v>
       </c>
       <c r="Z35" s="20" t="s">
-        <v>2323</v>
+        <v>2347</v>
       </c>
       <c r="AA35" s="20"/>
       <c r="AB35" s="20"/>
@@ -17463,19 +16791,19 @@
     </row>
     <row r="36" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="20" t="s">
-        <v>2332</v>
+        <v>2356</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>2333</v>
+        <v>2357</v>
       </c>
       <c r="C36" s="20" t="s">
-        <v>2334</v>
+        <v>2358</v>
       </c>
       <c r="D36" s="20" t="s">
         <v>84</v>
       </c>
       <c r="E36" s="20" t="s">
-        <v>2335</v>
+        <v>2359</v>
       </c>
       <c r="F36" s="24">
         <v>275</v>
@@ -17504,37 +16832,37 @@
         <v>210</v>
       </c>
       <c r="P36" s="20" t="s">
-        <v>2319</v>
+        <v>2343</v>
       </c>
       <c r="Q36" s="20" t="s">
-        <v>2175</v>
+        <v>2199</v>
       </c>
       <c r="R36" s="20" t="s">
-        <v>2176</v>
+        <v>2200</v>
       </c>
       <c r="S36" s="20" t="s">
         <v>208</v>
       </c>
       <c r="T36" s="20" t="s">
-        <v>2320</v>
+        <v>2344</v>
       </c>
       <c r="U36" s="20" t="s">
-        <v>2279</v>
+        <v>2303</v>
       </c>
       <c r="V36" s="20" t="s">
-        <v>2321</v>
+        <v>2345</v>
       </c>
       <c r="W36" s="20" t="s">
-        <v>2281</v>
+        <v>2305</v>
       </c>
       <c r="X36" s="20" t="s">
-        <v>2322</v>
+        <v>2346</v>
       </c>
       <c r="Y36" s="20" t="s">
         <v>1862</v>
       </c>
       <c r="Z36" s="20" t="s">
-        <v>2323</v>
+        <v>2347</v>
       </c>
       <c r="AA36" s="20"/>
       <c r="AB36" s="20"/>
@@ -17547,19 +16875,19 @@
     </row>
     <row r="37" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="20" t="s">
-        <v>2336</v>
+        <v>2360</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>2337</v>
+        <v>2361</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>2338</v>
+        <v>2362</v>
       </c>
       <c r="D37" s="20" t="s">
         <v>84</v>
       </c>
       <c r="E37" s="20" t="s">
-        <v>2339</v>
+        <v>2363</v>
       </c>
       <c r="F37" s="24">
         <v>150</v>
@@ -17588,19 +16916,19 @@
         <v>210</v>
       </c>
       <c r="P37" s="20" t="s">
-        <v>2340</v>
+        <v>2364</v>
       </c>
       <c r="Q37" s="20" t="s">
         <v>208</v>
       </c>
       <c r="R37" s="20" t="s">
-        <v>2341</v>
+        <v>2365</v>
       </c>
       <c r="S37" s="20" t="s">
-        <v>2279</v>
+        <v>2303</v>
       </c>
       <c r="T37" s="20" t="s">
-        <v>2321</v>
+        <v>2345</v>
       </c>
       <c r="U37" s="20"/>
       <c r="V37" s="20"/>
@@ -17619,19 +16947,19 @@
     </row>
     <row r="38" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="20" t="s">
-        <v>2342</v>
+        <v>2366</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>2343</v>
+        <v>2367</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>2344</v>
+        <v>2368</v>
       </c>
       <c r="D38" s="20" t="s">
         <v>84</v>
       </c>
       <c r="E38" s="20" t="s">
-        <v>2345</v>
+        <v>2369</v>
       </c>
       <c r="F38" s="24">
         <v>175</v>
@@ -17660,19 +16988,19 @@
         <v>210</v>
       </c>
       <c r="P38" s="20" t="s">
-        <v>2340</v>
+        <v>2364</v>
       </c>
       <c r="Q38" s="20" t="s">
         <v>208</v>
       </c>
       <c r="R38" s="20" t="s">
-        <v>2341</v>
+        <v>2365</v>
       </c>
       <c r="S38" s="20" t="s">
-        <v>2279</v>
+        <v>2303</v>
       </c>
       <c r="T38" s="20" t="s">
-        <v>2321</v>
+        <v>2345</v>
       </c>
       <c r="U38" s="20"/>
       <c r="V38" s="20"/>
@@ -17691,19 +17019,19 @@
     </row>
     <row r="39" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="20" t="s">
-        <v>2346</v>
+        <v>2370</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>2347</v>
+        <v>2371</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>2348</v>
+        <v>2372</v>
       </c>
       <c r="D39" s="20" t="s">
         <v>84</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>2349</v>
+        <v>2373</v>
       </c>
       <c r="F39" s="24">
         <v>275</v>
@@ -17730,13 +17058,13 @@
         <v>208</v>
       </c>
       <c r="P39" s="20" t="s">
-        <v>2350</v>
+        <v>2374</v>
       </c>
       <c r="Q39" s="20" t="s">
         <v>936</v>
       </c>
       <c r="R39" s="20" t="s">
-        <v>2351</v>
+        <v>2375</v>
       </c>
       <c r="S39" s="20"/>
       <c r="T39" s="20"/>
@@ -17757,19 +17085,19 @@
     </row>
     <row r="40" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="20" t="s">
-        <v>2352</v>
+        <v>2376</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>2353</v>
+        <v>2377</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>2354</v>
+        <v>2378</v>
       </c>
       <c r="D40" s="20" t="s">
         <v>84</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>2355</v>
+        <v>2379</v>
       </c>
       <c r="F40" s="24">
         <v>325</v>
@@ -17796,13 +17124,13 @@
         <v>210</v>
       </c>
       <c r="P40" s="20" t="s">
-        <v>2356</v>
+        <v>2380</v>
       </c>
       <c r="Q40" s="20" t="s">
-        <v>2024</v>
+        <v>1986</v>
       </c>
       <c r="R40" s="20" t="s">
-        <v>2357</v>
+        <v>2381</v>
       </c>
       <c r="S40" s="20"/>
       <c r="T40" s="20"/>
@@ -17823,19 +17151,19 @@
     </row>
     <row r="41" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="20" t="s">
-        <v>2358</v>
+        <v>2382</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>2359</v>
+        <v>2383</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>2360</v>
+        <v>2384</v>
       </c>
       <c r="D41" s="20" t="s">
         <v>84</v>
       </c>
       <c r="E41" s="20" t="s">
-        <v>2361</v>
+        <v>2385</v>
       </c>
       <c r="F41" s="24">
         <v>325</v>
@@ -17862,13 +17190,13 @@
         <v>210</v>
       </c>
       <c r="P41" s="20" t="s">
-        <v>2356</v>
+        <v>2380</v>
       </c>
       <c r="Q41" s="20" t="s">
         <v>1864</v>
       </c>
       <c r="R41" s="20" t="s">
-        <v>2362</v>
+        <v>2386</v>
       </c>
       <c r="S41" s="20"/>
       <c r="T41" s="20"/>
@@ -17889,19 +17217,19 @@
     </row>
     <row r="42" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="20" t="s">
-        <v>2363</v>
+        <v>2387</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>2364</v>
+        <v>2388</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>2365</v>
+        <v>2389</v>
       </c>
       <c r="D42" s="20" t="s">
         <v>84</v>
       </c>
       <c r="E42" s="20" t="s">
-        <v>2366</v>
+        <v>2390</v>
       </c>
       <c r="F42" s="24">
         <v>950</v>
@@ -17928,13 +17256,13 @@
         <v>298</v>
       </c>
       <c r="P42" s="20" t="s">
-        <v>2367</v>
+        <v>2391</v>
       </c>
       <c r="Q42" s="20" t="s">
         <v>950</v>
       </c>
       <c r="R42" s="20" t="s">
-        <v>2368</v>
+        <v>2392</v>
       </c>
       <c r="S42" s="20"/>
       <c r="T42" s="20"/>
@@ -17955,19 +17283,19 @@
     </row>
     <row r="43" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="20" t="s">
-        <v>2369</v>
+        <v>2393</v>
       </c>
       <c r="B43" s="20" t="s">
-        <v>2370</v>
+        <v>2394</v>
       </c>
       <c r="C43" s="20" t="s">
-        <v>2371</v>
+        <v>2395</v>
       </c>
       <c r="D43" s="20" t="s">
         <v>84</v>
       </c>
       <c r="E43" s="20" t="s">
-        <v>2372</v>
+        <v>2396</v>
       </c>
       <c r="F43" s="24">
         <v>775</v>
@@ -17994,13 +17322,13 @@
         <v>298</v>
       </c>
       <c r="P43" s="20" t="s">
-        <v>2373</v>
+        <v>2397</v>
       </c>
       <c r="Q43" s="20" t="s">
         <v>950</v>
       </c>
       <c r="R43" s="20" t="s">
-        <v>2368</v>
+        <v>2392</v>
       </c>
       <c r="S43" s="20"/>
       <c r="T43" s="20"/>
@@ -18021,19 +17349,19 @@
     </row>
     <row r="44" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="20" t="s">
-        <v>2374</v>
+        <v>2398</v>
       </c>
       <c r="B44" s="20" t="s">
-        <v>2375</v>
+        <v>2399</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>2376</v>
+        <v>2400</v>
       </c>
       <c r="D44" s="20" t="s">
         <v>84</v>
       </c>
       <c r="E44" s="20" t="s">
-        <v>2377</v>
+        <v>2401</v>
       </c>
       <c r="F44" s="24">
         <v>250</v>
@@ -18057,28 +17385,28 @@
       </c>
       <c r="N44" s="21"/>
       <c r="O44" s="20" t="s">
-        <v>2024</v>
+        <v>1986</v>
       </c>
       <c r="P44" s="20" t="s">
-        <v>2378</v>
+        <v>2402</v>
       </c>
       <c r="Q44" s="20" t="s">
-        <v>2195</v>
+        <v>2219</v>
       </c>
       <c r="R44" s="20" t="s">
-        <v>2219</v>
+        <v>2243</v>
       </c>
       <c r="S44" s="20" t="s">
         <v>556</v>
       </c>
       <c r="T44" s="20" t="s">
-        <v>2379</v>
+        <v>2403</v>
       </c>
       <c r="U44" s="20" t="s">
         <v>936</v>
       </c>
       <c r="V44" s="20" t="s">
-        <v>2380</v>
+        <v>2404</v>
       </c>
       <c r="W44" s="20"/>
       <c r="X44" s="20"/>
@@ -18095,19 +17423,19 @@
     </row>
     <row r="45" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="20" t="s">
-        <v>2381</v>
+        <v>2405</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>2382</v>
+        <v>2406</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>2383</v>
+        <v>2407</v>
       </c>
       <c r="D45" s="20" t="s">
         <v>84</v>
       </c>
       <c r="E45" s="20" t="s">
-        <v>2384</v>
+        <v>2408</v>
       </c>
       <c r="F45" s="24">
         <v>250</v>
@@ -18131,28 +17459,28 @@
       </c>
       <c r="N45" s="21"/>
       <c r="O45" s="20" t="s">
-        <v>2024</v>
+        <v>1986</v>
       </c>
       <c r="P45" s="20" t="s">
-        <v>2378</v>
+        <v>2402</v>
       </c>
       <c r="Q45" s="20" t="s">
-        <v>2195</v>
+        <v>2219</v>
       </c>
       <c r="R45" s="20" t="s">
-        <v>2385</v>
+        <v>2409</v>
       </c>
       <c r="S45" s="20" t="s">
         <v>556</v>
       </c>
       <c r="T45" s="20" t="s">
-        <v>2379</v>
+        <v>2403</v>
       </c>
       <c r="U45" s="20" t="s">
         <v>936</v>
       </c>
       <c r="V45" s="20" t="s">
-        <v>2380</v>
+        <v>2404</v>
       </c>
       <c r="W45" s="20"/>
       <c r="X45" s="20"/>
@@ -18169,19 +17497,19 @@
     </row>
     <row r="46" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="20" t="s">
-        <v>2386</v>
+        <v>2410</v>
       </c>
       <c r="B46" s="20" t="s">
-        <v>2387</v>
+        <v>2411</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>2388</v>
+        <v>2412</v>
       </c>
       <c r="D46" s="20" t="s">
         <v>153</v>
       </c>
       <c r="E46" s="20" t="s">
-        <v>2389</v>
+        <v>2413</v>
       </c>
       <c r="F46" s="24">
         <v>595</v>
@@ -18205,49 +17533,53 @@
       </c>
       <c r="N46" s="21"/>
       <c r="O46" s="20" t="s">
-        <v>2086</v>
+        <v>2110</v>
       </c>
       <c r="P46" s="20" t="s">
-        <v>2390</v>
+        <v>2414</v>
       </c>
       <c r="Q46" s="20" t="s">
-        <v>2024</v>
+        <v>1986</v>
       </c>
       <c r="R46" s="20" t="s">
-        <v>2391</v>
+        <v>2415</v>
       </c>
       <c r="S46" s="20" t="s">
-        <v>2392</v>
+        <v>2416</v>
       </c>
       <c r="T46" s="20" t="s">
-        <v>2393</v>
+        <v>2417</v>
       </c>
       <c r="U46" s="20" t="s">
         <v>556</v>
       </c>
       <c r="V46" s="20" t="s">
-        <v>2394</v>
+        <v>2418</v>
       </c>
       <c r="W46" s="20" t="s">
         <v>1864</v>
       </c>
       <c r="X46" s="20" t="s">
-        <v>2395</v>
+        <v>2419</v>
       </c>
       <c r="Y46" s="20" t="s">
-        <v>1992</v>
+        <v>1994</v>
       </c>
       <c r="Z46" s="20" t="s">
-        <v>2396</v>
+        <v>2420</v>
       </c>
       <c r="AA46" s="20" t="s">
-        <v>2397</v>
+        <v>2421</v>
       </c>
       <c r="AB46" s="20" t="s">
-        <v>2398</v>
-      </c>
-      <c r="AC46" s="20"/>
-      <c r="AD46" s="25"/>
+        <v>2422</v>
+      </c>
+      <c r="AC46" s="20" t="s">
+        <v>2423</v>
+      </c>
+      <c r="AD46" s="25" t="s">
+        <v>2424</v>
+      </c>
       <c r="AE46" s="25"/>
       <c r="AF46" s="25"/>
       <c r="AG46" s="25"/>
@@ -18255,19 +17587,19 @@
     </row>
     <row r="47" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="20" t="s">
-        <v>2399</v>
+        <v>2425</v>
       </c>
       <c r="B47" s="20" t="s">
-        <v>2400</v>
+        <v>2426</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>2401</v>
+        <v>2427</v>
       </c>
       <c r="D47" s="20" t="s">
         <v>153</v>
       </c>
       <c r="E47" s="20" t="s">
-        <v>2402</v>
+        <v>2428</v>
       </c>
       <c r="F47" s="24">
         <v>110</v>
@@ -18289,35 +17621,45 @@
       <c r="M47" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="N47" s="21"/>
+      <c r="N47" s="21">
+        <v>5.18</v>
+      </c>
       <c r="O47" s="20" t="s">
-        <v>2086</v>
+        <v>2110</v>
       </c>
       <c r="P47" s="20" t="s">
-        <v>2403</v>
+        <v>2429</v>
       </c>
       <c r="Q47" s="20" t="s">
-        <v>2024</v>
+        <v>1986</v>
       </c>
       <c r="R47" s="20" t="s">
-        <v>2404</v>
+        <v>2430</v>
       </c>
       <c r="S47" s="20" t="s">
-        <v>2405</v>
+        <v>2431</v>
       </c>
       <c r="T47" s="20" t="s">
-        <v>2406</v>
+        <v>2432</v>
       </c>
       <c r="U47" s="20" t="s">
         <v>637</v>
       </c>
       <c r="V47" s="20" t="s">
-        <v>2407</v>
-      </c>
-      <c r="W47" s="20"/>
-      <c r="X47" s="20"/>
-      <c r="Y47" s="20"/>
-      <c r="Z47" s="20"/>
+        <v>2433</v>
+      </c>
+      <c r="W47" s="20" t="s">
+        <v>2416</v>
+      </c>
+      <c r="X47" s="20" t="s">
+        <v>2434</v>
+      </c>
+      <c r="Y47" s="20" t="s">
+        <v>1994</v>
+      </c>
+      <c r="Z47" s="20" t="s">
+        <v>2053</v>
+      </c>
       <c r="AA47" s="20"/>
       <c r="AB47" s="20"/>
       <c r="AC47" s="20"/>
@@ -18329,19 +17671,19 @@
     </row>
     <row r="48" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="20" t="s">
-        <v>2408</v>
+        <v>2435</v>
       </c>
       <c r="B48" s="20" t="s">
-        <v>2409</v>
+        <v>2436</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>2410</v>
+        <v>2437</v>
       </c>
       <c r="D48" s="20" t="s">
         <v>153</v>
       </c>
       <c r="E48" s="20" t="s">
-        <v>2411</v>
+        <v>2438</v>
       </c>
       <c r="F48" s="24">
         <v>125</v>
@@ -18365,29 +17707,41 @@
       </c>
       <c r="N48" s="21"/>
       <c r="O48" s="20" t="s">
-        <v>2086</v>
+        <v>2110</v>
       </c>
       <c r="P48" s="20" t="s">
-        <v>2412</v>
+        <v>2439</v>
       </c>
       <c r="Q48" s="20" t="s">
-        <v>2413</v>
+        <v>1986</v>
       </c>
       <c r="R48" s="20" t="s">
-        <v>2414</v>
+        <v>2440</v>
       </c>
       <c r="S48" s="20" t="s">
-        <v>2415</v>
+        <v>2441</v>
       </c>
       <c r="T48" s="20" t="s">
-        <v>2416</v>
-      </c>
-      <c r="U48" s="20"/>
-      <c r="V48" s="20"/>
-      <c r="W48" s="20"/>
-      <c r="X48" s="20"/>
-      <c r="Y48" s="20"/>
-      <c r="Z48" s="20"/>
+        <v>2442</v>
+      </c>
+      <c r="U48" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="V48" s="20" t="s">
+        <v>2443</v>
+      </c>
+      <c r="W48" s="20" t="s">
+        <v>1805</v>
+      </c>
+      <c r="X48" s="20" t="s">
+        <v>2444</v>
+      </c>
+      <c r="Y48" s="20" t="s">
+        <v>1864</v>
+      </c>
+      <c r="Z48" s="20" t="s">
+        <v>2445</v>
+      </c>
       <c r="AA48" s="20"/>
       <c r="AB48" s="20"/>
       <c r="AC48" s="20"/>
@@ -18399,19 +17753,19 @@
     </row>
     <row r="49" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="20" t="s">
-        <v>2417</v>
+        <v>2446</v>
       </c>
       <c r="B49" s="20" t="s">
-        <v>2418</v>
+        <v>2447</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>2419</v>
+        <v>2448</v>
       </c>
       <c r="D49" s="20" t="s">
         <v>114</v>
       </c>
       <c r="E49" s="20" t="s">
-        <v>2420</v>
+        <v>2449</v>
       </c>
       <c r="F49" s="24">
         <v>150</v>
@@ -18437,34 +17791,34 @@
         <v>4.88</v>
       </c>
       <c r="O49" s="20" t="s">
-        <v>2175</v>
+        <v>2199</v>
       </c>
       <c r="P49" s="20" t="s">
-        <v>2176</v>
+        <v>2200</v>
       </c>
       <c r="Q49" s="20" t="s">
         <v>208</v>
       </c>
       <c r="R49" s="20" t="s">
-        <v>2421</v>
+        <v>2450</v>
       </c>
       <c r="S49" s="20" t="s">
-        <v>2422</v>
+        <v>2451</v>
       </c>
       <c r="T49" s="20" t="s">
-        <v>2423</v>
+        <v>2452</v>
       </c>
       <c r="U49" s="20" t="s">
-        <v>2279</v>
+        <v>2303</v>
       </c>
       <c r="V49" s="20" t="s">
-        <v>2424</v>
+        <v>2453</v>
       </c>
       <c r="W49" s="20" t="s">
-        <v>2425</v>
+        <v>2454</v>
       </c>
       <c r="X49" s="20" t="s">
-        <v>2426</v>
+        <v>2455</v>
       </c>
       <c r="Y49" s="20"/>
       <c r="Z49" s="20"/>
@@ -18479,19 +17833,19 @@
     </row>
     <row r="50" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="20" t="s">
-        <v>2427</v>
+        <v>2456</v>
       </c>
       <c r="B50" s="20" t="s">
-        <v>2428</v>
+        <v>2457</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>2429</v>
+        <v>2458</v>
       </c>
       <c r="D50" s="20" t="s">
         <v>114</v>
       </c>
       <c r="E50" s="20" t="s">
-        <v>2430</v>
+        <v>2459</v>
       </c>
       <c r="F50" s="24">
         <v>150</v>
@@ -18517,34 +17871,34 @@
         <v>1.83</v>
       </c>
       <c r="O50" s="20" t="s">
-        <v>2175</v>
+        <v>2199</v>
       </c>
       <c r="P50" s="20" t="s">
-        <v>2176</v>
+        <v>2200</v>
       </c>
       <c r="Q50" s="20" t="s">
         <v>208</v>
       </c>
       <c r="R50" s="20" t="s">
-        <v>2421</v>
+        <v>2450</v>
       </c>
       <c r="S50" s="20" t="s">
-        <v>2422</v>
+        <v>2451</v>
       </c>
       <c r="T50" s="20" t="s">
-        <v>2423</v>
+        <v>2452</v>
       </c>
       <c r="U50" s="20" t="s">
-        <v>2279</v>
+        <v>2303</v>
       </c>
       <c r="V50" s="20" t="s">
-        <v>2424</v>
+        <v>2453</v>
       </c>
       <c r="W50" s="20" t="s">
-        <v>2425</v>
+        <v>2454</v>
       </c>
       <c r="X50" s="20" t="s">
-        <v>2426</v>
+        <v>2455</v>
       </c>
       <c r="Y50" s="20"/>
       <c r="Z50" s="20"/>
@@ -18559,19 +17913,19 @@
     </row>
     <row r="51" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="20" t="s">
-        <v>2431</v>
+        <v>2460</v>
       </c>
       <c r="B51" s="20" t="s">
-        <v>2432</v>
+        <v>2461</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>2433</v>
+        <v>2462</v>
       </c>
       <c r="D51" s="20" t="s">
         <v>114</v>
       </c>
       <c r="E51" s="20" t="s">
-        <v>2434</v>
+        <v>2463</v>
       </c>
       <c r="F51" s="24">
         <v>325</v>
@@ -18595,34 +17949,34 @@
       </c>
       <c r="N51" s="21"/>
       <c r="O51" s="20" t="s">
-        <v>2086</v>
+        <v>2110</v>
       </c>
       <c r="P51" s="20" t="s">
-        <v>2435</v>
+        <v>2464</v>
       </c>
       <c r="Q51" s="20" t="s">
         <v>1578</v>
       </c>
       <c r="R51" s="20" t="s">
-        <v>2436</v>
+        <v>2465</v>
       </c>
       <c r="S51" s="20" t="s">
-        <v>2137</v>
+        <v>2161</v>
       </c>
       <c r="T51" s="20" t="s">
-        <v>2437</v>
+        <v>2466</v>
       </c>
       <c r="U51" s="20" t="s">
-        <v>2438</v>
+        <v>2467</v>
       </c>
       <c r="V51" s="20" t="s">
-        <v>2439</v>
+        <v>2468</v>
       </c>
       <c r="W51" s="20" t="s">
         <v>950</v>
       </c>
       <c r="X51" s="20" t="s">
-        <v>2440</v>
+        <v>2469</v>
       </c>
       <c r="Y51" s="20"/>
       <c r="Z51" s="20"/>
@@ -18637,19 +17991,19 @@
     </row>
     <row r="52" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="20" t="s">
-        <v>2441</v>
+        <v>2470</v>
       </c>
       <c r="B52" s="20" t="s">
-        <v>2442</v>
+        <v>2471</v>
       </c>
       <c r="C52" s="20" t="s">
-        <v>2443</v>
+        <v>2472</v>
       </c>
       <c r="D52" s="20" t="s">
         <v>140</v>
       </c>
       <c r="E52" s="20" t="s">
-        <v>2444</v>
+        <v>2473</v>
       </c>
       <c r="F52" s="24">
         <v>1050</v>
@@ -18682,7 +18036,7 @@
         <v>936</v>
       </c>
       <c r="R52" s="20" t="s">
-        <v>2445</v>
+        <v>2474</v>
       </c>
       <c r="S52" s="20"/>
       <c r="T52" s="20"/>
@@ -18703,19 +18057,19 @@
     </row>
     <row r="53" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="20" t="s">
-        <v>2446</v>
+        <v>2475</v>
       </c>
       <c r="B53" s="20" t="s">
-        <v>2447</v>
+        <v>2476</v>
       </c>
       <c r="C53" s="20" t="s">
-        <v>2448</v>
+        <v>2477</v>
       </c>
       <c r="D53" s="20" t="s">
         <v>140</v>
       </c>
       <c r="E53" s="20" t="s">
-        <v>2449</v>
+        <v>2478</v>
       </c>
       <c r="F53" s="24">
         <v>395</v>
@@ -18742,13 +18096,13 @@
         <v>210</v>
       </c>
       <c r="P53" s="20" t="s">
-        <v>2450</v>
+        <v>2479</v>
       </c>
       <c r="Q53" s="20" t="s">
-        <v>2175</v>
+        <v>2199</v>
       </c>
       <c r="R53" s="20" t="s">
-        <v>2451</v>
+        <v>2480</v>
       </c>
       <c r="S53" s="20"/>
       <c r="T53" s="20"/>
@@ -18769,19 +18123,19 @@
     </row>
     <row r="54" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="20" t="s">
-        <v>2452</v>
+        <v>2481</v>
       </c>
       <c r="B54" s="20" t="s">
-        <v>2453</v>
+        <v>2482</v>
       </c>
       <c r="C54" s="20" t="s">
-        <v>2454</v>
+        <v>2483</v>
       </c>
       <c r="D54" s="20" t="s">
         <v>140</v>
       </c>
       <c r="E54" s="20" t="s">
-        <v>2455</v>
+        <v>2484</v>
       </c>
       <c r="F54" s="24">
         <v>1150</v>
@@ -18808,13 +18162,13 @@
         <v>210</v>
       </c>
       <c r="P54" s="20" t="s">
-        <v>2450</v>
+        <v>2479</v>
       </c>
       <c r="Q54" s="20" t="s">
-        <v>2175</v>
+        <v>2199</v>
       </c>
       <c r="R54" s="20" t="s">
-        <v>2456</v>
+        <v>2485</v>
       </c>
       <c r="S54" s="20"/>
       <c r="T54" s="20"/>
@@ -18835,19 +18189,19 @@
     </row>
     <row r="55" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="20" t="s">
-        <v>2457</v>
+        <v>2486</v>
       </c>
       <c r="B55" s="20" t="s">
-        <v>2458</v>
+        <v>2487</v>
       </c>
       <c r="C55" s="20" t="s">
-        <v>2459</v>
+        <v>2488</v>
       </c>
       <c r="D55" s="20" t="s">
         <v>140</v>
       </c>
       <c r="E55" s="20" t="s">
-        <v>2460</v>
+        <v>2489</v>
       </c>
       <c r="F55" s="24">
         <v>275</v>
@@ -18879,22 +18233,22 @@
         <v>516</v>
       </c>
       <c r="Q55" s="20" t="s">
-        <v>2175</v>
+        <v>2199</v>
       </c>
       <c r="R55" s="20" t="s">
-        <v>2277</v>
+        <v>2301</v>
       </c>
       <c r="S55" s="20" t="s">
-        <v>2422</v>
+        <v>2451</v>
       </c>
       <c r="T55" s="20" t="s">
-        <v>2423</v>
+        <v>2452</v>
       </c>
       <c r="U55" s="20" t="s">
         <v>445</v>
       </c>
       <c r="V55" s="20" t="s">
-        <v>2461</v>
+        <v>2490</v>
       </c>
       <c r="W55" s="20"/>
       <c r="X55" s="20"/>
@@ -18911,19 +18265,19 @@
     </row>
     <row r="56" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="20" t="s">
-        <v>2462</v>
+        <v>2491</v>
       </c>
       <c r="B56" s="20" t="s">
-        <v>2463</v>
+        <v>2492</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>2464</v>
+        <v>2493</v>
       </c>
       <c r="D56" s="20" t="s">
         <v>140</v>
       </c>
       <c r="E56" s="20" t="s">
-        <v>2465</v>
+        <v>2494</v>
       </c>
       <c r="F56" s="24">
         <v>250</v>
@@ -18955,22 +18309,22 @@
         <v>516</v>
       </c>
       <c r="Q56" s="20" t="s">
-        <v>2175</v>
+        <v>2199</v>
       </c>
       <c r="R56" s="20" t="s">
-        <v>2277</v>
+        <v>2301</v>
       </c>
       <c r="S56" s="20" t="s">
-        <v>2422</v>
+        <v>2451</v>
       </c>
       <c r="T56" s="20" t="s">
-        <v>2423</v>
+        <v>2452</v>
       </c>
       <c r="U56" s="20" t="s">
         <v>445</v>
       </c>
       <c r="V56" s="20" t="s">
-        <v>2461</v>
+        <v>2490</v>
       </c>
       <c r="W56" s="20"/>
       <c r="X56" s="20"/>
@@ -18987,19 +18341,19 @@
     </row>
     <row r="57" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="20" t="s">
-        <v>2466</v>
+        <v>2495</v>
       </c>
       <c r="B57" s="20" t="s">
-        <v>2467</v>
+        <v>2496</v>
       </c>
       <c r="C57" s="20" t="s">
-        <v>2468</v>
+        <v>2497</v>
       </c>
       <c r="D57" s="20" t="s">
         <v>140</v>
       </c>
       <c r="E57" s="20" t="s">
-        <v>2469</v>
+        <v>2498</v>
       </c>
       <c r="F57" s="24">
         <v>225</v>
@@ -19031,22 +18385,22 @@
         <v>516</v>
       </c>
       <c r="Q57" s="20" t="s">
-        <v>2175</v>
+        <v>2199</v>
       </c>
       <c r="R57" s="20" t="s">
-        <v>2277</v>
+        <v>2301</v>
       </c>
       <c r="S57" s="20" t="s">
-        <v>2422</v>
+        <v>2451</v>
       </c>
       <c r="T57" s="20" t="s">
-        <v>2423</v>
+        <v>2452</v>
       </c>
       <c r="U57" s="20" t="s">
         <v>445</v>
       </c>
       <c r="V57" s="20" t="s">
-        <v>2461</v>
+        <v>2490</v>
       </c>
       <c r="W57" s="20"/>
       <c r="X57" s="20"/>
@@ -19063,19 +18417,19 @@
     </row>
     <row r="58" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="20" t="s">
-        <v>2470</v>
+        <v>2499</v>
       </c>
       <c r="B58" s="20" t="s">
-        <v>2471</v>
+        <v>2500</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>2472</v>
+        <v>2501</v>
       </c>
       <c r="D58" s="20" t="s">
         <v>140</v>
       </c>
       <c r="E58" s="20" t="s">
-        <v>2473</v>
+        <v>2502</v>
       </c>
       <c r="F58" s="24">
         <v>175</v>
@@ -19107,22 +18461,22 @@
         <v>516</v>
       </c>
       <c r="Q58" s="20" t="s">
-        <v>2175</v>
+        <v>2199</v>
       </c>
       <c r="R58" s="20" t="s">
-        <v>2176</v>
+        <v>2200</v>
       </c>
       <c r="S58" s="20" t="s">
-        <v>2422</v>
+        <v>2451</v>
       </c>
       <c r="T58" s="20" t="s">
-        <v>2423</v>
+        <v>2452</v>
       </c>
       <c r="U58" s="20" t="s">
         <v>445</v>
       </c>
       <c r="V58" s="20" t="s">
-        <v>2461</v>
+        <v>2490</v>
       </c>
       <c r="W58" s="20"/>
       <c r="X58" s="20"/>
@@ -19139,19 +18493,19 @@
     </row>
     <row r="59" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="20" t="s">
-        <v>2474</v>
+        <v>2503</v>
       </c>
       <c r="B59" s="20" t="s">
-        <v>2475</v>
+        <v>2504</v>
       </c>
       <c r="C59" s="20" t="s">
-        <v>2476</v>
+        <v>2505</v>
       </c>
       <c r="D59" s="20" t="s">
         <v>140</v>
       </c>
       <c r="E59" s="20" t="s">
-        <v>2477</v>
+        <v>2506</v>
       </c>
       <c r="F59" s="24">
         <v>150</v>
@@ -19183,22 +18537,22 @@
         <v>516</v>
       </c>
       <c r="Q59" s="20" t="s">
-        <v>2175</v>
+        <v>2199</v>
       </c>
       <c r="R59" s="20" t="s">
-        <v>2176</v>
+        <v>2200</v>
       </c>
       <c r="S59" s="20" t="s">
-        <v>2422</v>
+        <v>2451</v>
       </c>
       <c r="T59" s="20" t="s">
-        <v>2423</v>
+        <v>2452</v>
       </c>
       <c r="U59" s="20" t="s">
         <v>445</v>
       </c>
       <c r="V59" s="20" t="s">
-        <v>2461</v>
+        <v>2490</v>
       </c>
       <c r="W59" s="20"/>
       <c r="X59" s="20"/>
@@ -19215,19 +18569,19 @@
     </row>
     <row r="60" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="20" t="s">
-        <v>2478</v>
+        <v>2507</v>
       </c>
       <c r="B60" s="20" t="s">
-        <v>2479</v>
+        <v>2508</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>2480</v>
+        <v>2509</v>
       </c>
       <c r="D60" s="20" t="s">
         <v>140</v>
       </c>
       <c r="E60" s="20" t="s">
-        <v>2481</v>
+        <v>2510</v>
       </c>
       <c r="F60" s="24">
         <v>125</v>
@@ -19259,22 +18613,22 @@
         <v>516</v>
       </c>
       <c r="Q60" s="20" t="s">
-        <v>2175</v>
+        <v>2199</v>
       </c>
       <c r="R60" s="20" t="s">
-        <v>2176</v>
+        <v>2200</v>
       </c>
       <c r="S60" s="20" t="s">
-        <v>2422</v>
+        <v>2451</v>
       </c>
       <c r="T60" s="20" t="s">
-        <v>2423</v>
+        <v>2452</v>
       </c>
       <c r="U60" s="20" t="s">
         <v>445</v>
       </c>
       <c r="V60" s="20" t="s">
-        <v>2461</v>
+        <v>2490</v>
       </c>
       <c r="W60" s="20"/>
       <c r="X60" s="20"/>
@@ -19291,19 +18645,19 @@
     </row>
     <row r="61" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="20" t="s">
-        <v>2482</v>
+        <v>2511</v>
       </c>
       <c r="B61" s="20" t="s">
-        <v>2483</v>
+        <v>2512</v>
       </c>
       <c r="C61" s="20" t="s">
-        <v>2484</v>
+        <v>2513</v>
       </c>
       <c r="D61" s="20" t="s">
         <v>140</v>
       </c>
       <c r="E61" s="20" t="s">
-        <v>2163</v>
+        <v>2187</v>
       </c>
       <c r="F61" s="24">
         <v>125</v>
@@ -19336,7 +18690,7 @@
         <v>235</v>
       </c>
       <c r="R61" s="20" t="s">
-        <v>2165</v>
+        <v>2189</v>
       </c>
       <c r="S61" s="20"/>
       <c r="T61" s="20"/>
@@ -19357,19 +18711,19 @@
     </row>
     <row r="62" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="20" t="s">
-        <v>2485</v>
+        <v>2514</v>
       </c>
       <c r="B62" s="20" t="s">
-        <v>2486</v>
+        <v>2515</v>
       </c>
       <c r="C62" s="20" t="s">
-        <v>2487</v>
+        <v>2516</v>
       </c>
       <c r="D62" s="20" t="s">
         <v>140</v>
       </c>
       <c r="E62" s="20" t="s">
-        <v>2488</v>
+        <v>2517</v>
       </c>
       <c r="F62" s="24">
         <v>125</v>
@@ -19402,7 +18756,7 @@
         <v>235</v>
       </c>
       <c r="R62" s="20" t="s">
-        <v>2314</v>
+        <v>2338</v>
       </c>
       <c r="S62" s="20"/>
       <c r="T62" s="20"/>
@@ -19423,19 +18777,19 @@
     </row>
     <row r="63" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="20" t="s">
-        <v>2489</v>
+        <v>2518</v>
       </c>
       <c r="B63" s="20" t="s">
-        <v>2490</v>
+        <v>2519</v>
       </c>
       <c r="C63" s="20" t="s">
-        <v>2491</v>
+        <v>2520</v>
       </c>
       <c r="D63" s="20" t="s">
         <v>140</v>
       </c>
       <c r="E63" s="20" t="s">
-        <v>2361</v>
+        <v>2385</v>
       </c>
       <c r="F63" s="24">
         <v>150</v>
@@ -19468,7 +18822,7 @@
         <v>1864</v>
       </c>
       <c r="R63" s="20" t="s">
-        <v>2492</v>
+        <v>2521</v>
       </c>
       <c r="S63" s="20"/>
       <c r="T63" s="20"/>
@@ -19489,19 +18843,19 @@
     </row>
     <row r="64" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="20" t="s">
-        <v>2493</v>
+        <v>2522</v>
       </c>
       <c r="B64" s="20" t="s">
-        <v>2494</v>
+        <v>2523</v>
       </c>
       <c r="C64" s="20" t="s">
-        <v>2495</v>
+        <v>2524</v>
       </c>
       <c r="D64" s="20" t="s">
         <v>140</v>
       </c>
       <c r="E64" s="20" t="s">
-        <v>2496</v>
+        <v>2525</v>
       </c>
       <c r="F64" s="24">
         <v>75</v>
@@ -19525,16 +18879,16 @@
       </c>
       <c r="N64" s="21"/>
       <c r="O64" s="20" t="s">
-        <v>2497</v>
+        <v>2526</v>
       </c>
       <c r="P64" s="20" t="s">
-        <v>2498</v>
+        <v>2527</v>
       </c>
       <c r="Q64" s="20" t="s">
         <v>1864</v>
       </c>
       <c r="R64" s="20" t="s">
-        <v>2499</v>
+        <v>2528</v>
       </c>
       <c r="S64" s="20"/>
       <c r="T64" s="20"/>
@@ -19555,19 +18909,19 @@
     </row>
     <row r="65" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="20" t="s">
-        <v>2500</v>
+        <v>2529</v>
       </c>
       <c r="B65" s="20" t="s">
-        <v>2501</v>
+        <v>2530</v>
       </c>
       <c r="C65" s="20" t="s">
-        <v>2502</v>
+        <v>2531</v>
       </c>
       <c r="D65" s="20" t="s">
         <v>140</v>
       </c>
       <c r="E65" s="20" t="s">
-        <v>2503</v>
+        <v>2532</v>
       </c>
       <c r="F65" s="24">
         <v>225</v>
@@ -19591,16 +18945,16 @@
       </c>
       <c r="N65" s="21"/>
       <c r="O65" s="20" t="s">
-        <v>2156</v>
+        <v>2180</v>
       </c>
       <c r="P65" s="20" t="s">
-        <v>2504</v>
+        <v>2533</v>
       </c>
       <c r="Q65" s="20" t="s">
-        <v>2137</v>
+        <v>2161</v>
       </c>
       <c r="R65" s="20" t="s">
-        <v>2505</v>
+        <v>2534</v>
       </c>
       <c r="S65" s="20"/>
       <c r="T65" s="20"/>
@@ -19621,19 +18975,19 @@
     </row>
     <row r="66" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="20" t="s">
-        <v>2506</v>
+        <v>2535</v>
       </c>
       <c r="B66" s="20" t="s">
-        <v>2507</v>
+        <v>2536</v>
       </c>
       <c r="C66" s="20" t="s">
-        <v>2508</v>
+        <v>2537</v>
       </c>
       <c r="D66" s="20" t="s">
         <v>140</v>
       </c>
       <c r="E66" s="20" t="s">
-        <v>2509</v>
+        <v>2538</v>
       </c>
       <c r="F66" s="24">
         <v>125</v>
@@ -19657,16 +19011,16 @@
       </c>
       <c r="N66" s="21"/>
       <c r="O66" s="20" t="s">
-        <v>2156</v>
+        <v>2180</v>
       </c>
       <c r="P66" s="20" t="s">
-        <v>2510</v>
+        <v>2539</v>
       </c>
       <c r="Q66" s="20" t="s">
-        <v>2235</v>
+        <v>2259</v>
       </c>
       <c r="R66" s="20" t="s">
-        <v>2511</v>
+        <v>2540</v>
       </c>
       <c r="S66" s="20"/>
       <c r="T66" s="20"/>
@@ -19687,19 +19041,19 @@
     </row>
     <row r="67" spans="1:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="20" t="s">
-        <v>2512</v>
+        <v>2541</v>
       </c>
       <c r="B67" s="20" t="s">
-        <v>2513</v>
+        <v>2542</v>
       </c>
       <c r="C67" s="20" t="s">
-        <v>2514</v>
+        <v>2543</v>
       </c>
       <c r="D67" s="20" t="s">
         <v>140</v>
       </c>
       <c r="E67" s="20" t="s">
-        <v>2515</v>
+        <v>2544</v>
       </c>
       <c r="F67" s="24">
         <v>350</v>
@@ -19726,25 +19080,25 @@
         <v>210</v>
       </c>
       <c r="P67" s="20" t="s">
-        <v>2516</v>
+        <v>2545</v>
       </c>
       <c r="Q67" s="20" t="s">
-        <v>2175</v>
+        <v>2199</v>
       </c>
       <c r="R67" s="20" t="s">
-        <v>2176</v>
+        <v>2200</v>
       </c>
       <c r="S67" s="20" t="s">
-        <v>2517</v>
+        <v>2546</v>
       </c>
       <c r="T67" s="20" t="s">
-        <v>2518</v>
+        <v>2547</v>
       </c>
       <c r="U67" s="20" t="s">
-        <v>2519</v>
+        <v>2548</v>
       </c>
       <c r="V67" s="20" t="s">
-        <v>2520</v>
+        <v>2549</v>
       </c>
       <c r="W67" s="20"/>
       <c r="X67" s="20"/>
@@ -20191,7 +19545,7 @@
         <v>55</v>
       </c>
       <c r="M1" s="16" t="s">
-        <v>2521</v>
+        <v>2550</v>
       </c>
       <c r="N1" s="19" t="s">
         <v>181</v>
@@ -20256,19 +19610,19 @@
     </row>
     <row r="2" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="20" t="s">
-        <v>2522</v>
+        <v>2551</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>2523</v>
+        <v>2552</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>2524</v>
+        <v>2553</v>
       </c>
       <c r="D2" s="20" t="s">
         <v>84</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>2525</v>
+        <v>2554</v>
       </c>
       <c r="F2" s="21">
         <v>5795</v>
@@ -20294,10 +19648,10 @@
         <v>296</v>
       </c>
       <c r="O2" s="25" t="s">
-        <v>2526</v>
+        <v>2555</v>
       </c>
       <c r="P2" s="25" t="s">
-        <v>2527</v>
+        <v>2556</v>
       </c>
       <c r="Q2" s="25" t="s">
         <v>414</v>
@@ -20306,13 +19660,13 @@
         <v>235</v>
       </c>
       <c r="S2" s="25" t="s">
-        <v>2528</v>
+        <v>2557</v>
       </c>
       <c r="T2" s="25" t="s">
-        <v>2529</v>
+        <v>2558</v>
       </c>
       <c r="U2" s="25" t="s">
-        <v>2530</v>
+        <v>2559</v>
       </c>
       <c r="V2" s="25" t="s">
         <v>962</v>
@@ -20324,44 +19678,44 @@
         <v>517</v>
       </c>
       <c r="Y2" s="25" t="s">
-        <v>2531</v>
+        <v>2560</v>
       </c>
       <c r="Z2" s="25" t="s">
         <v>1712</v>
       </c>
       <c r="AA2" s="25" t="s">
-        <v>2532</v>
+        <v>2561</v>
       </c>
       <c r="AB2" s="25" t="s">
-        <v>2533</v>
+        <v>2562</v>
       </c>
       <c r="AC2" s="25" t="s">
-        <v>2534</v>
+        <v>2563</v>
       </c>
       <c r="AD2" s="25" t="s">
-        <v>2535</v>
+        <v>2564</v>
       </c>
       <c r="AE2" s="25" t="s">
-        <v>2536</v>
+        <v>2565</v>
       </c>
       <c r="AF2" s="25"/>
       <c r="AG2" s="25"/>
     </row>
     <row r="3" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="20" t="s">
-        <v>2537</v>
+        <v>2566</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>2538</v>
+        <v>2567</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>2539</v>
+        <v>2568</v>
       </c>
       <c r="D3" s="20" t="s">
         <v>114</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>2540</v>
+        <v>2569</v>
       </c>
       <c r="F3" s="21">
         <v>70000</v>
@@ -20381,37 +19735,37 @@
         <v>113</v>
       </c>
       <c r="M3" s="20" t="s">
-        <v>2541</v>
+        <v>2570</v>
       </c>
       <c r="N3" s="25" t="s">
         <v>940</v>
       </c>
       <c r="O3" s="25" t="s">
-        <v>2542</v>
+        <v>2571</v>
       </c>
       <c r="P3" s="25" t="s">
         <v>235</v>
       </c>
       <c r="Q3" s="25" t="s">
-        <v>2543</v>
+        <v>2572</v>
       </c>
       <c r="R3" s="25" t="s">
         <v>936</v>
       </c>
       <c r="S3" s="25" t="s">
-        <v>2544</v>
+        <v>2573</v>
       </c>
       <c r="T3" s="25" t="s">
         <v>556</v>
       </c>
       <c r="U3" s="25" t="s">
-        <v>2545</v>
+        <v>2574</v>
       </c>
       <c r="V3" s="25" t="s">
         <v>509</v>
       </c>
       <c r="W3" s="25" t="s">
-        <v>2546</v>
+        <v>2575</v>
       </c>
       <c r="X3" s="25"/>
       <c r="Y3" s="25"/>
@@ -20426,19 +19780,19 @@
     </row>
     <row r="4" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="20" t="s">
-        <v>2547</v>
+        <v>2576</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>2548</v>
+        <v>2577</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>2549</v>
+        <v>2578</v>
       </c>
       <c r="D4" s="20" t="s">
         <v>114</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>2550</v>
+        <v>2579</v>
       </c>
       <c r="F4" s="21">
         <v>46200</v>
@@ -20458,37 +19812,37 @@
         <v>113</v>
       </c>
       <c r="M4" s="20" t="s">
-        <v>2541</v>
+        <v>2570</v>
       </c>
       <c r="N4" s="25" t="s">
         <v>940</v>
       </c>
       <c r="O4" s="25" t="s">
-        <v>2542</v>
+        <v>2571</v>
       </c>
       <c r="P4" s="25" t="s">
         <v>235</v>
       </c>
       <c r="Q4" s="25" t="s">
-        <v>2551</v>
+        <v>2580</v>
       </c>
       <c r="R4" s="25" t="s">
         <v>936</v>
       </c>
       <c r="S4" s="25" t="s">
-        <v>2544</v>
+        <v>2573</v>
       </c>
       <c r="T4" s="25" t="s">
         <v>556</v>
       </c>
       <c r="U4" s="25" t="s">
-        <v>2552</v>
+        <v>2581</v>
       </c>
       <c r="V4" s="25" t="s">
         <v>509</v>
       </c>
       <c r="W4" s="25" t="s">
-        <v>2546</v>
+        <v>2575</v>
       </c>
       <c r="X4" s="25"/>
       <c r="Y4" s="25"/>
@@ -20503,19 +19857,19 @@
     </row>
     <row r="5" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="20" t="s">
-        <v>2553</v>
+        <v>2582</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>2554</v>
+        <v>2583</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>2555</v>
+        <v>2584</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>114</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>2556</v>
+        <v>2585</v>
       </c>
       <c r="F5" s="21">
         <v>31000</v>
@@ -20535,80 +19889,80 @@
         <v>113</v>
       </c>
       <c r="M5" s="20" t="s">
-        <v>2541</v>
+        <v>2570</v>
       </c>
       <c r="N5" s="25" t="s">
         <v>296</v>
       </c>
       <c r="O5" s="25" t="s">
-        <v>2557</v>
+        <v>2586</v>
       </c>
       <c r="P5" s="25" t="s">
-        <v>2558</v>
+        <v>2587</v>
       </c>
       <c r="Q5" s="25" t="s">
-        <v>2559</v>
+        <v>2588</v>
       </c>
       <c r="R5" s="25" t="s">
         <v>940</v>
       </c>
       <c r="S5" s="25" t="s">
-        <v>2560</v>
+        <v>2589</v>
       </c>
       <c r="T5" s="25" t="s">
-        <v>2561</v>
+        <v>2590</v>
       </c>
       <c r="U5" s="25" t="s">
-        <v>2562</v>
+        <v>2591</v>
       </c>
       <c r="V5" s="25" t="s">
-        <v>2563</v>
+        <v>2592</v>
       </c>
       <c r="W5" s="25" t="s">
-        <v>2564</v>
+        <v>2593</v>
       </c>
       <c r="X5" s="25" t="s">
-        <v>2565</v>
+        <v>2594</v>
       </c>
       <c r="Y5" s="25" t="s">
-        <v>2566</v>
+        <v>2595</v>
       </c>
       <c r="Z5" s="25" t="s">
-        <v>2567</v>
+        <v>2596</v>
       </c>
       <c r="AA5" s="25" t="s">
-        <v>2568</v>
+        <v>2597</v>
       </c>
       <c r="AB5" s="25" t="s">
         <v>936</v>
       </c>
       <c r="AC5" s="25" t="s">
-        <v>2569</v>
+        <v>2598</v>
       </c>
       <c r="AD5" s="25" t="s">
         <v>616</v>
       </c>
       <c r="AE5" s="25" t="s">
-        <v>2570</v>
+        <v>2599</v>
       </c>
       <c r="AF5" s="25"/>
       <c r="AG5" s="25"/>
     </row>
     <row r="6" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="20" t="s">
-        <v>2571</v>
+        <v>2600</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>2572</v>
+        <v>2601</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>2573</v>
+        <v>2602</v>
       </c>
       <c r="D6" s="20" t="s">
         <v>114</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>2556</v>
+        <v>2585</v>
       </c>
       <c r="F6" s="21">
         <v>17000</v>
@@ -20628,80 +19982,80 @@
         <v>113</v>
       </c>
       <c r="M6" s="20" t="s">
-        <v>2541</v>
+        <v>2570</v>
       </c>
       <c r="N6" s="25" t="s">
         <v>296</v>
       </c>
       <c r="O6" s="25" t="s">
-        <v>2557</v>
+        <v>2586</v>
       </c>
       <c r="P6" s="25" t="s">
-        <v>2558</v>
+        <v>2587</v>
       </c>
       <c r="Q6" s="25" t="s">
-        <v>2559</v>
+        <v>2588</v>
       </c>
       <c r="R6" s="25" t="s">
         <v>940</v>
       </c>
       <c r="S6" s="25" t="s">
-        <v>2574</v>
+        <v>2603</v>
       </c>
       <c r="T6" s="25" t="s">
-        <v>2561</v>
+        <v>2590</v>
       </c>
       <c r="U6" s="25" t="s">
-        <v>2575</v>
+        <v>2604</v>
       </c>
       <c r="V6" s="25" t="s">
-        <v>2563</v>
+        <v>2592</v>
       </c>
       <c r="W6" s="25" t="s">
-        <v>2576</v>
+        <v>2605</v>
       </c>
       <c r="X6" s="25" t="s">
-        <v>2565</v>
+        <v>2594</v>
       </c>
       <c r="Y6" s="25" t="s">
-        <v>2577</v>
+        <v>2606</v>
       </c>
       <c r="Z6" s="25" t="s">
-        <v>2567</v>
+        <v>2596</v>
       </c>
       <c r="AA6" s="25" t="s">
-        <v>2578</v>
+        <v>2607</v>
       </c>
       <c r="AB6" s="25" t="s">
         <v>936</v>
       </c>
       <c r="AC6" s="25" t="s">
-        <v>2569</v>
+        <v>2598</v>
       </c>
       <c r="AD6" s="25" t="s">
-        <v>2579</v>
+        <v>2608</v>
       </c>
       <c r="AE6" s="25" t="s">
-        <v>2580</v>
+        <v>2609</v>
       </c>
       <c r="AF6" s="25"/>
       <c r="AG6" s="25"/>
     </row>
     <row r="7" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="20" t="s">
-        <v>2581</v>
+        <v>2610</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>2582</v>
+        <v>2611</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>2583</v>
+        <v>2612</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>140</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>2584</v>
+        <v>2613</v>
       </c>
       <c r="F7" s="21">
         <v>4695</v>
@@ -20727,31 +20081,31 @@
         <v>296</v>
       </c>
       <c r="O7" s="25" t="s">
-        <v>2585</v>
+        <v>2614</v>
       </c>
       <c r="P7" s="25" t="s">
         <v>85</v>
       </c>
       <c r="Q7" s="25" t="s">
-        <v>2586</v>
+        <v>2615</v>
       </c>
       <c r="R7" s="25" t="s">
         <v>1712</v>
       </c>
       <c r="S7" s="25" t="s">
-        <v>2587</v>
+        <v>2616</v>
       </c>
       <c r="T7" s="25" t="s">
         <v>936</v>
       </c>
       <c r="U7" s="25" t="s">
-        <v>2588</v>
+        <v>2617</v>
       </c>
       <c r="V7" s="25" t="s">
         <v>298</v>
       </c>
       <c r="W7" s="25" t="s">
-        <v>2589</v>
+        <v>2618</v>
       </c>
       <c r="X7" s="25"/>
       <c r="Y7" s="25"/>
@@ -20766,19 +20120,19 @@
     </row>
     <row r="8" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="20" t="s">
-        <v>2590</v>
+        <v>2619</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>2591</v>
+        <v>2620</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>2592</v>
+        <v>2621</v>
       </c>
       <c r="D8" s="20" t="s">
         <v>146</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>2593</v>
+        <v>2622</v>
       </c>
       <c r="F8" s="21">
         <v>3195</v>
@@ -20801,16 +20155,16 @@
         <v>70</v>
       </c>
       <c r="N8" s="25" t="s">
-        <v>2527</v>
+        <v>2556</v>
       </c>
       <c r="O8" s="25" t="s">
         <v>414</v>
       </c>
       <c r="P8" s="25" t="s">
-        <v>2195</v>
+        <v>2219</v>
       </c>
       <c r="Q8" s="25" t="s">
-        <v>2594</v>
+        <v>2623</v>
       </c>
       <c r="R8" s="25" t="s">
         <v>210</v>
@@ -20822,7 +20176,7 @@
         <v>298</v>
       </c>
       <c r="U8" s="25" t="s">
-        <v>2595</v>
+        <v>2624</v>
       </c>
       <c r="V8" s="25" t="s">
         <v>206</v>
@@ -20834,44 +20188,44 @@
         <v>517</v>
       </c>
       <c r="Y8" s="25" t="s">
-        <v>2596</v>
+        <v>2625</v>
       </c>
       <c r="Z8" s="25" t="s">
-        <v>2597</v>
+        <v>2626</v>
       </c>
       <c r="AA8" s="25" t="s">
-        <v>2598</v>
+        <v>2627</v>
       </c>
       <c r="AB8" s="25" t="s">
         <v>214</v>
       </c>
       <c r="AC8" s="25" t="s">
-        <v>2599</v>
+        <v>2628</v>
       </c>
       <c r="AD8" s="25" t="s">
-        <v>2600</v>
+        <v>2629</v>
       </c>
       <c r="AE8" s="25" t="s">
-        <v>2601</v>
+        <v>2630</v>
       </c>
       <c r="AF8" s="25"/>
       <c r="AG8" s="25"/>
     </row>
     <row r="9" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="20" t="s">
-        <v>2602</v>
+        <v>2631</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>2603</v>
+        <v>2632</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>2604</v>
+        <v>2633</v>
       </c>
       <c r="D9" s="20" t="s">
         <v>146</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>2605</v>
+        <v>2634</v>
       </c>
       <c r="F9" s="21">
         <v>2995</v>
@@ -20894,16 +20248,16 @@
         <v>70</v>
       </c>
       <c r="N9" s="25" t="s">
-        <v>2527</v>
+        <v>2556</v>
       </c>
       <c r="O9" s="25" t="s">
         <v>414</v>
       </c>
       <c r="P9" s="25" t="s">
-        <v>2195</v>
+        <v>2219</v>
       </c>
       <c r="Q9" s="25" t="s">
-        <v>2594</v>
+        <v>2623</v>
       </c>
       <c r="R9" s="25" t="s">
         <v>210</v>
@@ -20915,7 +20269,7 @@
         <v>298</v>
       </c>
       <c r="U9" s="25" t="s">
-        <v>2606</v>
+        <v>2635</v>
       </c>
       <c r="V9" s="25" t="s">
         <v>206</v>
@@ -20927,44 +20281,44 @@
         <v>517</v>
       </c>
       <c r="Y9" s="25" t="s">
-        <v>2596</v>
+        <v>2625</v>
       </c>
       <c r="Z9" s="25" t="s">
         <v>559</v>
       </c>
       <c r="AA9" s="25" t="s">
-        <v>2607</v>
+        <v>2636</v>
       </c>
       <c r="AB9" s="25" t="s">
         <v>214</v>
       </c>
       <c r="AC9" s="25" t="s">
-        <v>2608</v>
+        <v>2637</v>
       </c>
       <c r="AD9" s="25" t="s">
-        <v>2600</v>
+        <v>2629</v>
       </c>
       <c r="AE9" s="25" t="s">
-        <v>2609</v>
+        <v>2638</v>
       </c>
       <c r="AF9" s="25"/>
       <c r="AG9" s="25"/>
     </row>
     <row r="10" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="20" t="s">
-        <v>2610</v>
+        <v>2639</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>2611</v>
+        <v>2640</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>2612</v>
+        <v>2641</v>
       </c>
       <c r="D10" s="20" t="s">
         <v>84</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>2613</v>
+        <v>2642</v>
       </c>
       <c r="F10" s="21">
         <v>5995</v>
@@ -20990,49 +20344,49 @@
         <v>296</v>
       </c>
       <c r="O10" s="25" t="s">
-        <v>2614</v>
+        <v>2643</v>
       </c>
       <c r="P10" s="25" t="s">
-        <v>2527</v>
+        <v>2556</v>
       </c>
       <c r="Q10" s="25" t="s">
         <v>387</v>
       </c>
       <c r="R10" s="25" t="s">
-        <v>2195</v>
+        <v>2219</v>
       </c>
       <c r="S10" s="25" t="s">
-        <v>2615</v>
+        <v>2644</v>
       </c>
       <c r="T10" s="25" t="s">
-        <v>2616</v>
+        <v>2645</v>
       </c>
       <c r="U10" s="25" t="s">
-        <v>2617</v>
+        <v>2646</v>
       </c>
       <c r="V10" s="25" t="s">
         <v>1801</v>
       </c>
       <c r="W10" s="25" t="s">
-        <v>2618</v>
+        <v>2647</v>
       </c>
       <c r="X10" s="25" t="s">
         <v>235</v>
       </c>
       <c r="Y10" s="25" t="s">
-        <v>2619</v>
+        <v>2648</v>
       </c>
       <c r="Z10" s="25" t="s">
         <v>352</v>
       </c>
       <c r="AA10" s="25" t="s">
-        <v>2620</v>
+        <v>2649</v>
       </c>
       <c r="AB10" s="25" t="s">
         <v>208</v>
       </c>
       <c r="AC10" s="25" t="s">
-        <v>2621</v>
+        <v>2650</v>
       </c>
       <c r="AD10" s="25" t="s">
         <v>206</v>
@@ -21045,19 +20399,19 @@
     </row>
     <row r="11" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="20" t="s">
-        <v>2622</v>
+        <v>2651</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>2623</v>
+        <v>2652</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>2624</v>
+        <v>2653</v>
       </c>
       <c r="D11" s="20" t="s">
         <v>84</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>2625</v>
+        <v>2654</v>
       </c>
       <c r="F11" s="21">
         <v>3995</v>
@@ -21083,19 +20437,19 @@
         <v>296</v>
       </c>
       <c r="O11" s="25" t="s">
-        <v>2626</v>
+        <v>2655</v>
       </c>
       <c r="P11" s="25" t="s">
-        <v>2527</v>
+        <v>2556</v>
       </c>
       <c r="Q11" s="25" t="s">
         <v>406</v>
       </c>
       <c r="R11" s="25" t="s">
-        <v>2195</v>
+        <v>2219</v>
       </c>
       <c r="S11" s="25" t="s">
-        <v>2615</v>
+        <v>2644</v>
       </c>
       <c r="T11" s="25" t="s">
         <v>210</v>
@@ -21104,53 +20458,53 @@
         <v>373</v>
       </c>
       <c r="V11" s="25" t="s">
-        <v>2616</v>
+        <v>2645</v>
       </c>
       <c r="W11" s="25" t="s">
-        <v>2617</v>
+        <v>2646</v>
       </c>
       <c r="X11" s="25" t="s">
         <v>1801</v>
       </c>
       <c r="Y11" s="25" t="s">
-        <v>2627</v>
+        <v>2656</v>
       </c>
       <c r="Z11" s="25" t="s">
         <v>235</v>
       </c>
       <c r="AA11" s="25" t="s">
-        <v>2628</v>
+        <v>2657</v>
       </c>
       <c r="AB11" s="25" t="s">
         <v>352</v>
       </c>
       <c r="AC11" s="25" t="s">
-        <v>2629</v>
+        <v>2658</v>
       </c>
       <c r="AD11" s="25" t="s">
         <v>208</v>
       </c>
       <c r="AE11" s="25" t="s">
-        <v>2621</v>
+        <v>2650</v>
       </c>
       <c r="AF11" s="25"/>
       <c r="AG11" s="25"/>
     </row>
     <row r="12" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="20" t="s">
-        <v>2630</v>
+        <v>2659</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>2631</v>
+        <v>2660</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>2632</v>
+        <v>2661</v>
       </c>
       <c r="D12" s="20" t="s">
         <v>84</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>2633</v>
+        <v>2662</v>
       </c>
       <c r="F12" s="21">
         <v>5595</v>
@@ -21176,19 +20530,19 @@
         <v>296</v>
       </c>
       <c r="O12" s="25" t="s">
-        <v>2634</v>
+        <v>2663</v>
       </c>
       <c r="P12" s="25" t="s">
-        <v>2527</v>
+        <v>2556</v>
       </c>
       <c r="Q12" s="25" t="s">
         <v>430</v>
       </c>
       <c r="R12" s="25" t="s">
-        <v>2195</v>
+        <v>2219</v>
       </c>
       <c r="S12" s="25" t="s">
-        <v>2615</v>
+        <v>2644</v>
       </c>
       <c r="T12" s="25" t="s">
         <v>1801</v>
@@ -21200,25 +20554,25 @@
         <v>517</v>
       </c>
       <c r="W12" s="25" t="s">
-        <v>2635</v>
+        <v>2664</v>
       </c>
       <c r="X12" s="25" t="s">
         <v>235</v>
       </c>
       <c r="Y12" s="25" t="s">
-        <v>2636</v>
+        <v>2665</v>
       </c>
       <c r="Z12" s="25" t="s">
         <v>352</v>
       </c>
       <c r="AA12" s="25" t="s">
-        <v>2637</v>
+        <v>2666</v>
       </c>
       <c r="AB12" s="25" t="s">
         <v>298</v>
       </c>
       <c r="AC12" s="25" t="s">
-        <v>2638</v>
+        <v>2667</v>
       </c>
       <c r="AD12" s="25"/>
       <c r="AE12" s="25"/>
@@ -21227,19 +20581,19 @@
     </row>
     <row r="13" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="20" t="s">
-        <v>2639</v>
+        <v>2668</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>2640</v>
+        <v>2669</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>2641</v>
+        <v>2670</v>
       </c>
       <c r="D13" s="20" t="s">
         <v>84</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>2642</v>
+        <v>2671</v>
       </c>
       <c r="F13" s="21">
         <v>3995</v>
@@ -21262,16 +20616,16 @@
         <v>70</v>
       </c>
       <c r="N13" s="25" t="s">
-        <v>2527</v>
+        <v>2556</v>
       </c>
       <c r="O13" s="25" t="s">
         <v>414</v>
       </c>
       <c r="P13" s="25" t="s">
-        <v>2195</v>
+        <v>2219</v>
       </c>
       <c r="Q13" s="25" t="s">
-        <v>2615</v>
+        <v>2644</v>
       </c>
       <c r="R13" s="25" t="s">
         <v>1801</v>
@@ -21280,28 +20634,28 @@
         <v>1564</v>
       </c>
       <c r="T13" s="25" t="s">
-        <v>2616</v>
+        <v>2645</v>
       </c>
       <c r="U13" s="25" t="s">
-        <v>2643</v>
+        <v>2672</v>
       </c>
       <c r="V13" s="25" t="s">
         <v>517</v>
       </c>
       <c r="W13" s="25" t="s">
-        <v>2644</v>
+        <v>2673</v>
       </c>
       <c r="X13" s="25" t="s">
         <v>235</v>
       </c>
       <c r="Y13" s="25" t="s">
-        <v>2645</v>
+        <v>2674</v>
       </c>
       <c r="Z13" s="25" t="s">
         <v>352</v>
       </c>
       <c r="AA13" s="25" t="s">
-        <v>2646</v>
+        <v>2675</v>
       </c>
       <c r="AB13" s="25" t="s">
         <v>210</v>
@@ -21316,19 +20670,19 @@
     </row>
     <row r="14" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="20" t="s">
-        <v>2647</v>
+        <v>2676</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>2648</v>
+        <v>2677</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>2649</v>
+        <v>2678</v>
       </c>
       <c r="D14" s="20" t="s">
         <v>84</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>2650</v>
+        <v>2679</v>
       </c>
       <c r="F14" s="21">
         <v>7995</v>
@@ -21354,19 +20708,19 @@
         <v>296</v>
       </c>
       <c r="O14" s="25" t="s">
-        <v>2651</v>
+        <v>2680</v>
       </c>
       <c r="P14" s="25" t="s">
-        <v>2527</v>
+        <v>2556</v>
       </c>
       <c r="Q14" s="25" t="s">
         <v>643</v>
       </c>
       <c r="R14" s="25" t="s">
-        <v>2195</v>
+        <v>2219</v>
       </c>
       <c r="S14" s="25" t="s">
-        <v>2594</v>
+        <v>2623</v>
       </c>
       <c r="T14" s="25" t="s">
         <v>1801</v>
@@ -21375,53 +20729,53 @@
         <v>1564</v>
       </c>
       <c r="V14" s="25" t="s">
-        <v>2616</v>
+        <v>2645</v>
       </c>
       <c r="W14" s="25" t="s">
-        <v>2643</v>
+        <v>2672</v>
       </c>
       <c r="X14" s="25" t="s">
         <v>517</v>
       </c>
       <c r="Y14" s="25" t="s">
-        <v>2652</v>
+        <v>2681</v>
       </c>
       <c r="Z14" s="25" t="s">
         <v>235</v>
       </c>
       <c r="AA14" s="25" t="s">
-        <v>2653</v>
+        <v>2682</v>
       </c>
       <c r="AB14" s="25" t="s">
         <v>208</v>
       </c>
       <c r="AC14" s="25" t="s">
-        <v>2654</v>
+        <v>2683</v>
       </c>
       <c r="AD14" s="25" t="s">
         <v>936</v>
       </c>
       <c r="AE14" s="25" t="s">
-        <v>2655</v>
+        <v>2684</v>
       </c>
       <c r="AF14" s="25"/>
       <c r="AG14" s="25"/>
     </row>
     <row r="15" spans="1:33" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="20" t="s">
-        <v>2656</v>
+        <v>2685</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>2657</v>
+        <v>2686</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>2658</v>
+        <v>2687</v>
       </c>
       <c r="D15" s="20" t="s">
         <v>84</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>2659</v>
+        <v>2688</v>
       </c>
       <c r="F15" s="21">
         <v>1795</v>
@@ -21447,25 +20801,25 @@
         <v>1712</v>
       </c>
       <c r="O15" s="25" t="s">
-        <v>2660</v>
+        <v>2689</v>
       </c>
       <c r="P15" s="25" t="s">
-        <v>2661</v>
+        <v>2690</v>
       </c>
       <c r="Q15" s="25" t="s">
-        <v>2662</v>
+        <v>2691</v>
       </c>
       <c r="R15" s="25" t="s">
-        <v>2558</v>
+        <v>2587</v>
       </c>
       <c r="S15" s="25" t="s">
-        <v>2663</v>
+        <v>2692</v>
       </c>
       <c r="T15" s="25" t="s">
         <v>962</v>
       </c>
       <c r="U15" s="25" t="s">
-        <v>2664</v>
+        <v>2693</v>
       </c>
       <c r="V15" s="25"/>
       <c r="W15" s="25"/>
@@ -47899,17 +47253,29 @@
         <v>1993</v>
       </c>
       <c r="X2" s="20" t="s">
+        <v>1994</v>
+      </c>
+      <c r="Y2" s="20" t="s">
+        <v>1995</v>
+      </c>
+      <c r="Z2" s="20" t="s">
         <v>637</v>
       </c>
-      <c r="Y2" s="20" t="s">
-        <v>1994</v>
-      </c>
-      <c r="Z2" s="20"/>
-      <c r="AA2" s="25"/>
-      <c r="AB2" s="25"/>
-      <c r="AC2" s="25"/>
-      <c r="AD2" s="25"/>
-      <c r="AE2" s="25"/>
+      <c r="AA2" s="25" t="s">
+        <v>1996</v>
+      </c>
+      <c r="AB2" s="25" t="s">
+        <v>1997</v>
+      </c>
+      <c r="AC2" s="25" t="s">
+        <v>1998</v>
+      </c>
+      <c r="AD2" s="25" t="s">
+        <v>1805</v>
+      </c>
+      <c r="AE2" s="25" t="s">
+        <v>1999</v>
+      </c>
       <c r="AF2" s="25"/>
       <c r="AG2" s="25"/>
       <c r="AH2" s="25"/>
@@ -47917,19 +47283,19 @@
     </row>
     <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="20" t="s">
-        <v>1995</v>
+        <v>2000</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>1996</v>
+        <v>2001</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>1997</v>
+        <v>2002</v>
       </c>
       <c r="D3" s="20" t="s">
         <v>153</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>1998</v>
+        <v>2003</v>
       </c>
       <c r="F3" s="21">
         <v>2400</v>
@@ -47961,32 +47327,44 @@
         <v>1986</v>
       </c>
       <c r="Q3" s="20" t="s">
-        <v>1999</v>
+        <v>2004</v>
       </c>
       <c r="R3" s="20" t="s">
         <v>1988</v>
       </c>
       <c r="S3" s="20" t="s">
-        <v>2000</v>
+        <v>2005</v>
       </c>
       <c r="T3" s="20" t="s">
         <v>1990</v>
       </c>
       <c r="U3" s="20" t="s">
-        <v>2001</v>
+        <v>2006</v>
       </c>
       <c r="V3" s="20" t="s">
+        <v>1992</v>
+      </c>
+      <c r="W3" s="20" t="s">
+        <v>2007</v>
+      </c>
+      <c r="X3" s="20" t="s">
+        <v>2008</v>
+      </c>
+      <c r="Y3" s="20" t="s">
+        <v>2009</v>
+      </c>
+      <c r="Z3" s="20" t="s">
         <v>950</v>
       </c>
-      <c r="W3" s="20" t="s">
-        <v>2002</v>
-      </c>
-      <c r="X3" s="20"/>
-      <c r="Y3" s="20"/>
-      <c r="Z3" s="20"/>
-      <c r="AA3" s="25"/>
-      <c r="AB3" s="25"/>
-      <c r="AC3" s="25"/>
+      <c r="AA3" s="25" t="s">
+        <v>2010</v>
+      </c>
+      <c r="AB3" s="25" t="s">
+        <v>1805</v>
+      </c>
+      <c r="AC3" s="25" t="s">
+        <v>2011</v>
+      </c>
       <c r="AD3" s="25"/>
       <c r="AE3" s="25"/>
       <c r="AF3" s="25"/>
@@ -47996,19 +47374,19 @@
     </row>
     <row r="4" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="20" t="s">
-        <v>2003</v>
+        <v>2012</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>2004</v>
+        <v>2013</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>2005</v>
+        <v>2014</v>
       </c>
       <c r="D4" s="20" t="s">
         <v>153</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>2006</v>
+        <v>2015</v>
       </c>
       <c r="F4" s="21">
         <v>1400</v>
@@ -48040,20 +47418,32 @@
         <v>1986</v>
       </c>
       <c r="Q4" s="20" t="s">
-        <v>2007</v>
+        <v>2016</v>
       </c>
       <c r="R4" s="20" t="s">
         <v>1988</v>
       </c>
       <c r="S4" s="20" t="s">
-        <v>2008</v>
-      </c>
-      <c r="T4" s="20"/>
-      <c r="U4" s="20"/>
-      <c r="V4" s="20"/>
-      <c r="W4" s="20"/>
-      <c r="X4" s="20"/>
-      <c r="Y4" s="20"/>
+        <v>2017</v>
+      </c>
+      <c r="T4" s="20" t="s">
+        <v>1990</v>
+      </c>
+      <c r="U4" s="20" t="s">
+        <v>2018</v>
+      </c>
+      <c r="V4" s="20" t="s">
+        <v>950</v>
+      </c>
+      <c r="W4" s="20" t="s">
+        <v>2019</v>
+      </c>
+      <c r="X4" s="20" t="s">
+        <v>1805</v>
+      </c>
+      <c r="Y4" s="20" t="s">
+        <v>2020</v>
+      </c>
       <c r="Z4" s="20"/>
       <c r="AA4" s="25"/>
       <c r="AB4" s="25"/>
@@ -48067,19 +47457,19 @@
     </row>
     <row r="5" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="20" t="s">
-        <v>2009</v>
+        <v>2021</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>2011</v>
+        <v>2023</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>153</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>2012</v>
+        <v>2024</v>
       </c>
       <c r="F5" s="21">
         <v>2000</v>
@@ -48111,32 +47501,44 @@
         <v>1986</v>
       </c>
       <c r="Q5" s="20" t="s">
-        <v>2013</v>
+        <v>2025</v>
       </c>
       <c r="R5" s="20" t="s">
         <v>1988</v>
       </c>
       <c r="S5" s="20" t="s">
-        <v>2014</v>
+        <v>2026</v>
       </c>
       <c r="T5" s="20" t="s">
-        <v>2015</v>
+        <v>1990</v>
       </c>
       <c r="U5" s="20" t="s">
-        <v>2016</v>
+        <v>2027</v>
       </c>
       <c r="V5" s="20" t="s">
-        <v>2017</v>
+        <v>2028</v>
       </c>
       <c r="W5" s="20" t="s">
-        <v>2018</v>
-      </c>
-      <c r="X5" s="20"/>
-      <c r="Y5" s="20"/>
-      <c r="Z5" s="20"/>
-      <c r="AA5" s="25"/>
-      <c r="AB5" s="25"/>
-      <c r="AC5" s="25"/>
+        <v>2029</v>
+      </c>
+      <c r="X5" s="20" t="s">
+        <v>2030</v>
+      </c>
+      <c r="Y5" s="20" t="s">
+        <v>2031</v>
+      </c>
+      <c r="Z5" s="20" t="s">
+        <v>2032</v>
+      </c>
+      <c r="AA5" s="25" t="s">
+        <v>2033</v>
+      </c>
+      <c r="AB5" s="25" t="s">
+        <v>1805</v>
+      </c>
+      <c r="AC5" s="25" t="s">
+        <v>2034</v>
+      </c>
       <c r="AD5" s="25"/>
       <c r="AE5" s="25"/>
       <c r="AF5" s="25"/>
@@ -48146,19 +47548,19 @@
     </row>
     <row r="6" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="20" t="s">
-        <v>2019</v>
+        <v>2035</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>2020</v>
+        <v>2036</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>2021</v>
+        <v>2037</v>
       </c>
       <c r="D6" s="20" t="s">
         <v>153</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>2022</v>
+        <v>2038</v>
       </c>
       <c r="F6" s="21">
         <v>1050</v>
@@ -48190,26 +47592,38 @@
         <v>1986</v>
       </c>
       <c r="Q6" s="20" t="s">
-        <v>2023</v>
+        <v>2039</v>
       </c>
       <c r="R6" s="20" t="s">
-        <v>2024</v>
+        <v>1988</v>
       </c>
       <c r="S6" s="20" t="s">
-        <v>2025</v>
+        <v>2040</v>
       </c>
       <c r="T6" s="20" t="s">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="U6" s="20" t="s">
-        <v>2026</v>
-      </c>
-      <c r="V6" s="20"/>
-      <c r="W6" s="20"/>
-      <c r="X6" s="20"/>
-      <c r="Y6" s="20"/>
-      <c r="Z6" s="20"/>
-      <c r="AA6" s="25"/>
+        <v>2041</v>
+      </c>
+      <c r="V6" s="20" t="s">
+        <v>1994</v>
+      </c>
+      <c r="W6" s="20" t="s">
+        <v>2042</v>
+      </c>
+      <c r="X6" s="20" t="s">
+        <v>637</v>
+      </c>
+      <c r="Y6" s="20" t="s">
+        <v>2043</v>
+      </c>
+      <c r="Z6" s="20" t="s">
+        <v>1805</v>
+      </c>
+      <c r="AA6" s="25" t="s">
+        <v>2044</v>
+      </c>
       <c r="AB6" s="25"/>
       <c r="AC6" s="25"/>
       <c r="AD6" s="25"/>
@@ -48221,19 +47635,19 @@
     </row>
     <row r="7" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="20" t="s">
-        <v>2027</v>
+        <v>2045</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>2028</v>
+        <v>2046</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>2029</v>
+        <v>2047</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>153</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>2030</v>
+        <v>2048</v>
       </c>
       <c r="F7" s="21">
         <v>700</v>
@@ -48265,24 +47679,44 @@
         <v>1986</v>
       </c>
       <c r="Q7" s="20" t="s">
-        <v>2031</v>
+        <v>2049</v>
       </c>
       <c r="R7" s="20" t="s">
-        <v>2024</v>
+        <v>1988</v>
       </c>
       <c r="S7" s="20" t="s">
-        <v>2032</v>
-      </c>
-      <c r="T7" s="20"/>
-      <c r="U7" s="20"/>
-      <c r="V7" s="20"/>
-      <c r="W7" s="20"/>
-      <c r="X7" s="20"/>
-      <c r="Y7" s="20"/>
-      <c r="Z7" s="20"/>
-      <c r="AA7" s="25"/>
-      <c r="AB7" s="25"/>
-      <c r="AC7" s="25"/>
+        <v>2050</v>
+      </c>
+      <c r="T7" s="20" t="s">
+        <v>1990</v>
+      </c>
+      <c r="U7" s="20" t="s">
+        <v>2051</v>
+      </c>
+      <c r="V7" s="20" t="s">
+        <v>2028</v>
+      </c>
+      <c r="W7" s="20" t="s">
+        <v>2052</v>
+      </c>
+      <c r="X7" s="20" t="s">
+        <v>1994</v>
+      </c>
+      <c r="Y7" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="Z7" s="20" t="s">
+        <v>637</v>
+      </c>
+      <c r="AA7" s="25" t="s">
+        <v>2054</v>
+      </c>
+      <c r="AB7" s="25" t="s">
+        <v>1805</v>
+      </c>
+      <c r="AC7" s="25" t="s">
+        <v>2055</v>
+      </c>
       <c r="AD7" s="25"/>
       <c r="AE7" s="25"/>
       <c r="AF7" s="25"/>
@@ -48292,19 +47726,19 @@
     </row>
     <row r="8" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="20" t="s">
-        <v>2033</v>
+        <v>2056</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>2034</v>
+        <v>2057</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>2035</v>
+        <v>2058</v>
       </c>
       <c r="D8" s="20" t="s">
         <v>153</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>2036</v>
+        <v>2059</v>
       </c>
       <c r="F8" s="21">
         <v>600</v>
@@ -48336,24 +47770,32 @@
         <v>1986</v>
       </c>
       <c r="Q8" s="20" t="s">
-        <v>2037</v>
+        <v>2060</v>
       </c>
       <c r="R8" s="20" t="s">
-        <v>2024</v>
+        <v>1988</v>
       </c>
       <c r="S8" s="20" t="s">
-        <v>2038</v>
+        <v>2061</v>
       </c>
       <c r="T8" s="20" t="s">
-        <v>556</v>
+        <v>1990</v>
       </c>
       <c r="U8" s="20" t="s">
-        <v>2039</v>
-      </c>
-      <c r="V8" s="20"/>
-      <c r="W8" s="20"/>
-      <c r="X8" s="20"/>
-      <c r="Y8" s="20"/>
+        <v>2062</v>
+      </c>
+      <c r="V8" s="20" t="s">
+        <v>1994</v>
+      </c>
+      <c r="W8" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="X8" s="20" t="s">
+        <v>637</v>
+      </c>
+      <c r="Y8" s="20" t="s">
+        <v>2063</v>
+      </c>
       <c r="Z8" s="20"/>
       <c r="AA8" s="25"/>
       <c r="AB8" s="25"/>
@@ -48807,7 +48249,7 @@
         <v>65</v>
       </c>
       <c r="O1" s="18" t="s">
-        <v>2040</v>
+        <v>2064</v>
       </c>
       <c r="P1" s="19" t="s">
         <v>181</v>
@@ -48872,19 +48314,19 @@
     </row>
     <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="20" t="s">
-        <v>2041</v>
+        <v>2065</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>2042</v>
+        <v>2066</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>2043</v>
+        <v>2067</v>
       </c>
       <c r="D2" s="20" t="s">
         <v>146</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>2044</v>
+        <v>2068</v>
       </c>
       <c r="F2" s="24">
         <v>395</v>
@@ -48913,40 +48355,40 @@
         <v>2000</v>
       </c>
       <c r="P2" s="20" t="s">
-        <v>2045</v>
+        <v>2069</v>
       </c>
       <c r="Q2" s="20" t="s">
-        <v>2046</v>
+        <v>2070</v>
       </c>
       <c r="R2" s="20" t="s">
         <v>147</v>
       </c>
       <c r="S2" s="20" t="s">
-        <v>2047</v>
+        <v>2071</v>
       </c>
       <c r="T2" s="20" t="s">
-        <v>2048</v>
+        <v>2072</v>
       </c>
       <c r="U2" s="20" t="s">
-        <v>2049</v>
+        <v>2073</v>
       </c>
       <c r="V2" s="20" t="s">
-        <v>2050</v>
+        <v>2074</v>
       </c>
       <c r="W2" s="20" t="s">
-        <v>2051</v>
+        <v>2075</v>
       </c>
       <c r="X2" s="20" t="s">
-        <v>2052</v>
+        <v>2076</v>
       </c>
       <c r="Y2" s="20" t="s">
-        <v>2053</v>
+        <v>2077</v>
       </c>
       <c r="Z2" s="20" t="s">
-        <v>2054</v>
+        <v>2078</v>
       </c>
       <c r="AA2" s="20" t="s">
-        <v>2055</v>
+        <v>2079</v>
       </c>
       <c r="AB2" s="20"/>
       <c r="AC2" s="20"/>
@@ -48959,19 +48401,19 @@
     </row>
     <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="20" t="s">
-        <v>2056</v>
+        <v>2080</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>2057</v>
+        <v>2081</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>2058</v>
+        <v>2082</v>
       </c>
       <c r="D3" s="20" t="s">
         <v>146</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>2059</v>
+        <v>2083</v>
       </c>
       <c r="F3" s="24">
         <v>275</v>
@@ -49000,40 +48442,40 @@
         <v>1200</v>
       </c>
       <c r="P3" s="20" t="s">
-        <v>2045</v>
+        <v>2069</v>
       </c>
       <c r="Q3" s="20" t="s">
-        <v>2046</v>
+        <v>2070</v>
       </c>
       <c r="R3" s="20" t="s">
         <v>147</v>
       </c>
       <c r="S3" s="20" t="s">
-        <v>2047</v>
+        <v>2071</v>
       </c>
       <c r="T3" s="20" t="s">
-        <v>2048</v>
+        <v>2072</v>
       </c>
       <c r="U3" s="20" t="s">
-        <v>2060</v>
+        <v>2084</v>
       </c>
       <c r="V3" s="20" t="s">
-        <v>2050</v>
+        <v>2074</v>
       </c>
       <c r="W3" s="20" t="s">
-        <v>2061</v>
+        <v>2085</v>
       </c>
       <c r="X3" s="20" t="s">
-        <v>2052</v>
+        <v>2076</v>
       </c>
       <c r="Y3" s="20" t="s">
-        <v>2053</v>
+        <v>2077</v>
       </c>
       <c r="Z3" s="20" t="s">
-        <v>2054</v>
+        <v>2078</v>
       </c>
       <c r="AA3" s="20" t="s">
-        <v>2055</v>
+        <v>2079</v>
       </c>
       <c r="AB3" s="20"/>
       <c r="AC3" s="20"/>
@@ -49046,19 +48488,19 @@
     </row>
     <row r="4" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="20" t="s">
-        <v>2062</v>
+        <v>2086</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>2063</v>
+        <v>2087</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>2064</v>
+        <v>2088</v>
       </c>
       <c r="D4" s="20" t="s">
         <v>146</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>2065</v>
+        <v>2089</v>
       </c>
       <c r="F4" s="24">
         <v>525</v>
@@ -49087,40 +48529,40 @@
         <v>2500</v>
       </c>
       <c r="P4" s="20" t="s">
-        <v>2045</v>
+        <v>2069</v>
       </c>
       <c r="Q4" s="20" t="s">
-        <v>2066</v>
+        <v>2090</v>
       </c>
       <c r="R4" s="20" t="s">
         <v>147</v>
       </c>
       <c r="S4" s="20" t="s">
-        <v>2047</v>
+        <v>2071</v>
       </c>
       <c r="T4" s="20" t="s">
-        <v>2048</v>
+        <v>2072</v>
       </c>
       <c r="U4" s="20" t="s">
-        <v>2049</v>
+        <v>2073</v>
       </c>
       <c r="V4" s="20" t="s">
-        <v>2050</v>
+        <v>2074</v>
       </c>
       <c r="W4" s="20" t="s">
-        <v>2067</v>
+        <v>2091</v>
       </c>
       <c r="X4" s="20" t="s">
-        <v>2052</v>
+        <v>2076</v>
       </c>
       <c r="Y4" s="20" t="s">
-        <v>2053</v>
+        <v>2077</v>
       </c>
       <c r="Z4" s="20" t="s">
-        <v>2054</v>
+        <v>2078</v>
       </c>
       <c r="AA4" s="20" t="s">
-        <v>2055</v>
+        <v>2079</v>
       </c>
       <c r="AB4" s="20"/>
       <c r="AC4" s="20"/>
@@ -49133,19 +48575,19 @@
     </row>
     <row r="5" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="20" t="s">
-        <v>2068</v>
+        <v>2092</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>2069</v>
+        <v>2093</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>2070</v>
+        <v>2094</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>146</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>2071</v>
+        <v>2095</v>
       </c>
       <c r="F5" s="24">
         <v>325</v>
@@ -49174,40 +48616,40 @@
         <v>2000</v>
       </c>
       <c r="P5" s="20" t="s">
-        <v>2045</v>
+        <v>2069</v>
       </c>
       <c r="Q5" s="20" t="s">
-        <v>2072</v>
+        <v>2096</v>
       </c>
       <c r="R5" s="20" t="s">
         <v>147</v>
       </c>
       <c r="S5" s="20" t="s">
-        <v>2047</v>
+        <v>2071</v>
       </c>
       <c r="T5" s="20" t="s">
-        <v>2048</v>
+        <v>2072</v>
       </c>
       <c r="U5" s="20" t="s">
-        <v>2049</v>
+        <v>2073</v>
       </c>
       <c r="V5" s="20" t="s">
-        <v>2050</v>
+        <v>2074</v>
       </c>
       <c r="W5" s="20" t="s">
-        <v>2051</v>
+        <v>2075</v>
       </c>
       <c r="X5" s="20" t="s">
-        <v>2052</v>
+        <v>2076</v>
       </c>
       <c r="Y5" s="20" t="s">
-        <v>2053</v>
+        <v>2077</v>
       </c>
       <c r="Z5" s="20" t="s">
-        <v>2054</v>
+        <v>2078</v>
       </c>
       <c r="AA5" s="20" t="s">
-        <v>2073</v>
+        <v>2097</v>
       </c>
       <c r="AB5" s="20"/>
       <c r="AC5" s="20"/>
@@ -49220,19 +48662,19 @@
     </row>
     <row r="6" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="20" t="s">
-        <v>2074</v>
+        <v>2098</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>2075</v>
+        <v>2099</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>2076</v>
+        <v>2100</v>
       </c>
       <c r="D6" s="20" t="s">
         <v>146</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>2077</v>
+        <v>2101</v>
       </c>
       <c r="F6" s="24">
         <v>225</v>
@@ -49261,40 +48703,40 @@
         <v>1200</v>
       </c>
       <c r="P6" s="20" t="s">
-        <v>2045</v>
+        <v>2069</v>
       </c>
       <c r="Q6" s="20" t="s">
-        <v>2046</v>
+        <v>2070</v>
       </c>
       <c r="R6" s="20" t="s">
         <v>147</v>
       </c>
       <c r="S6" s="20" t="s">
-        <v>2047</v>
+        <v>2071</v>
       </c>
       <c r="T6" s="20" t="s">
-        <v>2048</v>
+        <v>2072</v>
       </c>
       <c r="U6" s="20" t="s">
-        <v>2060</v>
+        <v>2084</v>
       </c>
       <c r="V6" s="20" t="s">
-        <v>2050</v>
+        <v>2074</v>
       </c>
       <c r="W6" s="20" t="s">
-        <v>2061</v>
+        <v>2085</v>
       </c>
       <c r="X6" s="20" t="s">
-        <v>2052</v>
+        <v>2076</v>
       </c>
       <c r="Y6" s="20" t="s">
-        <v>2053</v>
+        <v>2077</v>
       </c>
       <c r="Z6" s="20" t="s">
-        <v>2054</v>
+        <v>2078</v>
       </c>
       <c r="AA6" s="20" t="s">
-        <v>2073</v>
+        <v>2097</v>
       </c>
       <c r="AB6" s="20"/>
       <c r="AC6" s="20"/>
@@ -49307,19 +48749,19 @@
     </row>
     <row r="7" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="20" t="s">
-        <v>2078</v>
+        <v>2102</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>2079</v>
+        <v>2103</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>2080</v>
+        <v>2104</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>84</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>2081</v>
+        <v>2105</v>
       </c>
       <c r="F7" s="24">
         <v>950</v>
@@ -49346,40 +48788,40 @@
       </c>
       <c r="O7" s="22"/>
       <c r="P7" s="20" t="s">
-        <v>2045</v>
+        <v>2069</v>
       </c>
       <c r="Q7" s="20" t="s">
-        <v>2082</v>
+        <v>2106</v>
       </c>
       <c r="R7" s="20" t="s">
         <v>147</v>
       </c>
       <c r="S7" s="20" t="s">
-        <v>2047</v>
+        <v>2071</v>
       </c>
       <c r="T7" s="20" t="s">
-        <v>2054</v>
+        <v>2078</v>
       </c>
       <c r="U7" s="20" t="s">
-        <v>2083</v>
+        <v>2107</v>
       </c>
       <c r="V7" s="20" t="s">
-        <v>2084</v>
+        <v>2108</v>
       </c>
       <c r="W7" s="20" t="s">
-        <v>2085</v>
+        <v>2109</v>
       </c>
       <c r="X7" s="20" t="s">
-        <v>2086</v>
+        <v>2110</v>
       </c>
       <c r="Y7" s="20" t="s">
-        <v>2087</v>
+        <v>2111</v>
       </c>
       <c r="Z7" s="20" t="s">
-        <v>2088</v>
+        <v>2112</v>
       </c>
       <c r="AA7" s="20" t="s">
-        <v>2089</v>
+        <v>2113</v>
       </c>
       <c r="AB7" s="20"/>
       <c r="AC7" s="20"/>
@@ -49392,19 +48834,19 @@
     </row>
     <row r="8" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="20" t="s">
-        <v>2090</v>
+        <v>2114</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>2091</v>
+        <v>2115</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>2092</v>
+        <v>2116</v>
       </c>
       <c r="D8" s="20" t="s">
         <v>84</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>2093</v>
+        <v>2117</v>
       </c>
       <c r="F8" s="24">
         <v>1825</v>
@@ -49431,40 +48873,40 @@
       </c>
       <c r="O8" s="22"/>
       <c r="P8" s="20" t="s">
-        <v>2045</v>
+        <v>2069</v>
       </c>
       <c r="Q8" s="20" t="s">
-        <v>2094</v>
+        <v>2118</v>
       </c>
       <c r="R8" s="20" t="s">
         <v>147</v>
       </c>
       <c r="S8" s="20" t="s">
-        <v>2047</v>
+        <v>2071</v>
       </c>
       <c r="T8" s="20" t="s">
-        <v>2048</v>
+        <v>2072</v>
       </c>
       <c r="U8" s="20" t="s">
-        <v>2095</v>
+        <v>2119</v>
       </c>
       <c r="V8" s="20" t="s">
-        <v>2050</v>
+        <v>2074</v>
       </c>
       <c r="W8" s="20" t="s">
-        <v>2096</v>
+        <v>2120</v>
       </c>
       <c r="X8" s="20" t="s">
-        <v>2052</v>
+        <v>2076</v>
       </c>
       <c r="Y8" s="20" t="s">
-        <v>2097</v>
+        <v>2121</v>
       </c>
       <c r="Z8" s="20" t="s">
-        <v>2084</v>
+        <v>2108</v>
       </c>
       <c r="AA8" s="20" t="s">
-        <v>2098</v>
+        <v>2122</v>
       </c>
       <c r="AB8" s="20"/>
       <c r="AC8" s="20"/>
@@ -49477,19 +48919,19 @@
     </row>
     <row r="9" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="20" t="s">
-        <v>2099</v>
+        <v>2123</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>2100</v>
+        <v>2124</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>2101</v>
+        <v>2125</v>
       </c>
       <c r="D9" s="20" t="s">
         <v>84</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>2102</v>
+        <v>2126</v>
       </c>
       <c r="F9" s="24">
         <v>950</v>
@@ -49516,40 +48958,40 @@
       </c>
       <c r="O9" s="22"/>
       <c r="P9" s="20" t="s">
-        <v>2045</v>
+        <v>2069</v>
       </c>
       <c r="Q9" s="20" t="s">
-        <v>2103</v>
+        <v>2127</v>
       </c>
       <c r="R9" s="20" t="s">
         <v>147</v>
       </c>
       <c r="S9" s="20" t="s">
-        <v>2047</v>
+        <v>2071</v>
       </c>
       <c r="T9" s="20" t="s">
-        <v>2048</v>
+        <v>2072</v>
       </c>
       <c r="U9" s="20" t="s">
-        <v>2104</v>
+        <v>2128</v>
       </c>
       <c r="V9" s="20" t="s">
-        <v>2050</v>
+        <v>2074</v>
       </c>
       <c r="W9" s="20" t="s">
-        <v>2105</v>
+        <v>2129</v>
       </c>
       <c r="X9" s="20" t="s">
-        <v>2052</v>
+        <v>2076</v>
       </c>
       <c r="Y9" s="20" t="s">
-        <v>2106</v>
+        <v>2130</v>
       </c>
       <c r="Z9" s="20" t="s">
-        <v>2084</v>
+        <v>2108</v>
       </c>
       <c r="AA9" s="20" t="s">
-        <v>2098</v>
+        <v>2122</v>
       </c>
       <c r="AB9" s="20"/>
       <c r="AC9" s="20"/>
@@ -49562,19 +49004,19 @@
     </row>
     <row r="10" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="20" t="s">
-        <v>2107</v>
+        <v>2131</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>2108</v>
+        <v>2132</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>2109</v>
+        <v>2133</v>
       </c>
       <c r="D10" s="20" t="s">
         <v>140</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>2110</v>
+        <v>2134</v>
       </c>
       <c r="F10" s="24">
         <v>1595</v>
@@ -49603,46 +49045,46 @@
         <v>1200</v>
       </c>
       <c r="P10" s="20" t="s">
-        <v>2045</v>
+        <v>2069</v>
       </c>
       <c r="Q10" s="20" t="s">
-        <v>2111</v>
+        <v>2135</v>
       </c>
       <c r="R10" s="20" t="s">
         <v>147</v>
       </c>
       <c r="S10" s="20" t="s">
-        <v>2047</v>
+        <v>2071</v>
       </c>
       <c r="T10" s="20" t="s">
-        <v>2048</v>
+        <v>2072</v>
       </c>
       <c r="U10" s="20" t="s">
-        <v>2112</v>
+        <v>2136</v>
       </c>
       <c r="V10" s="20" t="s">
-        <v>2050</v>
+        <v>2074</v>
       </c>
       <c r="W10" s="20" t="s">
-        <v>2113</v>
+        <v>2137</v>
       </c>
       <c r="X10" s="20" t="s">
-        <v>2052</v>
+        <v>2076</v>
       </c>
       <c r="Y10" s="20" t="s">
-        <v>2114</v>
+        <v>2138</v>
       </c>
       <c r="Z10" s="20" t="s">
-        <v>2054</v>
+        <v>2078</v>
       </c>
       <c r="AA10" s="20" t="s">
-        <v>2115</v>
+        <v>2139</v>
       </c>
       <c r="AB10" s="20" t="s">
-        <v>2084</v>
+        <v>2108</v>
       </c>
       <c r="AC10" s="20" t="s">
-        <v>2116</v>
+        <v>2140</v>
       </c>
       <c r="AD10" s="20"/>
       <c r="AE10" s="25"/>
@@ -49653,19 +49095,19 @@
     </row>
     <row r="11" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="20" t="s">
-        <v>2117</v>
+        <v>2141</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>2118</v>
+        <v>2142</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>2119</v>
+        <v>2143</v>
       </c>
       <c r="D11" s="20" t="s">
         <v>140</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>2120</v>
+        <v>2144</v>
       </c>
       <c r="F11" s="24">
         <v>875</v>
@@ -49692,46 +49134,46 @@
       </c>
       <c r="O11" s="22"/>
       <c r="P11" s="20" t="s">
-        <v>2045</v>
+        <v>2069</v>
       </c>
       <c r="Q11" s="20" t="s">
-        <v>2121</v>
+        <v>2145</v>
       </c>
       <c r="R11" s="20" t="s">
         <v>147</v>
       </c>
       <c r="S11" s="20" t="s">
-        <v>2047</v>
+        <v>2071</v>
       </c>
       <c r="T11" s="20" t="s">
-        <v>2048</v>
+        <v>2072</v>
       </c>
       <c r="U11" s="20" t="s">
-        <v>2122</v>
+        <v>2146</v>
       </c>
       <c r="V11" s="20" t="s">
-        <v>2050</v>
+        <v>2074</v>
       </c>
       <c r="W11" s="20" t="s">
-        <v>2123</v>
+        <v>2147</v>
       </c>
       <c r="X11" s="20" t="s">
-        <v>2054</v>
+        <v>2078</v>
       </c>
       <c r="Y11" s="20" t="s">
-        <v>2115</v>
+        <v>2139</v>
       </c>
       <c r="Z11" s="20" t="s">
-        <v>2084</v>
+        <v>2108</v>
       </c>
       <c r="AA11" s="20" t="s">
-        <v>2116</v>
+        <v>2140</v>
       </c>
       <c r="AB11" s="20" t="s">
-        <v>2124</v>
+        <v>2148</v>
       </c>
       <c r="AC11" s="20" t="s">
-        <v>2114</v>
+        <v>2138</v>
       </c>
       <c r="AD11" s="20"/>
       <c r="AE11" s="25"/>
